--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15105" windowHeight="11655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialAuxiliary" sheetId="1" r:id="rId1"/>
@@ -972,7 +972,7 @@
     <t>寻宝黄金城</t>
   </si>
   <si>
-    <t>10260009|10260001|10260005|10260006|10260007</t>
+    <t>10260009|10260001|10260005|10260006|10260007|10260010</t>
   </si>
   <si>
     <t>概率改出SCATTER符号+概率改出百搭wild符号+概率改出占据2、3、4个格子符号</t>
@@ -1480,7 +1480,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1498,20 +1499,19 @@
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -56440,7 +56440,7 @@
         <v>243</v>
       </c>
       <c r="D112" s="26">
-        <v>305001</v>
+        <v>305101</v>
       </c>
       <c r="E112" s="26" t="s">
         <v>244</v>
@@ -56476,7 +56476,7 @@
         <v>243</v>
       </c>
       <c r="D113" s="26">
-        <v>305002</v>
+        <v>305102</v>
       </c>
       <c r="E113" s="26" t="s">
         <v>247</v>
@@ -56512,7 +56512,7 @@
         <v>243</v>
       </c>
       <c r="D114" s="26">
-        <v>305003</v>
+        <v>305103</v>
       </c>
       <c r="E114" s="26" t="s">
         <v>250</v>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialAuxiliary" sheetId="1" r:id="rId1"/>
@@ -1053,7 +1053,7 @@
     <t>麻将胡了2</t>
   </si>
   <si>
-    <t>10530001|10530016|10530017</t>
+    <t>10530003|10530004|10530006|10530005</t>
   </si>
   <si>
     <t>概率改出SCATTER符号+第3轴必然出现金色符号+异形位置改为不中奖图案</t>
@@ -1062,16 +1062,16 @@
     <t>赏金大对决</t>
   </si>
   <si>
-    <t>10570002|10570001|10570006|10570015</t>
+    <t>10570001|10570004|10570006</t>
   </si>
   <si>
-    <t>概率改出SCATTER符号+概率改出百搭wild符号+概率改出金框符号+异形位置改为不中奖图案</t>
+    <t>概率改出SCATTER符号+概率改出金框符号+异形位置改为不中奖图案</t>
   </si>
   <si>
     <t>极速糖果1000</t>
   </si>
   <si>
-    <t>10580001|10580003</t>
+    <t>10580001|10580004</t>
   </si>
   <si>
     <t>概率改出SCATTER符号+概率改出奖池符号</t>
@@ -1529,24 +1529,11 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1561,6 +1548,19 @@
     <font>
       <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -56543,7 +56543,7 @@
       </c>
       <c r="T112" s="164"/>
     </row>
-    <row r="113" s="26" customFormat="1" ht="16.5" spans="1:20">
+    <row r="113" s="26" customFormat="1" ht="18" customHeight="1" spans="1:20">
       <c r="A113" s="26">
         <v>30510002</v>
       </c>
@@ -56851,7 +56851,7 @@
         <v>111</v>
       </c>
       <c r="G121" s="28">
-        <v>205301</v>
+        <v>2053001</v>
       </c>
       <c r="H121" s="169" t="s">
         <v>63</v>
@@ -56887,7 +56887,7 @@
         <v>82</v>
       </c>
       <c r="G122" s="28">
-        <v>205301</v>
+        <v>2053001</v>
       </c>
       <c r="H122" s="169" t="s">
         <v>63</v>
@@ -56923,7 +56923,7 @@
         <v>86</v>
       </c>
       <c r="G123" s="28">
-        <v>205301</v>
+        <v>2053001</v>
       </c>
       <c r="H123" s="169" t="s">
         <v>63</v>
@@ -56959,7 +56959,7 @@
         <v>111</v>
       </c>
       <c r="G124" s="172">
-        <v>205701</v>
+        <v>2057001</v>
       </c>
       <c r="H124" s="174" t="s">
         <v>63</v>
@@ -56995,7 +56995,7 @@
         <v>82</v>
       </c>
       <c r="G125" s="172">
-        <v>205701</v>
+        <v>2057001</v>
       </c>
       <c r="H125" s="174" t="s">
         <v>63</v>
@@ -57031,7 +57031,7 @@
         <v>86</v>
       </c>
       <c r="G126" s="172">
-        <v>205701</v>
+        <v>2057001</v>
       </c>
       <c r="H126" s="174" t="s">
         <v>63</v>
@@ -57067,7 +57067,7 @@
         <v>111</v>
       </c>
       <c r="G127" s="30">
-        <v>205801</v>
+        <v>2058001</v>
       </c>
       <c r="H127" s="176" t="s">
         <v>63</v>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialAuxiliary" sheetId="1" r:id="rId1"/>
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="351">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -1002,31 +1002,13 @@
     <t>糖果派对</t>
   </si>
   <si>
-    <t>免费游戏-第一层-免费旋转-10次</t>
+    <t>第一层-免费游戏-免费旋转10次</t>
   </si>
   <si>
-    <t>10510006|10510009</t>
+    <t>第二层-免费游戏-免费旋转10次</t>
   </si>
   <si>
-    <t>概率改出过关符号1+概率改出彩池符号</t>
-  </si>
-  <si>
-    <t>免费游戏-第二层-免费旋转-10次</t>
-  </si>
-  <si>
-    <t>10510007|10510009</t>
-  </si>
-  <si>
-    <t>概率改出过关符号2+概率改出彩池符号</t>
-  </si>
-  <si>
-    <t>免费游戏-第三层-免费旋转-10次</t>
-  </si>
-  <si>
-    <t>10510008|10510009</t>
-  </si>
-  <si>
-    <t>概率改出过关符号3+概率改出彩池符号</t>
+    <t>第三层-免费游戏-免费旋转10次</t>
   </si>
   <si>
     <t>黄金帝国</t>
@@ -1534,13 +1516,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1554,7 +1530,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1566,7 +1541,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1689,7 +1671,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2470,10 +2452,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -40116,7 +40100,7 @@
       <c r="XEL110" s="33"/>
       <c r="XEM110" s="33"/>
     </row>
-    <row r="111" s="25" customFormat="1" ht="16.5" spans="1:1024 1025:16367">
+    <row r="111" s="25" customFormat="1" ht="20" customHeight="1" spans="1:1024 1025:16367">
       <c r="A111" s="34">
         <v>30500003</v>
       </c>
@@ -56520,7 +56504,7 @@
       <c r="D112" s="26">
         <v>305101</v>
       </c>
-      <c r="E112" s="26" t="s">
+      <c r="E112" s="162" t="s">
         <v>244</v>
       </c>
       <c r="F112" s="26" t="s">
@@ -56529,21 +56513,19 @@
       <c r="G112" s="26">
         <v>2051001</v>
       </c>
-      <c r="H112" s="26" t="s">
+      <c r="H112" s="162" t="s">
         <v>63</v>
       </c>
-      <c r="I112" s="26" t="s">
+      <c r="I112" s="162" t="s">
         <v>83</v>
       </c>
-      <c r="K112" s="162" t="s">
-        <v>245</v>
-      </c>
-      <c r="L112" s="163" t="s">
-        <v>246</v>
-      </c>
+      <c r="K112" s="163"/>
+      <c r="L112" s="26"/>
+      <c r="M112" s="26"/>
+      <c r="N112" s="26"/>
       <c r="T112" s="164"/>
     </row>
-    <row r="113" s="26" customFormat="1" ht="18" customHeight="1" spans="1:20">
+    <row r="113" s="26" customFormat="1" ht="16.5" spans="1:20">
       <c r="A113" s="26">
         <v>30510002</v>
       </c>
@@ -56556,27 +56538,25 @@
       <c r="D113" s="26">
         <v>305102</v>
       </c>
-      <c r="E113" s="26" t="s">
-        <v>247</v>
+      <c r="E113" s="162" t="s">
+        <v>245</v>
       </c>
       <c r="F113" s="26" t="s">
         <v>111</v>
       </c>
       <c r="G113" s="26">
-        <v>2051001</v>
-      </c>
-      <c r="H113" s="26" t="s">
+        <v>2051002</v>
+      </c>
+      <c r="H113" s="162" t="s">
         <v>63</v>
       </c>
-      <c r="I113" s="26" t="s">
+      <c r="I113" s="162" t="s">
         <v>83</v>
       </c>
-      <c r="K113" s="162" t="s">
-        <v>248</v>
-      </c>
-      <c r="L113" s="163" t="s">
-        <v>249</v>
-      </c>
+      <c r="K113" s="163"/>
+      <c r="L113" s="26"/>
+      <c r="M113" s="26"/>
+      <c r="N113" s="26"/>
       <c r="T113" s="164"/>
     </row>
     <row r="114" s="26" customFormat="1" ht="16.5" spans="1:20">
@@ -56592,27 +56572,25 @@
       <c r="D114" s="26">
         <v>305103</v>
       </c>
-      <c r="E114" s="26" t="s">
-        <v>250</v>
+      <c r="E114" s="162" t="s">
+        <v>246</v>
       </c>
       <c r="F114" s="26" t="s">
         <v>111</v>
       </c>
       <c r="G114" s="26">
-        <v>2051001</v>
-      </c>
-      <c r="H114" s="26" t="s">
+        <v>2051003</v>
+      </c>
+      <c r="H114" s="162" t="s">
         <v>63</v>
       </c>
-      <c r="I114" s="26" t="s">
+      <c r="I114" s="162" t="s">
         <v>83</v>
       </c>
-      <c r="K114" s="162" t="s">
-        <v>251</v>
-      </c>
-      <c r="L114" s="163" t="s">
-        <v>252</v>
-      </c>
+      <c r="K114" s="163"/>
+      <c r="L114" s="26"/>
+      <c r="M114" s="26"/>
+      <c r="N114" s="26"/>
       <c r="T114" s="164"/>
     </row>
     <row r="115" s="27" customFormat="1" ht="16.5" spans="1:20">
@@ -56623,13 +56601,13 @@
         <v>400200</v>
       </c>
       <c r="C115" s="27" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D115" s="27">
         <v>300201</v>
       </c>
       <c r="E115" s="165" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="F115" s="27" t="s">
         <v>62</v>
@@ -56644,10 +56622,10 @@
         <v>83</v>
       </c>
       <c r="K115" s="166" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="L115" s="27" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="T115" s="167"/>
     </row>
@@ -56659,7 +56637,7 @@
         <v>400200</v>
       </c>
       <c r="C116" s="27" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D116" s="27">
         <v>300202</v>
@@ -56680,10 +56658,10 @@
         <v>83</v>
       </c>
       <c r="K116" s="166" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="L116" s="27" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="T116" s="167"/>
     </row>
@@ -56695,7 +56673,7 @@
         <v>400200</v>
       </c>
       <c r="C117" s="27" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D117" s="27">
         <v>300203</v>
@@ -56716,10 +56694,10 @@
         <v>83</v>
       </c>
       <c r="K117" s="166" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="L117" s="27" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="T117" s="167"/>
     </row>
@@ -56731,7 +56709,7 @@
         <v>100800</v>
       </c>
       <c r="C118" s="16" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="D118" s="16">
         <v>308001</v>
@@ -56752,10 +56730,10 @@
         <v>83</v>
       </c>
       <c r="K118" s="87" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="L118" s="21" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="T118" s="120"/>
     </row>
@@ -56767,7 +56745,7 @@
         <v>100800</v>
       </c>
       <c r="C119" s="16" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="D119" s="16">
         <v>308002</v>
@@ -56788,10 +56766,10 @@
         <v>83</v>
       </c>
       <c r="K119" s="87" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="L119" s="21" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="T119" s="120"/>
     </row>
@@ -56803,7 +56781,7 @@
         <v>100800</v>
       </c>
       <c r="C120" s="16" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="D120" s="16">
         <v>308003</v>
@@ -56824,10 +56802,10 @@
         <v>83</v>
       </c>
       <c r="K120" s="87" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="L120" s="21" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="T120" s="120"/>
     </row>
@@ -56839,7 +56817,7 @@
         <v>105300</v>
       </c>
       <c r="C121" s="59" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="D121" s="28">
         <v>305301</v>
@@ -56860,10 +56838,10 @@
         <v>83</v>
       </c>
       <c r="K121" s="28" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="L121" s="59" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="T121" s="170"/>
     </row>
@@ -56875,7 +56853,7 @@
         <v>105300</v>
       </c>
       <c r="C122" s="59" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="D122" s="28">
         <v>305302</v>
@@ -56896,10 +56874,10 @@
         <v>83</v>
       </c>
       <c r="K122" s="28" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="L122" s="59" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="T122" s="170"/>
     </row>
@@ -56911,7 +56889,7 @@
         <v>105300</v>
       </c>
       <c r="C123" s="59" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="D123" s="28">
         <v>305303</v>
@@ -56932,10 +56910,10 @@
         <v>83</v>
       </c>
       <c r="K123" s="28" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="L123" s="59" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="T123" s="171"/>
     </row>
@@ -56947,7 +56925,7 @@
         <v>105700</v>
       </c>
       <c r="C124" s="93" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="D124" s="172">
         <v>305701</v>
@@ -56968,10 +56946,10 @@
         <v>83</v>
       </c>
       <c r="K124" s="95" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="L124" s="172" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="T124" s="96"/>
     </row>
@@ -56983,7 +56961,7 @@
         <v>105700</v>
       </c>
       <c r="C125" s="93" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="D125" s="172">
         <v>305702</v>
@@ -57004,10 +56982,10 @@
         <v>83</v>
       </c>
       <c r="K125" s="95" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="L125" s="172" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="T125" s="96"/>
     </row>
@@ -57019,7 +56997,7 @@
         <v>105700</v>
       </c>
       <c r="C126" s="93" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="D126" s="172">
         <v>305703</v>
@@ -57040,10 +57018,10 @@
         <v>83</v>
       </c>
       <c r="K126" s="95" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="L126" s="172" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="T126" s="96"/>
     </row>
@@ -57055,7 +57033,7 @@
         <v>105800</v>
       </c>
       <c r="C127" s="175" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="D127" s="30">
         <v>305801</v>
@@ -57076,10 +57054,10 @@
         <v>83</v>
       </c>
       <c r="K127" s="177" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="L127" s="30" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="T127" s="178"/>
     </row>
@@ -57143,10 +57121,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -57154,7 +57132,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -57162,7 +57140,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -57170,16 +57148,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -57187,16 +57165,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -57204,16 +57182,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -57221,16 +57199,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -57238,16 +57216,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -57255,16 +57233,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -57272,16 +57250,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -57289,16 +57267,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -57306,16 +57284,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -57323,16 +57301,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -57340,16 +57318,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -57357,16 +57335,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -57374,16 +57352,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -57391,16 +57369,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -57408,7 +57386,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
@@ -57417,7 +57395,7 @@
         <v>188</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -57425,16 +57403,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -57442,16 +57420,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -57459,16 +57437,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -57476,16 +57454,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -57493,16 +57471,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -57510,16 +57488,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -57527,7 +57505,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -57535,7 +57513,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -57543,7 +57521,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -57551,7 +57529,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -57559,7 +57537,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -57567,7 +57545,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -57575,7 +57553,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -57583,7 +57561,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -57591,7 +57569,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -57599,7 +57577,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -57607,7 +57585,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -57615,7 +57593,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -57623,7 +57601,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -57631,7 +57609,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -57639,7 +57617,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -57647,7 +57625,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -57655,7 +57633,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -57663,7 +57641,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -57671,7 +57649,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -57679,7 +57657,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -57687,7 +57665,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -57695,7 +57673,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -57703,7 +57681,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14220" windowHeight="12240"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialAuxiliary" sheetId="1" r:id="rId1"/>
@@ -867,13 +867,13 @@
     <t>第三轴扩列成大wild</t>
   </si>
   <si>
+    <t>2_1</t>
+  </si>
+  <si>
     <t>在第三轴改出三个百搭wild</t>
   </si>
   <si>
     <t>在二三四扩列成大wild</t>
-  </si>
-  <si>
-    <t>2_1</t>
   </si>
   <si>
     <t>在二三四轴改出9个wild</t>
@@ -1544,17 +1544,13 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1563,6 +1559,11 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1580,14 +1581,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="57">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1782,49 +1782,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1860,67 +1818,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2106,76 +2010,76 @@
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -6659,7 +6563,7 @@
         <v>198</v>
       </c>
       <c r="F91" s="135" t="s">
-        <v>56</v>
+        <v>199</v>
       </c>
       <c r="G91" s="135">
         <v>2031001</v>
@@ -6673,7 +6577,7 @@
         <v>10310005</v>
       </c>
       <c r="L91" s="135" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M91" s="135"/>
       <c r="N91" s="135"/>
@@ -6698,10 +6602,10 @@
         <v>303102</v>
       </c>
       <c r="E92" s="135" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F92" s="135" t="s">
-        <v>201</v>
+        <v>56</v>
       </c>
       <c r="G92" s="135">
         <v>2031001</v>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialAuxiliary" sheetId="1" r:id="rId1"/>
@@ -1035,7 +1035,7 @@
     <t>麻将胡了2</t>
   </si>
   <si>
-    <t>10530003|10530004|10530006|10530005</t>
+    <t>10530003|10530004|10530006</t>
   </si>
   <si>
     <t>概率改出SCATTER符号+第3轴必然出现金色符号+异形位置改为不中奖图案</t>
@@ -1575,13 +1575,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2086,7 +2086,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="222">
+  <cellXfs count="215">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2255,9 +2255,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -2452,17 +2449,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2529,21 +2517,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4088,10 +4067,10 @@
       <c r="A31" s="74">
         <v>30120021</v>
       </c>
-      <c r="B31" s="84">
+      <c r="B31" s="77">
         <v>101200</v>
       </c>
-      <c r="C31" s="84" t="s">
+      <c r="C31" s="77" t="s">
         <v>95</v>
       </c>
       <c r="D31" s="74">
@@ -4103,7 +4082,7 @@
       <c r="F31" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="85">
+      <c r="G31" s="84">
         <v>2012001</v>
       </c>
       <c r="H31" s="23" t="s">
@@ -4113,7 +4092,7 @@
         <v>88</v>
       </c>
       <c r="J31" s="23"/>
-      <c r="K31" s="86">
+      <c r="K31" s="85">
         <v>10120041</v>
       </c>
     </row>
@@ -4121,10 +4100,10 @@
       <c r="A32" s="74">
         <v>30120022</v>
       </c>
-      <c r="B32" s="84">
+      <c r="B32" s="77">
         <v>101200</v>
       </c>
-      <c r="C32" s="84" t="s">
+      <c r="C32" s="77" t="s">
         <v>95</v>
       </c>
       <c r="D32" s="74">
@@ -4136,7 +4115,7 @@
       <c r="F32" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="G32" s="85">
+      <c r="G32" s="84">
         <v>2012001</v>
       </c>
       <c r="H32" s="23" t="s">
@@ -4146,7 +4125,7 @@
         <v>90</v>
       </c>
       <c r="J32" s="23"/>
-      <c r="K32" s="86">
+      <c r="K32" s="85">
         <v>10120042</v>
       </c>
     </row>
@@ -4154,10 +4133,10 @@
       <c r="A33" s="74">
         <v>30120023</v>
       </c>
-      <c r="B33" s="84">
+      <c r="B33" s="77">
         <v>101200</v>
       </c>
-      <c r="C33" s="84" t="s">
+      <c r="C33" s="77" t="s">
         <v>95</v>
       </c>
       <c r="D33" s="74">
@@ -4169,7 +4148,7 @@
       <c r="F33" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="G33" s="85">
+      <c r="G33" s="84">
         <v>2012001</v>
       </c>
       <c r="H33" s="23" t="s">
@@ -4179,7 +4158,7 @@
         <v>91</v>
       </c>
       <c r="J33" s="23"/>
-      <c r="K33" s="86">
+      <c r="K33" s="85">
         <v>10120043</v>
       </c>
     </row>
@@ -4187,10 +4166,10 @@
       <c r="A34" s="74">
         <v>30120024</v>
       </c>
-      <c r="B34" s="84">
+      <c r="B34" s="77">
         <v>101200</v>
       </c>
-      <c r="C34" s="84" t="s">
+      <c r="C34" s="77" t="s">
         <v>95</v>
       </c>
       <c r="D34" s="74">
@@ -4202,7 +4181,7 @@
       <c r="F34" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="G34" s="85">
+      <c r="G34" s="84">
         <v>2012001</v>
       </c>
       <c r="H34" s="23" t="s">
@@ -4212,7 +4191,7 @@
         <v>92</v>
       </c>
       <c r="J34" s="23"/>
-      <c r="K34" s="86">
+      <c r="K34" s="85">
         <v>10120044</v>
       </c>
     </row>
@@ -4220,10 +4199,10 @@
       <c r="A35" s="74">
         <v>30120025</v>
       </c>
-      <c r="B35" s="84">
+      <c r="B35" s="77">
         <v>101200</v>
       </c>
-      <c r="C35" s="84" t="s">
+      <c r="C35" s="77" t="s">
         <v>95</v>
       </c>
       <c r="D35" s="74">
@@ -4235,7 +4214,7 @@
       <c r="F35" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="G35" s="85">
+      <c r="G35" s="84">
         <v>2012001</v>
       </c>
       <c r="H35" s="23" t="s">
@@ -4245,7 +4224,7 @@
         <v>92</v>
       </c>
       <c r="J35" s="23"/>
-      <c r="K35" s="86">
+      <c r="K35" s="85">
         <v>10120045</v>
       </c>
     </row>
@@ -4253,10 +4232,10 @@
       <c r="A36" s="74">
         <v>30120026</v>
       </c>
-      <c r="B36" s="84">
+      <c r="B36" s="77">
         <v>101200</v>
       </c>
-      <c r="C36" s="84" t="s">
+      <c r="C36" s="77" t="s">
         <v>95</v>
       </c>
       <c r="D36" s="74">
@@ -4268,7 +4247,7 @@
       <c r="F36" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="G36" s="85">
+      <c r="G36" s="84">
         <v>2012001</v>
       </c>
       <c r="H36" s="23" t="s">
@@ -4278,547 +4257,547 @@
         <v>92</v>
       </c>
       <c r="J36" s="23"/>
-      <c r="K36" s="86">
+      <c r="K36" s="85">
         <v>10120046</v>
       </c>
     </row>
     <row r="37" s="6" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A37" s="87">
+      <c r="A37" s="86">
         <v>30240001</v>
       </c>
-      <c r="B37" s="88">
+      <c r="B37" s="87">
         <v>102400</v>
       </c>
-      <c r="C37" s="88" t="s">
+      <c r="C37" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="D37" s="87">
+      <c r="D37" s="86">
         <v>32401</v>
       </c>
-      <c r="E37" s="89" t="s">
+      <c r="E37" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="F37" s="89" t="s">
+      <c r="F37" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="G37" s="87"/>
-      <c r="H37" s="89"/>
-      <c r="I37" s="89" t="s">
+      <c r="G37" s="86"/>
+      <c r="H37" s="88"/>
+      <c r="I37" s="88" t="s">
         <v>37</v>
       </c>
-      <c r="J37" s="89"/>
-      <c r="K37" s="90"/>
-      <c r="L37" s="89" t="s">
+      <c r="J37" s="88"/>
+      <c r="K37" s="89"/>
+      <c r="L37" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="M37" s="89" t="s">
+      <c r="M37" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="N37" s="89" t="s">
+      <c r="N37" s="88" t="s">
         <v>40</v>
       </c>
-      <c r="O37" s="89"/>
-      <c r="P37" s="89"/>
-      <c r="Q37" s="91" t="s">
+      <c r="O37" s="88"/>
+      <c r="P37" s="88"/>
+      <c r="Q37" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="R37" s="92"/>
-      <c r="S37" s="92" t="s">
+      <c r="R37" s="91"/>
+      <c r="S37" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="T37" s="93" t="s">
+      <c r="T37" s="92" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="38" s="6" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A38" s="87">
+      <c r="A38" s="86">
         <v>30240002</v>
       </c>
-      <c r="B38" s="88">
+      <c r="B38" s="87">
         <v>102400</v>
       </c>
-      <c r="C38" s="88" t="s">
+      <c r="C38" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="D38" s="87">
+      <c r="D38" s="86">
         <v>32402</v>
       </c>
-      <c r="E38" s="89" t="s">
+      <c r="E38" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="F38" s="89" t="s">
+      <c r="F38" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="G38" s="87"/>
-      <c r="H38" s="89"/>
-      <c r="I38" s="89" t="s">
+      <c r="G38" s="86"/>
+      <c r="H38" s="88"/>
+      <c r="I38" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="J38" s="89"/>
-      <c r="K38" s="90"/>
-      <c r="L38" s="89" t="s">
+      <c r="J38" s="88"/>
+      <c r="K38" s="89"/>
+      <c r="L38" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="M38" s="89" t="s">
+      <c r="M38" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="N38" s="89" t="s">
+      <c r="N38" s="88" t="s">
         <v>40</v>
       </c>
-      <c r="O38" s="89"/>
-      <c r="P38" s="89"/>
-      <c r="Q38" s="91" t="s">
+      <c r="O38" s="88"/>
+      <c r="P38" s="88"/>
+      <c r="Q38" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="R38" s="92"/>
-      <c r="S38" s="92" t="s">
+      <c r="R38" s="91"/>
+      <c r="S38" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="T38" s="93"/>
+      <c r="T38" s="92"/>
     </row>
     <row r="39" s="6" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A39" s="87">
+      <c r="A39" s="86">
         <v>30240003</v>
       </c>
-      <c r="B39" s="88">
+      <c r="B39" s="87">
         <v>102400</v>
       </c>
-      <c r="C39" s="88" t="s">
+      <c r="C39" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="D39" s="87">
+      <c r="D39" s="86">
         <v>32403</v>
       </c>
-      <c r="E39" s="89" t="s">
+      <c r="E39" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="F39" s="89" t="s">
+      <c r="F39" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="G39" s="87"/>
-      <c r="H39" s="89"/>
-      <c r="I39" s="89" t="s">
+      <c r="G39" s="86"/>
+      <c r="H39" s="88"/>
+      <c r="I39" s="88" t="s">
         <v>49</v>
       </c>
-      <c r="J39" s="89"/>
-      <c r="K39" s="90"/>
-      <c r="L39" s="89" t="s">
+      <c r="J39" s="88"/>
+      <c r="K39" s="89"/>
+      <c r="L39" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="M39" s="89" t="s">
+      <c r="M39" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="N39" s="89" t="s">
+      <c r="N39" s="88" t="s">
         <v>40</v>
       </c>
-      <c r="O39" s="89"/>
-      <c r="P39" s="89"/>
-      <c r="Q39" s="91" t="s">
+      <c r="O39" s="88"/>
+      <c r="P39" s="88"/>
+      <c r="Q39" s="90" t="s">
         <v>50</v>
       </c>
-      <c r="R39" s="92"/>
-      <c r="S39" s="92" t="s">
+      <c r="R39" s="91"/>
+      <c r="S39" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="T39" s="93"/>
+      <c r="T39" s="92"/>
     </row>
     <row r="40" s="6" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A40" s="87">
+      <c r="A40" s="86">
         <v>30240004</v>
       </c>
-      <c r="B40" s="88">
+      <c r="B40" s="87">
         <v>102400</v>
       </c>
-      <c r="C40" s="88" t="s">
+      <c r="C40" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="D40" s="87">
+      <c r="D40" s="86">
         <v>32404</v>
       </c>
-      <c r="E40" s="89" t="s">
+      <c r="E40" s="88" t="s">
         <v>51</v>
       </c>
-      <c r="F40" s="89" t="s">
+      <c r="F40" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="G40" s="87"/>
-      <c r="H40" s="89"/>
-      <c r="I40" s="89" t="s">
+      <c r="G40" s="86"/>
+      <c r="H40" s="88"/>
+      <c r="I40" s="88" t="s">
         <v>52</v>
       </c>
-      <c r="J40" s="89"/>
-      <c r="K40" s="90"/>
-      <c r="L40" s="89" t="s">
+      <c r="J40" s="88"/>
+      <c r="K40" s="89"/>
+      <c r="L40" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="M40" s="89" t="s">
+      <c r="M40" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="N40" s="89" t="s">
+      <c r="N40" s="88" t="s">
         <v>40</v>
       </c>
-      <c r="O40" s="89"/>
-      <c r="P40" s="89"/>
-      <c r="Q40" s="91" t="s">
+      <c r="O40" s="88"/>
+      <c r="P40" s="88"/>
+      <c r="Q40" s="90" t="s">
         <v>53</v>
       </c>
-      <c r="R40" s="92"/>
-      <c r="S40" s="92" t="s">
+      <c r="R40" s="91"/>
+      <c r="S40" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="T40" s="93"/>
+      <c r="T40" s="92"/>
     </row>
     <row r="41" s="6" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A41" s="87">
+      <c r="A41" s="86">
         <v>30240005</v>
       </c>
-      <c r="B41" s="88">
+      <c r="B41" s="87">
         <v>102400</v>
       </c>
-      <c r="C41" s="88" t="s">
+      <c r="C41" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="87">
+      <c r="D41" s="86">
         <v>32411</v>
       </c>
-      <c r="E41" s="89" t="s">
+      <c r="E41" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="F41" s="89" t="s">
+      <c r="F41" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="G41" s="87"/>
-      <c r="H41" s="89"/>
-      <c r="I41" s="89" t="s">
+      <c r="G41" s="86"/>
+      <c r="H41" s="88"/>
+      <c r="I41" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="J41" s="89"/>
-      <c r="K41" s="90"/>
-      <c r="L41" s="89" t="s">
+      <c r="J41" s="88"/>
+      <c r="K41" s="89"/>
+      <c r="L41" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="M41" s="89" t="s">
+      <c r="M41" s="88" t="s">
         <v>56</v>
       </c>
-      <c r="N41" s="89"/>
-      <c r="O41" s="89" t="s">
+      <c r="N41" s="88"/>
+      <c r="O41" s="88" t="s">
         <v>57</v>
       </c>
-      <c r="P41" s="89"/>
-      <c r="Q41" s="91"/>
-      <c r="R41" s="91"/>
-      <c r="S41" s="91"/>
-      <c r="T41" s="93"/>
+      <c r="P41" s="88"/>
+      <c r="Q41" s="90"/>
+      <c r="R41" s="90"/>
+      <c r="S41" s="90"/>
+      <c r="T41" s="92"/>
     </row>
     <row r="42" s="6" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A42" s="87">
+      <c r="A42" s="86">
         <v>30240006</v>
       </c>
-      <c r="B42" s="88">
+      <c r="B42" s="87">
         <v>102400</v>
       </c>
-      <c r="C42" s="88" t="s">
+      <c r="C42" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="D42" s="87">
+      <c r="D42" s="86">
         <v>32421</v>
       </c>
-      <c r="E42" s="89" t="s">
+      <c r="E42" s="88" t="s">
         <v>58</v>
       </c>
-      <c r="F42" s="89" t="s">
+      <c r="F42" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="G42" s="87"/>
-      <c r="H42" s="89"/>
-      <c r="I42" s="89" t="s">
+      <c r="G42" s="86"/>
+      <c r="H42" s="88"/>
+      <c r="I42" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="J42" s="89"/>
-      <c r="K42" s="90"/>
-      <c r="L42" s="89" t="s">
+      <c r="J42" s="88"/>
+      <c r="K42" s="89"/>
+      <c r="L42" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="M42" s="89" t="s">
+      <c r="M42" s="88" t="s">
         <v>60</v>
       </c>
-      <c r="N42" s="89" t="s">
+      <c r="N42" s="88" t="s">
         <v>40</v>
       </c>
-      <c r="O42" s="89" t="s">
+      <c r="O42" s="88" t="s">
         <v>57</v>
       </c>
-      <c r="P42" s="89"/>
-      <c r="Q42" s="89"/>
-      <c r="R42" s="89"/>
-      <c r="S42" s="89"/>
-      <c r="T42" s="93"/>
+      <c r="P42" s="88"/>
+      <c r="Q42" s="88"/>
+      <c r="R42" s="88"/>
+      <c r="S42" s="88"/>
+      <c r="T42" s="92"/>
     </row>
     <row r="43" s="6" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A43" s="87">
+      <c r="A43" s="86">
         <v>30240007</v>
       </c>
-      <c r="B43" s="88">
+      <c r="B43" s="87">
         <v>102400</v>
       </c>
-      <c r="C43" s="88" t="s">
+      <c r="C43" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="D43" s="87">
+      <c r="D43" s="86">
         <v>32431</v>
       </c>
-      <c r="E43" s="89" t="s">
+      <c r="E43" s="88" t="s">
         <v>61</v>
       </c>
-      <c r="F43" s="89" t="s">
+      <c r="F43" s="88" t="s">
         <v>62</v>
       </c>
-      <c r="G43" s="87">
+      <c r="G43" s="86">
         <v>2024001</v>
       </c>
-      <c r="H43" s="89" t="s">
-        <v>63</v>
-      </c>
-      <c r="I43" s="89" t="s">
+      <c r="H43" s="88" t="s">
+        <v>63</v>
+      </c>
+      <c r="I43" s="88" t="s">
         <v>64</v>
       </c>
-      <c r="J43" s="89"/>
-      <c r="K43" s="90">
+      <c r="J43" s="88"/>
+      <c r="K43" s="89">
         <v>10240091</v>
       </c>
-      <c r="L43" s="89"/>
-      <c r="M43" s="89"/>
-      <c r="N43" s="89"/>
-      <c r="O43" s="89"/>
-      <c r="P43" s="89"/>
-      <c r="Q43" s="89"/>
-      <c r="R43" s="89"/>
-      <c r="S43" s="89"/>
-      <c r="T43" s="93"/>
+      <c r="L43" s="88"/>
+      <c r="M43" s="88"/>
+      <c r="N43" s="88"/>
+      <c r="O43" s="88"/>
+      <c r="P43" s="88"/>
+      <c r="Q43" s="88"/>
+      <c r="R43" s="88"/>
+      <c r="S43" s="88"/>
+      <c r="T43" s="92"/>
     </row>
     <row r="44" s="6" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A44" s="87">
+      <c r="A44" s="86">
         <v>30240008</v>
       </c>
-      <c r="B44" s="88">
+      <c r="B44" s="87">
         <v>102400</v>
       </c>
-      <c r="C44" s="88" t="s">
+      <c r="C44" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="D44" s="87">
+      <c r="D44" s="86">
         <v>32432</v>
       </c>
-      <c r="E44" s="89" t="s">
+      <c r="E44" s="88" t="s">
         <v>65</v>
       </c>
-      <c r="F44" s="89" t="s">
+      <c r="F44" s="88" t="s">
         <v>56</v>
       </c>
-      <c r="G44" s="87">
+      <c r="G44" s="86">
         <v>2024001</v>
       </c>
-      <c r="H44" s="89" t="s">
-        <v>63</v>
-      </c>
-      <c r="I44" s="89" t="s">
+      <c r="H44" s="88" t="s">
+        <v>63</v>
+      </c>
+      <c r="I44" s="88" t="s">
         <v>66</v>
       </c>
-      <c r="J44" s="89"/>
-      <c r="K44" s="94" t="s">
+      <c r="J44" s="88"/>
+      <c r="K44" s="93" t="s">
         <v>96</v>
       </c>
-      <c r="L44" s="89"/>
-      <c r="M44" s="89"/>
-      <c r="N44" s="89"/>
-      <c r="O44" s="89"/>
-      <c r="P44" s="89"/>
-      <c r="Q44" s="89"/>
-      <c r="R44" s="89"/>
-      <c r="S44" s="89"/>
-      <c r="T44" s="93"/>
+      <c r="L44" s="88"/>
+      <c r="M44" s="88"/>
+      <c r="N44" s="88"/>
+      <c r="O44" s="88"/>
+      <c r="P44" s="88"/>
+      <c r="Q44" s="88"/>
+      <c r="R44" s="88"/>
+      <c r="S44" s="88"/>
+      <c r="T44" s="92"/>
     </row>
     <row r="45" s="6" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A45" s="87">
+      <c r="A45" s="86">
         <v>30240009</v>
       </c>
-      <c r="B45" s="88">
+      <c r="B45" s="87">
         <v>102400</v>
       </c>
-      <c r="C45" s="88" t="s">
+      <c r="C45" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="D45" s="87">
+      <c r="D45" s="86">
         <v>32433</v>
       </c>
-      <c r="E45" s="89" t="s">
+      <c r="E45" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="F45" s="89" t="s">
+      <c r="F45" s="88" t="s">
         <v>56</v>
       </c>
-      <c r="G45" s="87">
+      <c r="G45" s="86">
         <v>2024001</v>
       </c>
-      <c r="H45" s="89" t="s">
-        <v>63</v>
-      </c>
-      <c r="I45" s="89" t="s">
+      <c r="H45" s="88" t="s">
+        <v>63</v>
+      </c>
+      <c r="I45" s="88" t="s">
         <v>69</v>
       </c>
-      <c r="J45" s="89"/>
-      <c r="K45" s="90" t="s">
+      <c r="J45" s="88"/>
+      <c r="K45" s="89" t="s">
         <v>97</v>
       </c>
-      <c r="L45" s="89"/>
-      <c r="M45" s="89"/>
-      <c r="N45" s="89"/>
-      <c r="O45" s="89"/>
-      <c r="P45" s="89"/>
-      <c r="Q45" s="89"/>
-      <c r="R45" s="89"/>
-      <c r="S45" s="89"/>
-      <c r="T45" s="93"/>
+      <c r="L45" s="88"/>
+      <c r="M45" s="88"/>
+      <c r="N45" s="88"/>
+      <c r="O45" s="88"/>
+      <c r="P45" s="88"/>
+      <c r="Q45" s="88"/>
+      <c r="R45" s="88"/>
+      <c r="S45" s="88"/>
+      <c r="T45" s="92"/>
     </row>
     <row r="46" s="6" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A46" s="87">
+      <c r="A46" s="86">
         <v>30240010</v>
       </c>
-      <c r="B46" s="88">
+      <c r="B46" s="87">
         <v>102400</v>
       </c>
-      <c r="C46" s="88" t="s">
+      <c r="C46" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="D46" s="87">
+      <c r="D46" s="86">
         <v>32441</v>
       </c>
-      <c r="E46" s="89" t="s">
+      <c r="E46" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="F46" s="89" t="s">
+      <c r="F46" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="G46" s="87"/>
-      <c r="H46" s="89"/>
-      <c r="I46" s="89" t="s">
+      <c r="G46" s="86"/>
+      <c r="H46" s="88"/>
+      <c r="I46" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="J46" s="89"/>
-      <c r="K46" s="94"/>
-      <c r="L46" s="89" t="s">
+      <c r="J46" s="88"/>
+      <c r="K46" s="93"/>
+      <c r="L46" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="M46" s="89" t="s">
+      <c r="M46" s="88" t="s">
         <v>73</v>
       </c>
-      <c r="N46" s="89"/>
-      <c r="O46" s="89"/>
-      <c r="P46" s="89"/>
-      <c r="Q46" s="91" t="s">
+      <c r="N46" s="88"/>
+      <c r="O46" s="88"/>
+      <c r="P46" s="88"/>
+      <c r="Q46" s="90" t="s">
         <v>74</v>
       </c>
-      <c r="R46" s="95"/>
-      <c r="S46" s="95" t="s">
+      <c r="R46" s="94"/>
+      <c r="S46" s="94" t="s">
         <v>75</v>
       </c>
-      <c r="T46" s="91" t="s">
+      <c r="T46" s="90" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="47" s="6" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A47" s="87">
+      <c r="A47" s="86">
         <v>30240011</v>
       </c>
-      <c r="B47" s="88">
+      <c r="B47" s="87">
         <v>102400</v>
       </c>
-      <c r="C47" s="88" t="s">
+      <c r="C47" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="D47" s="87">
+      <c r="D47" s="86">
         <v>32442</v>
       </c>
-      <c r="E47" s="89" t="s">
+      <c r="E47" s="88" t="s">
         <v>77</v>
       </c>
-      <c r="F47" s="89" t="s">
+      <c r="F47" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="G47" s="87"/>
-      <c r="H47" s="89"/>
-      <c r="I47" s="89" t="s">
+      <c r="G47" s="86"/>
+      <c r="H47" s="88"/>
+      <c r="I47" s="88" t="s">
         <v>78</v>
       </c>
-      <c r="J47" s="89"/>
-      <c r="K47" s="90"/>
-      <c r="L47" s="89" t="s">
+      <c r="J47" s="88"/>
+      <c r="K47" s="89"/>
+      <c r="L47" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="M47" s="89" t="s">
+      <c r="M47" s="88" t="s">
         <v>60</v>
       </c>
-      <c r="N47" s="89"/>
-      <c r="O47" s="89"/>
-      <c r="P47" s="89"/>
-      <c r="Q47" s="89"/>
-      <c r="R47" s="89"/>
-      <c r="S47" s="89"/>
-      <c r="T47" s="93"/>
+      <c r="N47" s="88"/>
+      <c r="O47" s="88"/>
+      <c r="P47" s="88"/>
+      <c r="Q47" s="88"/>
+      <c r="R47" s="88"/>
+      <c r="S47" s="88"/>
+      <c r="T47" s="92"/>
     </row>
     <row r="48" s="6" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A48" s="87">
+      <c r="A48" s="86">
         <v>30240012</v>
       </c>
-      <c r="B48" s="88">
+      <c r="B48" s="87">
         <v>102400</v>
       </c>
-      <c r="C48" s="88" t="s">
+      <c r="C48" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="D48" s="87">
+      <c r="D48" s="86">
         <v>32443</v>
       </c>
-      <c r="E48" s="89" t="s">
+      <c r="E48" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="F48" s="89" t="s">
+      <c r="F48" s="88" t="s">
         <v>56</v>
       </c>
-      <c r="G48" s="87">
+      <c r="G48" s="86">
         <v>2024001</v>
       </c>
-      <c r="H48" s="89" t="s">
-        <v>63</v>
-      </c>
-      <c r="I48" s="89" t="s">
+      <c r="H48" s="88" t="s">
+        <v>63</v>
+      </c>
+      <c r="I48" s="88" t="s">
         <v>69</v>
       </c>
-      <c r="J48" s="89"/>
-      <c r="K48" s="90" t="s">
+      <c r="J48" s="88"/>
+      <c r="K48" s="89" t="s">
         <v>97</v>
       </c>
-      <c r="L48" s="89"/>
-      <c r="M48" s="89"/>
-      <c r="N48" s="89"/>
-      <c r="O48" s="89"/>
-      <c r="P48" s="89"/>
-      <c r="Q48" s="89"/>
-      <c r="R48" s="89"/>
-      <c r="S48" s="89"/>
-      <c r="T48" s="93"/>
+      <c r="L48" s="88"/>
+      <c r="M48" s="88"/>
+      <c r="N48" s="88"/>
+      <c r="O48" s="88"/>
+      <c r="P48" s="88"/>
+      <c r="Q48" s="88"/>
+      <c r="R48" s="88"/>
+      <c r="S48" s="88"/>
+      <c r="T48" s="92"/>
     </row>
     <row r="49" s="7" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A49" s="96">
+      <c r="A49" s="95">
         <v>30170001</v>
       </c>
-      <c r="B49" s="97">
+      <c r="B49" s="96">
         <v>101700</v>
       </c>
-      <c r="C49" s="97" t="s">
+      <c r="C49" s="96" t="s">
         <v>98</v>
       </c>
-      <c r="D49" s="96">
+      <c r="D49" s="95">
         <v>301701</v>
       </c>
       <c r="E49" s="31" t="s">
@@ -4827,7 +4806,7 @@
       <c r="F49" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="G49" s="96">
+      <c r="G49" s="95">
         <v>2017001</v>
       </c>
       <c r="H49" s="31" t="s">
@@ -4837,7 +4816,7 @@
         <v>83</v>
       </c>
       <c r="J49" s="31"/>
-      <c r="K49" s="98" t="s">
+      <c r="K49" s="97" t="s">
         <v>100</v>
       </c>
       <c r="L49" s="31"/>
@@ -4848,19 +4827,19 @@
       <c r="Q49" s="31"/>
       <c r="R49" s="31"/>
       <c r="S49" s="31"/>
-      <c r="T49" s="99"/>
+      <c r="T49" s="98"/>
     </row>
     <row r="50" s="7" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A50" s="96">
+      <c r="A50" s="95">
         <v>30170002</v>
       </c>
-      <c r="B50" s="97">
+      <c r="B50" s="96">
         <v>101700</v>
       </c>
-      <c r="C50" s="97" t="s">
+      <c r="C50" s="96" t="s">
         <v>98</v>
       </c>
-      <c r="D50" s="96">
+      <c r="D50" s="95">
         <v>301702</v>
       </c>
       <c r="E50" s="31" t="s">
@@ -4869,7 +4848,7 @@
       <c r="F50" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="G50" s="96">
+      <c r="G50" s="95">
         <v>2017001</v>
       </c>
       <c r="H50" s="31" t="s">
@@ -4879,7 +4858,7 @@
         <v>83</v>
       </c>
       <c r="J50" s="31"/>
-      <c r="K50" s="98" t="s">
+      <c r="K50" s="97" t="s">
         <v>100</v>
       </c>
       <c r="L50" s="31"/>
@@ -4890,7 +4869,7 @@
       <c r="Q50" s="31"/>
       <c r="R50" s="31"/>
       <c r="S50" s="31"/>
-      <c r="T50" s="99"/>
+      <c r="T50" s="98"/>
     </row>
     <row r="51" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A51" s="80">
@@ -4919,7 +4898,7 @@
       </c>
       <c r="I51" s="20"/>
       <c r="J51" s="20"/>
-      <c r="K51" s="100" t="s">
+      <c r="K51" s="99" t="s">
         <v>105</v>
       </c>
       <c r="L51" s="20" t="s">
@@ -4932,7 +4911,7 @@
       <c r="Q51" s="20"/>
       <c r="R51" s="20"/>
       <c r="S51" s="20"/>
-      <c r="T51" s="101"/>
+      <c r="T51" s="100"/>
     </row>
     <row r="52" s="4" customFormat="1" ht="16.5" spans="1:20">
       <c r="A52" s="80">
@@ -4961,7 +4940,7 @@
       </c>
       <c r="I52" s="20"/>
       <c r="J52" s="20"/>
-      <c r="K52" s="100" t="s">
+      <c r="K52" s="99" t="s">
         <v>108</v>
       </c>
       <c r="L52" s="20" t="s">
@@ -4974,1097 +4953,1097 @@
       <c r="Q52" s="20"/>
       <c r="R52" s="20"/>
       <c r="S52" s="20"/>
-      <c r="T52" s="101"/>
+      <c r="T52" s="100"/>
     </row>
     <row r="53" s="8" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A53" s="102">
+      <c r="A53" s="101">
         <v>30210001</v>
       </c>
-      <c r="B53" s="103">
+      <c r="B53" s="102">
         <v>102100</v>
       </c>
-      <c r="C53" s="103" t="s">
+      <c r="C53" s="102" t="s">
         <v>109</v>
       </c>
-      <c r="D53" s="102">
+      <c r="D53" s="101">
         <v>302101</v>
       </c>
-      <c r="E53" s="104" t="s">
+      <c r="E53" s="103" t="s">
         <v>110</v>
       </c>
-      <c r="F53" s="104" t="s">
+      <c r="F53" s="103" t="s">
         <v>111</v>
       </c>
-      <c r="G53" s="102">
+      <c r="G53" s="101">
         <v>2021001</v>
       </c>
-      <c r="H53" s="104" t="s">
-        <v>63</v>
-      </c>
-      <c r="I53" s="104" t="s">
+      <c r="H53" s="103" t="s">
+        <v>63</v>
+      </c>
+      <c r="I53" s="103" t="s">
         <v>83</v>
       </c>
-      <c r="J53" s="104"/>
-      <c r="K53" s="105" t="s">
+      <c r="J53" s="103"/>
+      <c r="K53" s="104" t="s">
         <v>112</v>
       </c>
-      <c r="L53" s="104" t="s">
+      <c r="L53" s="103" t="s">
         <v>113</v>
       </c>
-      <c r="M53" s="104"/>
-      <c r="N53" s="104"/>
-      <c r="O53" s="104"/>
-      <c r="P53" s="104"/>
-      <c r="Q53" s="104"/>
-      <c r="R53" s="104"/>
-      <c r="S53" s="104"/>
-      <c r="T53" s="106"/>
+      <c r="M53" s="103"/>
+      <c r="N53" s="103"/>
+      <c r="O53" s="103"/>
+      <c r="P53" s="103"/>
+      <c r="Q53" s="103"/>
+      <c r="R53" s="103"/>
+      <c r="S53" s="103"/>
+      <c r="T53" s="105"/>
     </row>
     <row r="54" s="8" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A54" s="102">
+      <c r="A54" s="101">
         <v>30210002</v>
       </c>
-      <c r="B54" s="103">
+      <c r="B54" s="102">
         <v>102100</v>
       </c>
-      <c r="C54" s="103" t="s">
+      <c r="C54" s="102" t="s">
         <v>109</v>
       </c>
-      <c r="D54" s="102">
+      <c r="D54" s="101">
         <v>302102</v>
       </c>
-      <c r="E54" s="104" t="s">
+      <c r="E54" s="103" t="s">
         <v>114</v>
       </c>
-      <c r="F54" s="104" t="s">
+      <c r="F54" s="103" t="s">
         <v>36</v>
       </c>
-      <c r="G54" s="102"/>
-      <c r="H54" s="104"/>
-      <c r="I54" s="104" t="s">
+      <c r="G54" s="101"/>
+      <c r="H54" s="103"/>
+      <c r="I54" s="103" t="s">
         <v>115</v>
       </c>
-      <c r="J54" s="104"/>
-      <c r="K54" s="105"/>
-      <c r="L54" s="104"/>
-      <c r="M54" s="104" t="s">
+      <c r="J54" s="103"/>
+      <c r="K54" s="104"/>
+      <c r="L54" s="103"/>
+      <c r="M54" s="103" t="s">
         <v>39</v>
       </c>
-      <c r="N54" s="104" t="s">
+      <c r="N54" s="103" t="s">
         <v>116</v>
       </c>
-      <c r="O54" s="104"/>
-      <c r="P54" s="104"/>
-      <c r="Q54" s="104" t="s">
+      <c r="O54" s="103"/>
+      <c r="P54" s="103"/>
+      <c r="Q54" s="103" t="s">
         <v>117</v>
       </c>
-      <c r="R54" s="104"/>
-      <c r="S54" s="104"/>
-      <c r="T54" s="106"/>
+      <c r="R54" s="103"/>
+      <c r="S54" s="103"/>
+      <c r="T54" s="105"/>
     </row>
     <row r="55" s="9" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A55" s="107">
+      <c r="A55" s="106">
         <v>30180001</v>
       </c>
-      <c r="B55" s="108">
+      <c r="B55" s="107">
         <v>101800</v>
       </c>
-      <c r="C55" s="108" t="s">
+      <c r="C55" s="107" t="s">
         <v>118</v>
       </c>
-      <c r="D55" s="107">
+      <c r="D55" s="106">
         <v>301801</v>
       </c>
-      <c r="E55" s="109" t="s">
+      <c r="E55" s="108" t="s">
         <v>83</v>
       </c>
-      <c r="F55" s="109" t="s">
+      <c r="F55" s="108" t="s">
         <v>119</v>
       </c>
-      <c r="G55" s="107">
+      <c r="G55" s="106">
         <v>2018002</v>
       </c>
-      <c r="H55" s="109" t="s">
-        <v>63</v>
-      </c>
-      <c r="I55" s="109" t="s">
+      <c r="H55" s="108" t="s">
+        <v>63</v>
+      </c>
+      <c r="I55" s="108" t="s">
         <v>83</v>
       </c>
-      <c r="J55" s="109"/>
-      <c r="K55" s="110">
+      <c r="J55" s="108"/>
+      <c r="K55" s="109">
         <v>10180041</v>
       </c>
-      <c r="L55" s="109"/>
-      <c r="M55" s="109"/>
-      <c r="N55" s="109"/>
-      <c r="O55" s="109"/>
-      <c r="P55" s="109"/>
-      <c r="Q55" s="109"/>
-      <c r="R55" s="109"/>
-      <c r="S55" s="109"/>
-      <c r="T55" s="111"/>
+      <c r="L55" s="108"/>
+      <c r="M55" s="108"/>
+      <c r="N55" s="108"/>
+      <c r="O55" s="108"/>
+      <c r="P55" s="108"/>
+      <c r="Q55" s="108"/>
+      <c r="R55" s="108"/>
+      <c r="S55" s="108"/>
+      <c r="T55" s="110"/>
     </row>
     <row r="56" s="10" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A56" s="112">
+      <c r="A56" s="111">
         <v>30250001</v>
       </c>
-      <c r="B56" s="113">
+      <c r="B56" s="112">
         <v>102500</v>
       </c>
-      <c r="C56" s="113" t="s">
+      <c r="C56" s="112" t="s">
         <v>120</v>
       </c>
-      <c r="D56" s="112">
+      <c r="D56" s="111">
         <v>302501</v>
       </c>
-      <c r="E56" s="114" t="s">
+      <c r="E56" s="113" t="s">
         <v>110</v>
       </c>
-      <c r="F56" s="114" t="s">
+      <c r="F56" s="113" t="s">
         <v>111</v>
       </c>
-      <c r="G56" s="112">
+      <c r="G56" s="111">
         <v>2025001</v>
       </c>
-      <c r="H56" s="114" t="s">
-        <v>63</v>
-      </c>
-      <c r="I56" s="114" t="s">
+      <c r="H56" s="113" t="s">
+        <v>63</v>
+      </c>
+      <c r="I56" s="113" t="s">
         <v>83</v>
       </c>
-      <c r="J56" s="114"/>
-      <c r="K56" s="115" t="s">
+      <c r="J56" s="113"/>
+      <c r="K56" s="114" t="s">
         <v>121</v>
       </c>
-      <c r="L56" s="114" t="s">
+      <c r="L56" s="113" t="s">
         <v>122</v>
       </c>
-      <c r="M56" s="114"/>
-      <c r="N56" s="114"/>
-      <c r="O56" s="114"/>
-      <c r="P56" s="114"/>
-      <c r="Q56" s="114"/>
-      <c r="R56" s="114"/>
-      <c r="S56" s="114"/>
-      <c r="T56" s="116"/>
+      <c r="M56" s="113"/>
+      <c r="N56" s="113"/>
+      <c r="O56" s="113"/>
+      <c r="P56" s="113"/>
+      <c r="Q56" s="113"/>
+      <c r="R56" s="113"/>
+      <c r="S56" s="113"/>
+      <c r="T56" s="115"/>
     </row>
     <row r="57" s="10" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A57" s="112">
+      <c r="A57" s="111">
         <v>30250002</v>
       </c>
-      <c r="B57" s="113">
+      <c r="B57" s="112">
         <v>102500</v>
       </c>
-      <c r="C57" s="113" t="s">
+      <c r="C57" s="112" t="s">
         <v>120</v>
       </c>
-      <c r="D57" s="112">
+      <c r="D57" s="111">
         <v>302502</v>
       </c>
-      <c r="E57" s="114" t="s">
+      <c r="E57" s="113" t="s">
         <v>123</v>
       </c>
-      <c r="F57" s="114" t="s">
+      <c r="F57" s="113" t="s">
         <v>124</v>
       </c>
-      <c r="G57" s="112">
+      <c r="G57" s="111">
         <v>2025001</v>
       </c>
-      <c r="H57" s="114" t="s">
-        <v>63</v>
-      </c>
-      <c r="I57" s="114" t="s">
+      <c r="H57" s="113" t="s">
+        <v>63</v>
+      </c>
+      <c r="I57" s="113" t="s">
         <v>83</v>
       </c>
-      <c r="J57" s="114"/>
-      <c r="K57" s="115" t="s">
+      <c r="J57" s="113"/>
+      <c r="K57" s="114" t="s">
         <v>121</v>
       </c>
-      <c r="L57" s="114" t="s">
+      <c r="L57" s="113" t="s">
         <v>122</v>
       </c>
-      <c r="M57" s="114"/>
-      <c r="N57" s="114"/>
-      <c r="O57" s="114"/>
-      <c r="P57" s="114"/>
-      <c r="Q57" s="114"/>
-      <c r="R57" s="114"/>
-      <c r="S57" s="114"/>
-      <c r="T57" s="116"/>
+      <c r="M57" s="113"/>
+      <c r="N57" s="113"/>
+      <c r="O57" s="113"/>
+      <c r="P57" s="113"/>
+      <c r="Q57" s="113"/>
+      <c r="R57" s="113"/>
+      <c r="S57" s="113"/>
+      <c r="T57" s="115"/>
     </row>
     <row r="58" s="10" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A58" s="112">
+      <c r="A58" s="111">
         <v>30250003</v>
       </c>
-      <c r="B58" s="113">
+      <c r="B58" s="112">
         <v>102500</v>
       </c>
-      <c r="C58" s="113" t="s">
+      <c r="C58" s="112" t="s">
         <v>120</v>
       </c>
-      <c r="D58" s="112">
+      <c r="D58" s="111">
         <v>302503</v>
       </c>
-      <c r="E58" s="114" t="s">
+      <c r="E58" s="113" t="s">
         <v>125</v>
       </c>
-      <c r="F58" s="114" t="s">
+      <c r="F58" s="113" t="s">
         <v>126</v>
       </c>
-      <c r="G58" s="112">
+      <c r="G58" s="111">
         <v>2025001</v>
       </c>
-      <c r="H58" s="114" t="s">
-        <v>63</v>
-      </c>
-      <c r="I58" s="114" t="s">
+      <c r="H58" s="113" t="s">
+        <v>63</v>
+      </c>
+      <c r="I58" s="113" t="s">
         <v>83</v>
       </c>
-      <c r="J58" s="114"/>
-      <c r="K58" s="115" t="s">
+      <c r="J58" s="113"/>
+      <c r="K58" s="114" t="s">
         <v>121</v>
       </c>
-      <c r="L58" s="114" t="s">
+      <c r="L58" s="113" t="s">
         <v>122</v>
       </c>
-      <c r="M58" s="114"/>
-      <c r="N58" s="114"/>
-      <c r="O58" s="114"/>
-      <c r="P58" s="114"/>
-      <c r="Q58" s="114"/>
-      <c r="R58" s="114"/>
-      <c r="S58" s="114"/>
-      <c r="T58" s="116"/>
+      <c r="M58" s="113"/>
+      <c r="N58" s="113"/>
+      <c r="O58" s="113"/>
+      <c r="P58" s="113"/>
+      <c r="Q58" s="113"/>
+      <c r="R58" s="113"/>
+      <c r="S58" s="113"/>
+      <c r="T58" s="115"/>
     </row>
     <row r="59" s="11" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A59" s="117">
+      <c r="A59" s="116">
         <v>30230001</v>
       </c>
-      <c r="B59" s="118">
+      <c r="B59" s="117">
         <v>102300</v>
       </c>
-      <c r="C59" s="118" t="s">
+      <c r="C59" s="117" t="s">
         <v>127</v>
       </c>
-      <c r="D59" s="117">
+      <c r="D59" s="116">
         <v>302301</v>
       </c>
-      <c r="E59" s="119" t="s">
+      <c r="E59" s="118" t="s">
         <v>110</v>
       </c>
-      <c r="F59" s="119" t="s">
+      <c r="F59" s="118" t="s">
         <v>111</v>
       </c>
-      <c r="G59" s="117">
+      <c r="G59" s="116">
         <v>2023001</v>
       </c>
-      <c r="H59" s="119" t="s">
-        <v>63</v>
-      </c>
-      <c r="I59" s="119" t="s">
+      <c r="H59" s="118" t="s">
+        <v>63</v>
+      </c>
+      <c r="I59" s="118" t="s">
         <v>83</v>
       </c>
-      <c r="J59" s="119"/>
-      <c r="K59" s="120" t="s">
+      <c r="J59" s="118"/>
+      <c r="K59" s="119" t="s">
         <v>128</v>
       </c>
-      <c r="L59" s="119" t="s">
+      <c r="L59" s="118" t="s">
         <v>129</v>
       </c>
-      <c r="M59" s="119"/>
-      <c r="N59" s="119"/>
-      <c r="O59" s="119"/>
-      <c r="P59" s="119"/>
-      <c r="Q59" s="119"/>
-      <c r="R59" s="119"/>
-      <c r="S59" s="119"/>
-      <c r="T59" s="121"/>
+      <c r="M59" s="118"/>
+      <c r="N59" s="118"/>
+      <c r="O59" s="118"/>
+      <c r="P59" s="118"/>
+      <c r="Q59" s="118"/>
+      <c r="R59" s="118"/>
+      <c r="S59" s="118"/>
+      <c r="T59" s="120"/>
     </row>
     <row r="60" s="11" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A60" s="117">
+      <c r="A60" s="116">
         <v>30230002</v>
       </c>
-      <c r="B60" s="118">
+      <c r="B60" s="117">
         <v>102300</v>
       </c>
-      <c r="C60" s="118" t="s">
+      <c r="C60" s="117" t="s">
         <v>127</v>
       </c>
-      <c r="D60" s="117">
+      <c r="D60" s="116">
         <v>302302</v>
       </c>
-      <c r="E60" s="119" t="s">
+      <c r="E60" s="118" t="s">
         <v>130</v>
       </c>
-      <c r="F60" s="119" t="s">
+      <c r="F60" s="118" t="s">
         <v>82</v>
       </c>
-      <c r="G60" s="117">
+      <c r="G60" s="116">
         <v>2023001</v>
       </c>
-      <c r="H60" s="119" t="s">
-        <v>63</v>
-      </c>
-      <c r="I60" s="119" t="s">
+      <c r="H60" s="118" t="s">
+        <v>63</v>
+      </c>
+      <c r="I60" s="118" t="s">
         <v>83</v>
       </c>
-      <c r="J60" s="119"/>
-      <c r="K60" s="120" t="s">
+      <c r="J60" s="118"/>
+      <c r="K60" s="119" t="s">
         <v>128</v>
       </c>
-      <c r="L60" s="119" t="s">
+      <c r="L60" s="118" t="s">
         <v>129</v>
       </c>
-      <c r="M60" s="119"/>
-      <c r="N60" s="119"/>
-      <c r="O60" s="119"/>
-      <c r="P60" s="119"/>
-      <c r="Q60" s="119"/>
-      <c r="R60" s="119"/>
-      <c r="S60" s="119"/>
-      <c r="T60" s="121"/>
+      <c r="M60" s="118"/>
+      <c r="N60" s="118"/>
+      <c r="O60" s="118"/>
+      <c r="P60" s="118"/>
+      <c r="Q60" s="118"/>
+      <c r="R60" s="118"/>
+      <c r="S60" s="118"/>
+      <c r="T60" s="120"/>
     </row>
     <row r="61" s="11" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A61" s="117">
+      <c r="A61" s="116">
         <v>30230003</v>
       </c>
-      <c r="B61" s="118">
+      <c r="B61" s="117">
         <v>102300</v>
       </c>
-      <c r="C61" s="118" t="s">
+      <c r="C61" s="117" t="s">
         <v>127</v>
       </c>
-      <c r="D61" s="117">
+      <c r="D61" s="116">
         <v>302303</v>
       </c>
-      <c r="E61" s="119" t="s">
+      <c r="E61" s="118" t="s">
         <v>131</v>
       </c>
-      <c r="F61" s="119" t="s">
+      <c r="F61" s="118" t="s">
         <v>86</v>
       </c>
-      <c r="G61" s="117">
+      <c r="G61" s="116">
         <v>2023001</v>
       </c>
-      <c r="H61" s="119" t="s">
-        <v>63</v>
-      </c>
-      <c r="I61" s="119" t="s">
+      <c r="H61" s="118" t="s">
+        <v>63</v>
+      </c>
+      <c r="I61" s="118" t="s">
         <v>83</v>
       </c>
-      <c r="J61" s="119"/>
-      <c r="K61" s="120" t="s">
+      <c r="J61" s="118"/>
+      <c r="K61" s="119" t="s">
         <v>128</v>
       </c>
-      <c r="L61" s="119" t="s">
+      <c r="L61" s="118" t="s">
         <v>129</v>
       </c>
-      <c r="M61" s="119"/>
-      <c r="N61" s="119"/>
-      <c r="O61" s="119"/>
-      <c r="P61" s="119"/>
-      <c r="Q61" s="119"/>
-      <c r="R61" s="119"/>
-      <c r="S61" s="119"/>
-      <c r="T61" s="121"/>
+      <c r="M61" s="118"/>
+      <c r="N61" s="118"/>
+      <c r="O61" s="118"/>
+      <c r="P61" s="118"/>
+      <c r="Q61" s="118"/>
+      <c r="R61" s="118"/>
+      <c r="S61" s="118"/>
+      <c r="T61" s="120"/>
     </row>
     <row r="62" s="12" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A62" s="122">
+      <c r="A62" s="121">
         <v>30350001</v>
       </c>
-      <c r="B62" s="123">
+      <c r="B62" s="122">
         <v>103500</v>
       </c>
-      <c r="C62" s="123" t="s">
+      <c r="C62" s="122" t="s">
         <v>132</v>
       </c>
-      <c r="D62" s="122">
+      <c r="D62" s="121">
         <v>303501</v>
       </c>
-      <c r="E62" s="124" t="s">
+      <c r="E62" s="123" t="s">
         <v>133</v>
       </c>
-      <c r="F62" s="124" t="s">
+      <c r="F62" s="123" t="s">
         <v>62</v>
       </c>
-      <c r="G62" s="122">
+      <c r="G62" s="121">
         <v>2035002</v>
       </c>
-      <c r="H62" s="124" t="s">
-        <v>63</v>
-      </c>
-      <c r="I62" s="124" t="s">
+      <c r="H62" s="123" t="s">
+        <v>63</v>
+      </c>
+      <c r="I62" s="123" t="s">
         <v>134</v>
       </c>
-      <c r="J62" s="124"/>
-      <c r="K62" s="125" t="s">
+      <c r="J62" s="123"/>
+      <c r="K62" s="124" t="s">
         <v>135</v>
       </c>
-      <c r="L62" s="124" t="s">
+      <c r="L62" s="123" t="s">
         <v>136</v>
       </c>
-      <c r="M62" s="124"/>
-      <c r="N62" s="124"/>
-      <c r="O62" s="124"/>
-      <c r="P62" s="124"/>
-      <c r="Q62" s="124"/>
-      <c r="R62" s="124"/>
-      <c r="S62" s="124"/>
-      <c r="T62" s="126"/>
+      <c r="M62" s="123"/>
+      <c r="N62" s="123"/>
+      <c r="O62" s="123"/>
+      <c r="P62" s="123"/>
+      <c r="Q62" s="123"/>
+      <c r="R62" s="123"/>
+      <c r="S62" s="123"/>
+      <c r="T62" s="125"/>
     </row>
     <row r="63" s="12" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A63" s="122">
+      <c r="A63" s="121">
         <v>30350002</v>
       </c>
-      <c r="B63" s="123">
+      <c r="B63" s="122">
         <v>103500</v>
       </c>
-      <c r="C63" s="123" t="s">
+      <c r="C63" s="122" t="s">
         <v>132</v>
       </c>
-      <c r="D63" s="122">
+      <c r="D63" s="121">
         <v>303502</v>
       </c>
-      <c r="E63" s="124" t="s">
+      <c r="E63" s="123" t="s">
         <v>137</v>
       </c>
-      <c r="F63" s="124" t="s">
+      <c r="F63" s="123" t="s">
         <v>36</v>
       </c>
-      <c r="G63" s="122"/>
-      <c r="H63" s="124"/>
-      <c r="I63" s="124"/>
-      <c r="J63" s="124"/>
-      <c r="K63" s="125"/>
-      <c r="L63" s="124"/>
-      <c r="M63" s="124" t="s">
+      <c r="G63" s="121"/>
+      <c r="H63" s="123"/>
+      <c r="I63" s="123"/>
+      <c r="J63" s="123"/>
+      <c r="K63" s="124"/>
+      <c r="L63" s="123"/>
+      <c r="M63" s="123" t="s">
         <v>56</v>
       </c>
-      <c r="N63" s="124"/>
-      <c r="O63" s="124" t="s">
+      <c r="N63" s="123"/>
+      <c r="O63" s="123" t="s">
         <v>138</v>
       </c>
-      <c r="P63" s="124"/>
-      <c r="Q63" s="124"/>
-      <c r="R63" s="124"/>
-      <c r="S63" s="124"/>
-      <c r="T63" s="126"/>
+      <c r="P63" s="123"/>
+      <c r="Q63" s="123"/>
+      <c r="R63" s="123"/>
+      <c r="S63" s="123"/>
+      <c r="T63" s="125"/>
     </row>
     <row r="64" s="12" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A64" s="122">
+      <c r="A64" s="121">
         <v>30350101</v>
       </c>
-      <c r="B64" s="123">
+      <c r="B64" s="122">
         <v>103501</v>
       </c>
-      <c r="C64" s="123" t="s">
+      <c r="C64" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="D64" s="122">
+      <c r="D64" s="121">
         <v>303503</v>
       </c>
-      <c r="E64" s="124" t="s">
+      <c r="E64" s="123" t="s">
         <v>133</v>
       </c>
-      <c r="F64" s="124" t="s">
+      <c r="F64" s="123" t="s">
         <v>62</v>
       </c>
-      <c r="G64" s="122">
+      <c r="G64" s="121">
         <v>2035012</v>
       </c>
-      <c r="H64" s="124" t="s">
-        <v>63</v>
-      </c>
-      <c r="I64" s="124" t="s">
+      <c r="H64" s="123" t="s">
+        <v>63</v>
+      </c>
+      <c r="I64" s="123" t="s">
         <v>134</v>
       </c>
-      <c r="J64" s="124"/>
-      <c r="K64" s="125" t="s">
+      <c r="J64" s="123"/>
+      <c r="K64" s="124" t="s">
         <v>140</v>
       </c>
-      <c r="L64" s="124" t="s">
+      <c r="L64" s="123" t="s">
         <v>136</v>
       </c>
-      <c r="M64" s="124"/>
-      <c r="N64" s="124"/>
-      <c r="O64" s="124"/>
-      <c r="P64" s="124"/>
-      <c r="Q64" s="124"/>
-      <c r="R64" s="124"/>
-      <c r="S64" s="124"/>
-      <c r="T64" s="126"/>
+      <c r="M64" s="123"/>
+      <c r="N64" s="123"/>
+      <c r="O64" s="123"/>
+      <c r="P64" s="123"/>
+      <c r="Q64" s="123"/>
+      <c r="R64" s="123"/>
+      <c r="S64" s="123"/>
+      <c r="T64" s="125"/>
     </row>
     <row r="65" s="12" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A65" s="122">
+      <c r="A65" s="121">
         <v>30350102</v>
       </c>
-      <c r="B65" s="123">
+      <c r="B65" s="122">
         <v>103501</v>
       </c>
-      <c r="C65" s="123" t="s">
+      <c r="C65" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="D65" s="122">
+      <c r="D65" s="121">
         <v>303504</v>
       </c>
-      <c r="E65" s="124" t="s">
+      <c r="E65" s="123" t="s">
         <v>137</v>
       </c>
-      <c r="F65" s="124" t="s">
+      <c r="F65" s="123" t="s">
         <v>36</v>
       </c>
-      <c r="G65" s="122"/>
-      <c r="H65" s="124"/>
-      <c r="I65" s="124"/>
-      <c r="J65" s="124"/>
-      <c r="K65" s="125"/>
-      <c r="L65" s="124"/>
-      <c r="M65" s="124" t="s">
+      <c r="G65" s="121"/>
+      <c r="H65" s="123"/>
+      <c r="I65" s="123"/>
+      <c r="J65" s="123"/>
+      <c r="K65" s="124"/>
+      <c r="L65" s="123"/>
+      <c r="M65" s="123" t="s">
         <v>56</v>
       </c>
-      <c r="N65" s="124"/>
-      <c r="O65" s="124" t="s">
+      <c r="N65" s="123"/>
+      <c r="O65" s="123" t="s">
         <v>138</v>
       </c>
-      <c r="P65" s="124"/>
-      <c r="Q65" s="124"/>
-      <c r="R65" s="124"/>
-      <c r="S65" s="124"/>
-      <c r="T65" s="126"/>
+      <c r="P65" s="123"/>
+      <c r="Q65" s="123"/>
+      <c r="R65" s="123"/>
+      <c r="S65" s="123"/>
+      <c r="T65" s="125"/>
     </row>
     <row r="66" s="13" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A66" s="127">
+      <c r="A66" s="126">
         <v>30360001</v>
       </c>
-      <c r="B66" s="128">
+      <c r="B66" s="127">
         <v>103600</v>
       </c>
-      <c r="C66" s="128" t="s">
+      <c r="C66" s="127" t="s">
         <v>141</v>
       </c>
-      <c r="D66" s="127">
+      <c r="D66" s="126">
         <v>303601</v>
       </c>
-      <c r="E66" s="129" t="s">
+      <c r="E66" s="128" t="s">
         <v>142</v>
       </c>
-      <c r="F66" s="129" t="s">
+      <c r="F66" s="128" t="s">
         <v>111</v>
       </c>
-      <c r="G66" s="127">
+      <c r="G66" s="126">
         <v>2036002</v>
       </c>
-      <c r="H66" s="129" t="s">
-        <v>63</v>
-      </c>
-      <c r="I66" s="129" t="s">
+      <c r="H66" s="128" t="s">
+        <v>63</v>
+      </c>
+      <c r="I66" s="128" t="s">
         <v>142</v>
       </c>
-      <c r="J66" s="129"/>
-      <c r="K66" s="130">
+      <c r="J66" s="128"/>
+      <c r="K66" s="129">
         <v>10360005</v>
       </c>
-      <c r="L66" s="129" t="s">
+      <c r="L66" s="128" t="s">
         <v>143</v>
       </c>
-      <c r="M66" s="129"/>
-      <c r="N66" s="129"/>
-      <c r="O66" s="129"/>
-      <c r="P66" s="129"/>
-      <c r="Q66" s="129"/>
-      <c r="R66" s="129"/>
-      <c r="S66" s="129"/>
-      <c r="T66" s="131"/>
+      <c r="M66" s="128"/>
+      <c r="N66" s="128"/>
+      <c r="O66" s="128"/>
+      <c r="P66" s="128"/>
+      <c r="Q66" s="128"/>
+      <c r="R66" s="128"/>
+      <c r="S66" s="128"/>
+      <c r="T66" s="130"/>
     </row>
     <row r="67" s="14" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A67" s="132">
+      <c r="A67" s="131">
         <v>30280001</v>
       </c>
-      <c r="B67" s="133">
+      <c r="B67" s="132">
         <v>102800</v>
       </c>
-      <c r="C67" s="133" t="s">
+      <c r="C67" s="132" t="s">
         <v>144</v>
       </c>
-      <c r="D67" s="132">
+      <c r="D67" s="131">
         <v>302801</v>
       </c>
-      <c r="E67" s="134" t="s">
+      <c r="E67" s="133" t="s">
         <v>110</v>
       </c>
-      <c r="F67" s="134" t="s">
+      <c r="F67" s="133" t="s">
         <v>111</v>
       </c>
-      <c r="G67" s="132">
+      <c r="G67" s="131">
         <v>2028001</v>
       </c>
-      <c r="H67" s="134" t="s">
-        <v>63</v>
-      </c>
-      <c r="I67" s="134" t="s">
+      <c r="H67" s="133" t="s">
+        <v>63</v>
+      </c>
+      <c r="I67" s="133" t="s">
         <v>83</v>
       </c>
-      <c r="J67" s="134"/>
-      <c r="K67" s="135" t="s">
+      <c r="J67" s="133"/>
+      <c r="K67" s="134" t="s">
         <v>145</v>
       </c>
-      <c r="L67" s="134" t="s">
+      <c r="L67" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="M67" s="134"/>
-      <c r="N67" s="134"/>
-      <c r="O67" s="134"/>
-      <c r="P67" s="134"/>
-      <c r="Q67" s="134"/>
-      <c r="R67" s="134"/>
-      <c r="S67" s="134"/>
-      <c r="T67" s="136"/>
+      <c r="M67" s="133"/>
+      <c r="N67" s="133"/>
+      <c r="O67" s="133"/>
+      <c r="P67" s="133"/>
+      <c r="Q67" s="133"/>
+      <c r="R67" s="133"/>
+      <c r="S67" s="133"/>
+      <c r="T67" s="135"/>
     </row>
     <row r="68" s="14" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A68" s="132">
+      <c r="A68" s="131">
         <v>30280002</v>
       </c>
-      <c r="B68" s="133">
+      <c r="B68" s="132">
         <v>102800</v>
       </c>
-      <c r="C68" s="133" t="s">
+      <c r="C68" s="132" t="s">
         <v>144</v>
       </c>
-      <c r="D68" s="132">
+      <c r="D68" s="131">
         <v>302802</v>
       </c>
-      <c r="E68" s="134" t="s">
+      <c r="E68" s="133" t="s">
         <v>130</v>
       </c>
-      <c r="F68" s="134" t="s">
+      <c r="F68" s="133" t="s">
         <v>82</v>
       </c>
-      <c r="G68" s="132">
+      <c r="G68" s="131">
         <v>2028001</v>
       </c>
-      <c r="H68" s="134" t="s">
-        <v>63</v>
-      </c>
-      <c r="I68" s="134" t="s">
+      <c r="H68" s="133" t="s">
+        <v>63</v>
+      </c>
+      <c r="I68" s="133" t="s">
         <v>83</v>
       </c>
-      <c r="J68" s="134"/>
-      <c r="K68" s="135" t="s">
+      <c r="J68" s="133"/>
+      <c r="K68" s="134" t="s">
         <v>145</v>
       </c>
-      <c r="L68" s="134" t="s">
+      <c r="L68" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="M68" s="134"/>
-      <c r="N68" s="134"/>
-      <c r="O68" s="134"/>
-      <c r="P68" s="134"/>
-      <c r="Q68" s="134"/>
-      <c r="R68" s="134"/>
-      <c r="S68" s="134"/>
-      <c r="T68" s="136"/>
+      <c r="M68" s="133"/>
+      <c r="N68" s="133"/>
+      <c r="O68" s="133"/>
+      <c r="P68" s="133"/>
+      <c r="Q68" s="133"/>
+      <c r="R68" s="133"/>
+      <c r="S68" s="133"/>
+      <c r="T68" s="135"/>
     </row>
     <row r="69" s="14" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A69" s="132">
+      <c r="A69" s="131">
         <v>30280003</v>
       </c>
-      <c r="B69" s="133">
+      <c r="B69" s="132">
         <v>102800</v>
       </c>
-      <c r="C69" s="133" t="s">
+      <c r="C69" s="132" t="s">
         <v>144</v>
       </c>
-      <c r="D69" s="132">
+      <c r="D69" s="131">
         <v>302803</v>
       </c>
-      <c r="E69" s="134" t="s">
+      <c r="E69" s="133" t="s">
         <v>131</v>
       </c>
-      <c r="F69" s="134" t="s">
+      <c r="F69" s="133" t="s">
         <v>86</v>
       </c>
-      <c r="G69" s="132">
+      <c r="G69" s="131">
         <v>2028001</v>
       </c>
-      <c r="H69" s="134" t="s">
-        <v>63</v>
-      </c>
-      <c r="I69" s="134" t="s">
+      <c r="H69" s="133" t="s">
+        <v>63</v>
+      </c>
+      <c r="I69" s="133" t="s">
         <v>83</v>
       </c>
-      <c r="J69" s="134"/>
-      <c r="K69" s="135" t="s">
+      <c r="J69" s="133"/>
+      <c r="K69" s="134" t="s">
         <v>145</v>
       </c>
-      <c r="L69" s="134" t="s">
+      <c r="L69" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="M69" s="134"/>
-      <c r="N69" s="134"/>
-      <c r="O69" s="134"/>
-      <c r="P69" s="134"/>
-      <c r="Q69" s="134"/>
-      <c r="R69" s="134"/>
-      <c r="S69" s="134"/>
-      <c r="T69" s="136"/>
+      <c r="M69" s="133"/>
+      <c r="N69" s="133"/>
+      <c r="O69" s="133"/>
+      <c r="P69" s="133"/>
+      <c r="Q69" s="133"/>
+      <c r="R69" s="133"/>
+      <c r="S69" s="133"/>
+      <c r="T69" s="135"/>
     </row>
     <row r="70" s="15" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A70" s="137">
+      <c r="A70" s="136">
         <v>30200003</v>
       </c>
-      <c r="B70" s="138">
+      <c r="B70" s="137">
         <v>102000</v>
       </c>
-      <c r="C70" s="138" t="s">
+      <c r="C70" s="137" t="s">
         <v>147</v>
       </c>
-      <c r="D70" s="137">
+      <c r="D70" s="136">
         <v>302003</v>
       </c>
-      <c r="E70" s="139" t="s">
+      <c r="E70" s="138" t="s">
         <v>148</v>
       </c>
-      <c r="F70" s="139" t="s">
+      <c r="F70" s="138" t="s">
         <v>36</v>
       </c>
-      <c r="G70" s="137">
+      <c r="G70" s="136">
         <v>2020001</v>
       </c>
-      <c r="H70" s="139" t="s">
-        <v>63</v>
-      </c>
-      <c r="I70" s="139" t="s">
+      <c r="H70" s="138" t="s">
+        <v>63</v>
+      </c>
+      <c r="I70" s="138" t="s">
         <v>149</v>
       </c>
-      <c r="J70" s="139"/>
-      <c r="K70" s="140">
+      <c r="J70" s="138"/>
+      <c r="K70" s="139">
         <v>10200011</v>
       </c>
       <c r="L70" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="M70" s="139"/>
-      <c r="N70" s="139"/>
-      <c r="O70" s="139"/>
-      <c r="P70" s="139"/>
-      <c r="Q70" s="139" t="s">
+      <c r="M70" s="138"/>
+      <c r="N70" s="138"/>
+      <c r="O70" s="138"/>
+      <c r="P70" s="138"/>
+      <c r="Q70" s="138" t="s">
         <v>151</v>
       </c>
       <c r="R70" s="55"/>
       <c r="S70" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="T70" s="141"/>
+      <c r="T70" s="140"/>
     </row>
     <row r="71" s="15" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A71" s="137">
+      <c r="A71" s="136">
         <v>30200004</v>
       </c>
-      <c r="B71" s="138">
+      <c r="B71" s="137">
         <v>102000</v>
       </c>
-      <c r="C71" s="138" t="s">
+      <c r="C71" s="137" t="s">
         <v>147</v>
       </c>
-      <c r="D71" s="137">
+      <c r="D71" s="136">
         <v>302004</v>
       </c>
-      <c r="E71" s="139" t="s">
+      <c r="E71" s="138" t="s">
         <v>152</v>
       </c>
-      <c r="F71" s="139" t="s">
+      <c r="F71" s="138" t="s">
         <v>36</v>
       </c>
-      <c r="G71" s="137">
+      <c r="G71" s="136">
         <v>2020001</v>
       </c>
-      <c r="H71" s="139" t="s">
-        <v>63</v>
-      </c>
-      <c r="I71" s="139" t="s">
+      <c r="H71" s="138" t="s">
+        <v>63</v>
+      </c>
+      <c r="I71" s="138" t="s">
         <v>149</v>
       </c>
-      <c r="J71" s="139"/>
-      <c r="K71" s="140">
+      <c r="J71" s="138"/>
+      <c r="K71" s="139">
         <v>10200012</v>
       </c>
       <c r="L71" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="M71" s="139"/>
-      <c r="N71" s="139"/>
-      <c r="O71" s="139"/>
-      <c r="P71" s="139"/>
-      <c r="Q71" s="139" t="s">
+      <c r="M71" s="138"/>
+      <c r="N71" s="138"/>
+      <c r="O71" s="138"/>
+      <c r="P71" s="138"/>
+      <c r="Q71" s="138" t="s">
         <v>151</v>
       </c>
       <c r="R71" s="55"/>
       <c r="S71" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="T71" s="141"/>
+      <c r="T71" s="140"/>
     </row>
     <row r="72" s="15" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A72" s="137">
+      <c r="A72" s="136">
         <v>30200005</v>
       </c>
-      <c r="B72" s="138">
+      <c r="B72" s="137">
         <v>102000</v>
       </c>
-      <c r="C72" s="138" t="s">
+      <c r="C72" s="137" t="s">
         <v>147</v>
       </c>
-      <c r="D72" s="137">
+      <c r="D72" s="136">
         <v>302005</v>
       </c>
-      <c r="E72" s="139" t="s">
+      <c r="E72" s="138" t="s">
         <v>154</v>
       </c>
-      <c r="F72" s="139" t="s">
+      <c r="F72" s="138" t="s">
         <v>36</v>
       </c>
-      <c r="G72" s="137">
+      <c r="G72" s="136">
         <v>2020001</v>
       </c>
-      <c r="H72" s="139" t="s">
-        <v>63</v>
-      </c>
-      <c r="I72" s="139" t="s">
+      <c r="H72" s="138" t="s">
+        <v>63</v>
+      </c>
+      <c r="I72" s="138" t="s">
         <v>149</v>
       </c>
-      <c r="J72" s="139"/>
-      <c r="K72" s="140">
+      <c r="J72" s="138"/>
+      <c r="K72" s="139">
         <v>10200013</v>
       </c>
       <c r="L72" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="M72" s="139"/>
-      <c r="N72" s="139"/>
-      <c r="O72" s="139"/>
-      <c r="P72" s="139"/>
-      <c r="Q72" s="139" t="s">
+      <c r="M72" s="138"/>
+      <c r="N72" s="138"/>
+      <c r="O72" s="138"/>
+      <c r="P72" s="138"/>
+      <c r="Q72" s="138" t="s">
         <v>151</v>
       </c>
       <c r="R72" s="55"/>
       <c r="S72" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="T72" s="141"/>
+      <c r="T72" s="140"/>
     </row>
     <row r="73" s="15" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A73" s="137">
+      <c r="A73" s="136">
         <v>30200006</v>
       </c>
-      <c r="B73" s="138">
+      <c r="B73" s="137">
         <v>102000</v>
       </c>
-      <c r="C73" s="138" t="s">
+      <c r="C73" s="137" t="s">
         <v>147</v>
       </c>
-      <c r="D73" s="137">
+      <c r="D73" s="136">
         <v>302006</v>
       </c>
-      <c r="E73" s="139" t="s">
+      <c r="E73" s="138" t="s">
         <v>156</v>
       </c>
-      <c r="F73" s="139" t="s">
+      <c r="F73" s="138" t="s">
         <v>36</v>
       </c>
-      <c r="G73" s="137">
+      <c r="G73" s="136">
         <v>2020001</v>
       </c>
-      <c r="H73" s="139" t="s">
-        <v>63</v>
-      </c>
-      <c r="I73" s="139" t="s">
+      <c r="H73" s="138" t="s">
+        <v>63</v>
+      </c>
+      <c r="I73" s="138" t="s">
         <v>149</v>
       </c>
-      <c r="J73" s="139"/>
-      <c r="K73" s="140">
+      <c r="J73" s="138"/>
+      <c r="K73" s="139">
         <v>10200014</v>
       </c>
       <c r="L73" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="M73" s="139"/>
-      <c r="N73" s="139"/>
-      <c r="O73" s="139"/>
-      <c r="P73" s="139"/>
-      <c r="Q73" s="139" t="s">
+      <c r="M73" s="138"/>
+      <c r="N73" s="138"/>
+      <c r="O73" s="138"/>
+      <c r="P73" s="138"/>
+      <c r="Q73" s="138" t="s">
         <v>151</v>
       </c>
       <c r="R73" s="55"/>
       <c r="S73" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="T73" s="141"/>
+      <c r="T73" s="140"/>
     </row>
     <row r="74" s="15" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A74" s="137">
+      <c r="A74" s="136">
         <v>30200007</v>
       </c>
-      <c r="B74" s="138">
+      <c r="B74" s="137">
         <v>102000</v>
       </c>
-      <c r="C74" s="138" t="s">
+      <c r="C74" s="137" t="s">
         <v>147</v>
       </c>
-      <c r="D74" s="137">
+      <c r="D74" s="136">
         <v>302007</v>
       </c>
-      <c r="E74" s="139" t="s">
+      <c r="E74" s="138" t="s">
         <v>158</v>
       </c>
-      <c r="F74" s="139" t="s">
+      <c r="F74" s="138" t="s">
         <v>56</v>
       </c>
-      <c r="G74" s="137">
+      <c r="G74" s="136">
         <v>2020001</v>
       </c>
-      <c r="H74" s="139" t="s">
-        <v>63</v>
-      </c>
-      <c r="I74" s="139"/>
-      <c r="J74" s="139"/>
-      <c r="K74" s="140"/>
+      <c r="H74" s="138" t="s">
+        <v>63</v>
+      </c>
+      <c r="I74" s="138"/>
+      <c r="J74" s="138"/>
+      <c r="K74" s="139"/>
       <c r="L74" s="4"/>
-      <c r="M74" s="139"/>
-      <c r="N74" s="139"/>
-      <c r="O74" s="139"/>
-      <c r="P74" s="139"/>
-      <c r="Q74" s="139" t="s">
+      <c r="M74" s="138"/>
+      <c r="N74" s="138"/>
+      <c r="O74" s="138"/>
+      <c r="P74" s="138"/>
+      <c r="Q74" s="138" t="s">
         <v>151</v>
       </c>
-      <c r="R74" s="139"/>
-      <c r="S74" s="139" t="s">
+      <c r="R74" s="138"/>
+      <c r="S74" s="138" t="s">
         <v>42</v>
       </c>
-      <c r="T74" s="141"/>
+      <c r="T74" s="140"/>
     </row>
     <row r="75" s="15" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A75" s="137">
+      <c r="A75" s="136">
         <v>30200008</v>
       </c>
-      <c r="B75" s="138">
+      <c r="B75" s="137">
         <v>102000</v>
       </c>
-      <c r="C75" s="138" t="s">
+      <c r="C75" s="137" t="s">
         <v>147</v>
       </c>
-      <c r="D75" s="137">
+      <c r="D75" s="136">
         <v>302008</v>
       </c>
-      <c r="E75" s="139" t="s">
+      <c r="E75" s="138" t="s">
         <v>159</v>
       </c>
-      <c r="F75" s="139" t="s">
+      <c r="F75" s="138" t="s">
         <v>36</v>
       </c>
-      <c r="G75" s="137">
+      <c r="G75" s="136">
         <v>2020001</v>
       </c>
-      <c r="H75" s="139" t="s">
-        <v>63</v>
-      </c>
-      <c r="I75" s="139"/>
-      <c r="J75" s="139"/>
-      <c r="K75" s="140"/>
+      <c r="H75" s="138" t="s">
+        <v>63</v>
+      </c>
+      <c r="I75" s="138"/>
+      <c r="J75" s="138"/>
+      <c r="K75" s="139"/>
       <c r="L75" s="4"/>
-      <c r="M75" s="139"/>
-      <c r="N75" s="139"/>
-      <c r="O75" s="139"/>
-      <c r="P75" s="139"/>
-      <c r="Q75" s="139" t="s">
+      <c r="M75" s="138"/>
+      <c r="N75" s="138"/>
+      <c r="O75" s="138"/>
+      <c r="P75" s="138"/>
+      <c r="Q75" s="138" t="s">
         <v>151</v>
       </c>
-      <c r="R75" s="139"/>
-      <c r="S75" s="139" t="s">
+      <c r="R75" s="138"/>
+      <c r="S75" s="138" t="s">
         <v>42</v>
       </c>
-      <c r="T75" s="141"/>
+      <c r="T75" s="140"/>
     </row>
     <row r="76" s="16" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A76" s="142">
+      <c r="A76" s="141">
         <v>30200009</v>
       </c>
-      <c r="B76" s="143">
+      <c r="B76" s="142">
         <v>102000</v>
       </c>
-      <c r="C76" s="143" t="s">
+      <c r="C76" s="142" t="s">
         <v>147</v>
       </c>
-      <c r="D76" s="142">
+      <c r="D76" s="141">
         <v>302009</v>
       </c>
-      <c r="E76" s="144" t="s">
+      <c r="E76" s="143" t="s">
         <v>160</v>
       </c>
-      <c r="F76" s="144" t="s">
+      <c r="F76" s="143" t="s">
         <v>111</v>
       </c>
-      <c r="G76" s="142">
+      <c r="G76" s="141">
         <v>2020002</v>
       </c>
-      <c r="H76" s="144" t="s">
-        <v>63</v>
-      </c>
-      <c r="I76" s="144" t="s">
+      <c r="H76" s="143" t="s">
+        <v>63</v>
+      </c>
+      <c r="I76" s="143" t="s">
         <v>83</v>
       </c>
-      <c r="J76" s="144"/>
-      <c r="K76" s="145" t="s">
+      <c r="J76" s="143"/>
+      <c r="K76" s="144" t="s">
         <v>161</v>
       </c>
-      <c r="L76" s="144" t="s">
+      <c r="L76" s="143" t="s">
         <v>162</v>
       </c>
-      <c r="M76" s="144"/>
-      <c r="N76" s="144"/>
-      <c r="O76" s="144"/>
-      <c r="P76" s="144"/>
+      <c r="M76" s="143"/>
+      <c r="N76" s="143"/>
+      <c r="O76" s="143"/>
+      <c r="P76" s="143"/>
       <c r="Q76" s="54"/>
       <c r="R76" s="55"/>
       <c r="S76" s="55"/>
-      <c r="T76" s="146"/>
+      <c r="T76" s="145"/>
     </row>
     <row r="77" s="16" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A77" s="142">
+      <c r="A77" s="141">
         <v>30200010</v>
       </c>
-      <c r="B77" s="143">
+      <c r="B77" s="142">
         <v>102000</v>
       </c>
-      <c r="C77" s="143" t="s">
+      <c r="C77" s="142" t="s">
         <v>147</v>
       </c>
-      <c r="D77" s="142">
+      <c r="D77" s="141">
         <v>302010</v>
       </c>
-      <c r="E77" s="144" t="s">
+      <c r="E77" s="143" t="s">
         <v>163</v>
       </c>
-      <c r="F77" s="144" t="s">
+      <c r="F77" s="143" t="s">
         <v>56</v>
       </c>
-      <c r="G77" s="142">
+      <c r="G77" s="141">
         <v>2020002</v>
       </c>
-      <c r="H77" s="144" t="s">
-        <v>63</v>
-      </c>
-      <c r="I77" s="144"/>
-      <c r="J77" s="144"/>
+      <c r="H77" s="143" t="s">
+        <v>63</v>
+      </c>
+      <c r="I77" s="143"/>
+      <c r="J77" s="143"/>
       <c r="K77" s="53">
         <v>10200120</v>
       </c>
-      <c r="L77" s="147" t="s">
+      <c r="L77" s="146" t="s">
         <v>164</v>
       </c>
-      <c r="M77" s="144"/>
-      <c r="N77" s="144"/>
-      <c r="O77" s="144"/>
-      <c r="P77" s="144"/>
+      <c r="M77" s="143"/>
+      <c r="N77" s="143"/>
+      <c r="O77" s="143"/>
+      <c r="P77" s="143"/>
       <c r="Q77" s="54" t="s">
         <v>165</v>
       </c>
@@ -6072,45 +6051,45 @@
       <c r="S77" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="T77" s="146"/>
+      <c r="T77" s="145"/>
     </row>
     <row r="78" s="16" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A78" s="142">
+      <c r="A78" s="141">
         <v>30200011</v>
       </c>
-      <c r="B78" s="143">
+      <c r="B78" s="142">
         <v>102000</v>
       </c>
-      <c r="C78" s="143" t="s">
+      <c r="C78" s="142" t="s">
         <v>147</v>
       </c>
-      <c r="D78" s="142">
+      <c r="D78" s="141">
         <v>302011</v>
       </c>
-      <c r="E78" s="144" t="s">
+      <c r="E78" s="143" t="s">
         <v>166</v>
       </c>
-      <c r="F78" s="144" t="s">
+      <c r="F78" s="143" t="s">
         <v>56</v>
       </c>
-      <c r="G78" s="142">
+      <c r="G78" s="141">
         <v>2020002</v>
       </c>
-      <c r="H78" s="144" t="s">
-        <v>63</v>
-      </c>
-      <c r="I78" s="144"/>
-      <c r="J78" s="144"/>
+      <c r="H78" s="143" t="s">
+        <v>63</v>
+      </c>
+      <c r="I78" s="143"/>
+      <c r="J78" s="143"/>
       <c r="K78" s="53">
         <v>10200220</v>
       </c>
-      <c r="L78" s="147" t="s">
+      <c r="L78" s="146" t="s">
         <v>167</v>
       </c>
-      <c r="M78" s="144"/>
-      <c r="N78" s="144"/>
-      <c r="O78" s="144"/>
-      <c r="P78" s="144"/>
+      <c r="M78" s="143"/>
+      <c r="N78" s="143"/>
+      <c r="O78" s="143"/>
+      <c r="P78" s="143"/>
       <c r="Q78" s="54" t="s">
         <v>165</v>
       </c>
@@ -6118,45 +6097,45 @@
       <c r="S78" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="T78" s="146"/>
+      <c r="T78" s="145"/>
     </row>
     <row r="79" s="16" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A79" s="142">
+      <c r="A79" s="141">
         <v>30200012</v>
       </c>
-      <c r="B79" s="143">
+      <c r="B79" s="142">
         <v>102000</v>
       </c>
-      <c r="C79" s="143" t="s">
+      <c r="C79" s="142" t="s">
         <v>147</v>
       </c>
-      <c r="D79" s="142">
+      <c r="D79" s="141">
         <v>302012</v>
       </c>
-      <c r="E79" s="144" t="s">
+      <c r="E79" s="143" t="s">
         <v>168</v>
       </c>
-      <c r="F79" s="144" t="s">
+      <c r="F79" s="143" t="s">
         <v>56</v>
       </c>
-      <c r="G79" s="142">
+      <c r="G79" s="141">
         <v>2020002</v>
       </c>
-      <c r="H79" s="144" t="s">
-        <v>63</v>
-      </c>
-      <c r="I79" s="144"/>
-      <c r="J79" s="144"/>
+      <c r="H79" s="143" t="s">
+        <v>63</v>
+      </c>
+      <c r="I79" s="143"/>
+      <c r="J79" s="143"/>
       <c r="K79" s="53">
         <v>10200320</v>
       </c>
-      <c r="L79" s="147" t="s">
+      <c r="L79" s="146" t="s">
         <v>169</v>
       </c>
-      <c r="M79" s="144"/>
-      <c r="N79" s="144"/>
-      <c r="O79" s="144"/>
-      <c r="P79" s="144"/>
+      <c r="M79" s="143"/>
+      <c r="N79" s="143"/>
+      <c r="O79" s="143"/>
+      <c r="P79" s="143"/>
       <c r="Q79" s="54" t="s">
         <v>165</v>
       </c>
@@ -6164,45 +6143,45 @@
       <c r="S79" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="T79" s="146"/>
+      <c r="T79" s="145"/>
     </row>
     <row r="80" s="16" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A80" s="142">
+      <c r="A80" s="141">
         <v>30200013</v>
       </c>
-      <c r="B80" s="143">
+      <c r="B80" s="142">
         <v>102000</v>
       </c>
-      <c r="C80" s="143" t="s">
+      <c r="C80" s="142" t="s">
         <v>147</v>
       </c>
-      <c r="D80" s="142">
+      <c r="D80" s="141">
         <v>302013</v>
       </c>
-      <c r="E80" s="144" t="s">
+      <c r="E80" s="143" t="s">
         <v>170</v>
       </c>
-      <c r="F80" s="144" t="s">
+      <c r="F80" s="143" t="s">
         <v>56</v>
       </c>
-      <c r="G80" s="142">
+      <c r="G80" s="141">
         <v>2020002</v>
       </c>
-      <c r="H80" s="144" t="s">
-        <v>63</v>
-      </c>
-      <c r="I80" s="144"/>
-      <c r="J80" s="144"/>
+      <c r="H80" s="143" t="s">
+        <v>63</v>
+      </c>
+      <c r="I80" s="143"/>
+      <c r="J80" s="143"/>
       <c r="K80" s="53">
         <v>10200420</v>
       </c>
-      <c r="L80" s="147" t="s">
+      <c r="L80" s="146" t="s">
         <v>171</v>
       </c>
-      <c r="M80" s="144"/>
-      <c r="N80" s="144"/>
-      <c r="O80" s="144"/>
-      <c r="P80" s="144"/>
+      <c r="M80" s="143"/>
+      <c r="N80" s="143"/>
+      <c r="O80" s="143"/>
+      <c r="P80" s="143"/>
       <c r="Q80" s="54" t="s">
         <v>165</v>
       </c>
@@ -6210,675 +6189,675 @@
       <c r="S80" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="T80" s="146"/>
+      <c r="T80" s="145"/>
     </row>
     <row r="81" s="10" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A81" s="112">
+      <c r="A81" s="111">
         <v>30200014</v>
       </c>
-      <c r="B81" s="113">
+      <c r="B81" s="112">
         <v>102000</v>
       </c>
-      <c r="C81" s="113" t="s">
+      <c r="C81" s="112" t="s">
         <v>147</v>
       </c>
-      <c r="D81" s="112">
+      <c r="D81" s="111">
         <v>302014</v>
       </c>
-      <c r="E81" s="114" t="s">
+      <c r="E81" s="113" t="s">
         <v>172</v>
       </c>
-      <c r="F81" s="114" t="s">
+      <c r="F81" s="113" t="s">
         <v>111</v>
       </c>
-      <c r="G81" s="112">
+      <c r="G81" s="111">
         <v>2020003</v>
       </c>
-      <c r="H81" s="114" t="s">
-        <v>63</v>
-      </c>
-      <c r="I81" s="114" t="s">
+      <c r="H81" s="113" t="s">
+        <v>63</v>
+      </c>
+      <c r="I81" s="113" t="s">
         <v>83</v>
       </c>
-      <c r="J81" s="114"/>
-      <c r="K81" s="115" t="s">
+      <c r="J81" s="113"/>
+      <c r="K81" s="114" t="s">
         <v>173</v>
       </c>
-      <c r="L81" s="114" t="s">
+      <c r="L81" s="113" t="s">
         <v>174</v>
       </c>
-      <c r="M81" s="114"/>
-      <c r="N81" s="114"/>
-      <c r="O81" s="114"/>
-      <c r="P81" s="114"/>
-      <c r="Q81" s="114"/>
-      <c r="R81" s="114"/>
-      <c r="S81" s="114"/>
-      <c r="T81" s="116"/>
+      <c r="M81" s="113"/>
+      <c r="N81" s="113"/>
+      <c r="O81" s="113"/>
+      <c r="P81" s="113"/>
+      <c r="Q81" s="113"/>
+      <c r="R81" s="113"/>
+      <c r="S81" s="113"/>
+      <c r="T81" s="115"/>
     </row>
     <row r="82" s="10" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A82" s="112">
+      <c r="A82" s="111">
         <v>30200015</v>
       </c>
-      <c r="B82" s="113">
+      <c r="B82" s="112">
         <v>102000</v>
       </c>
-      <c r="C82" s="113" t="s">
+      <c r="C82" s="112" t="s">
         <v>147</v>
       </c>
-      <c r="D82" s="112">
+      <c r="D82" s="111">
         <v>302015</v>
       </c>
-      <c r="E82" s="114" t="s">
+      <c r="E82" s="113" t="s">
         <v>175</v>
       </c>
-      <c r="F82" s="114" t="s">
+      <c r="F82" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="G82" s="112">
+      <c r="G82" s="111">
         <v>2020003</v>
       </c>
-      <c r="H82" s="114" t="s">
-        <v>63</v>
-      </c>
-      <c r="I82" s="114"/>
-      <c r="J82" s="114"/>
-      <c r="K82" s="115">
+      <c r="H82" s="113" t="s">
+        <v>63</v>
+      </c>
+      <c r="I82" s="113"/>
+      <c r="J82" s="113"/>
+      <c r="K82" s="114">
         <v>10200125</v>
       </c>
-      <c r="L82" s="114" t="s">
+      <c r="L82" s="113" t="s">
         <v>176</v>
       </c>
-      <c r="M82" s="114"/>
-      <c r="N82" s="114"/>
-      <c r="O82" s="114"/>
-      <c r="P82" s="114"/>
-      <c r="Q82" s="148" t="s">
+      <c r="M82" s="113"/>
+      <c r="N82" s="113"/>
+      <c r="O82" s="113"/>
+      <c r="P82" s="113"/>
+      <c r="Q82" s="147" t="s">
         <v>165</v>
       </c>
-      <c r="R82" s="149"/>
-      <c r="S82" s="149" t="s">
+      <c r="R82" s="148"/>
+      <c r="S82" s="148" t="s">
         <v>42</v>
       </c>
-      <c r="T82" s="116"/>
+      <c r="T82" s="115"/>
     </row>
     <row r="83" s="10" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A83" s="112">
+      <c r="A83" s="111">
         <v>30200016</v>
       </c>
-      <c r="B83" s="113">
+      <c r="B83" s="112">
         <v>102000</v>
       </c>
-      <c r="C83" s="113" t="s">
+      <c r="C83" s="112" t="s">
         <v>147</v>
       </c>
-      <c r="D83" s="112">
+      <c r="D83" s="111">
         <v>302016</v>
       </c>
-      <c r="E83" s="114" t="s">
+      <c r="E83" s="113" t="s">
         <v>177</v>
       </c>
-      <c r="F83" s="114" t="s">
+      <c r="F83" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="G83" s="112">
+      <c r="G83" s="111">
         <v>2020003</v>
       </c>
-      <c r="H83" s="114" t="s">
-        <v>63</v>
-      </c>
-      <c r="I83" s="114"/>
-      <c r="J83" s="114"/>
-      <c r="K83" s="115">
+      <c r="H83" s="113" t="s">
+        <v>63</v>
+      </c>
+      <c r="I83" s="113"/>
+      <c r="J83" s="113"/>
+      <c r="K83" s="114">
         <v>10200225</v>
       </c>
-      <c r="L83" s="114" t="s">
+      <c r="L83" s="113" t="s">
         <v>178</v>
       </c>
-      <c r="M83" s="114"/>
-      <c r="N83" s="114"/>
-      <c r="O83" s="114"/>
-      <c r="P83" s="114"/>
-      <c r="Q83" s="148" t="s">
+      <c r="M83" s="113"/>
+      <c r="N83" s="113"/>
+      <c r="O83" s="113"/>
+      <c r="P83" s="113"/>
+      <c r="Q83" s="147" t="s">
         <v>165</v>
       </c>
-      <c r="R83" s="149"/>
-      <c r="S83" s="149" t="s">
+      <c r="R83" s="148"/>
+      <c r="S83" s="148" t="s">
         <v>42</v>
       </c>
-      <c r="T83" s="116"/>
+      <c r="T83" s="115"/>
     </row>
     <row r="84" s="10" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A84" s="112">
+      <c r="A84" s="111">
         <v>30200017</v>
       </c>
-      <c r="B84" s="113">
+      <c r="B84" s="112">
         <v>102000</v>
       </c>
-      <c r="C84" s="113" t="s">
+      <c r="C84" s="112" t="s">
         <v>147</v>
       </c>
-      <c r="D84" s="112">
+      <c r="D84" s="111">
         <v>302017</v>
       </c>
-      <c r="E84" s="114" t="s">
+      <c r="E84" s="113" t="s">
         <v>179</v>
       </c>
-      <c r="F84" s="114" t="s">
+      <c r="F84" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="G84" s="112">
+      <c r="G84" s="111">
         <v>2020003</v>
       </c>
-      <c r="H84" s="114" t="s">
-        <v>63</v>
-      </c>
-      <c r="I84" s="114"/>
-      <c r="J84" s="114"/>
-      <c r="K84" s="115">
+      <c r="H84" s="113" t="s">
+        <v>63</v>
+      </c>
+      <c r="I84" s="113"/>
+      <c r="J84" s="113"/>
+      <c r="K84" s="114">
         <v>10200325</v>
       </c>
-      <c r="L84" s="114" t="s">
+      <c r="L84" s="113" t="s">
         <v>180</v>
       </c>
-      <c r="M84" s="114"/>
-      <c r="N84" s="114"/>
-      <c r="O84" s="114"/>
-      <c r="P84" s="114"/>
-      <c r="Q84" s="148" t="s">
+      <c r="M84" s="113"/>
+      <c r="N84" s="113"/>
+      <c r="O84" s="113"/>
+      <c r="P84" s="113"/>
+      <c r="Q84" s="147" t="s">
         <v>165</v>
       </c>
-      <c r="R84" s="149"/>
-      <c r="S84" s="149" t="s">
+      <c r="R84" s="148"/>
+      <c r="S84" s="148" t="s">
         <v>42</v>
       </c>
-      <c r="T84" s="116"/>
+      <c r="T84" s="115"/>
     </row>
     <row r="85" s="10" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A85" s="112">
+      <c r="A85" s="111">
         <v>30200018</v>
       </c>
-      <c r="B85" s="113">
+      <c r="B85" s="112">
         <v>102000</v>
       </c>
-      <c r="C85" s="113" t="s">
+      <c r="C85" s="112" t="s">
         <v>147</v>
       </c>
-      <c r="D85" s="112">
+      <c r="D85" s="111">
         <v>302018</v>
       </c>
-      <c r="E85" s="114" t="s">
+      <c r="E85" s="113" t="s">
         <v>181</v>
       </c>
-      <c r="F85" s="114" t="s">
+      <c r="F85" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="G85" s="112">
+      <c r="G85" s="111">
         <v>2020003</v>
       </c>
-      <c r="H85" s="114" t="s">
-        <v>63</v>
-      </c>
-      <c r="I85" s="114"/>
-      <c r="J85" s="114"/>
-      <c r="K85" s="115">
+      <c r="H85" s="113" t="s">
+        <v>63</v>
+      </c>
+      <c r="I85" s="113"/>
+      <c r="J85" s="113"/>
+      <c r="K85" s="114">
         <v>10200425</v>
       </c>
-      <c r="L85" s="114" t="s">
+      <c r="L85" s="113" t="s">
         <v>182</v>
       </c>
-      <c r="M85" s="114"/>
-      <c r="N85" s="114"/>
-      <c r="O85" s="114"/>
-      <c r="P85" s="114"/>
-      <c r="Q85" s="148" t="s">
+      <c r="M85" s="113"/>
+      <c r="N85" s="113"/>
+      <c r="O85" s="113"/>
+      <c r="P85" s="113"/>
+      <c r="Q85" s="147" t="s">
         <v>165</v>
       </c>
-      <c r="R85" s="149"/>
-      <c r="S85" s="149" t="s">
+      <c r="R85" s="148"/>
+      <c r="S85" s="148" t="s">
         <v>42</v>
       </c>
-      <c r="T85" s="116"/>
+      <c r="T85" s="115"/>
     </row>
     <row r="86" s="13" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A86" s="127">
+      <c r="A86" s="126">
         <v>30380001</v>
       </c>
-      <c r="B86" s="128">
+      <c r="B86" s="127">
         <v>103800</v>
       </c>
-      <c r="C86" s="128" t="s">
+      <c r="C86" s="127" t="s">
         <v>183</v>
       </c>
-      <c r="D86" s="127">
+      <c r="D86" s="126">
         <v>303801</v>
       </c>
-      <c r="E86" s="129" t="s">
+      <c r="E86" s="128" t="s">
         <v>184</v>
       </c>
-      <c r="F86" s="129" t="s">
+      <c r="F86" s="128" t="s">
         <v>185</v>
       </c>
-      <c r="G86" s="127">
+      <c r="G86" s="126">
         <v>2038001</v>
       </c>
-      <c r="H86" s="129" t="s">
-        <v>63</v>
-      </c>
-      <c r="I86" s="129"/>
-      <c r="J86" s="129"/>
-      <c r="K86" s="130" t="s">
+      <c r="H86" s="128" t="s">
+        <v>63</v>
+      </c>
+      <c r="I86" s="128"/>
+      <c r="J86" s="128"/>
+      <c r="K86" s="129" t="s">
         <v>186</v>
       </c>
-      <c r="L86" s="129" t="s">
+      <c r="L86" s="128" t="s">
         <v>187</v>
       </c>
-      <c r="M86" s="129"/>
-      <c r="N86" s="129"/>
-      <c r="O86" s="129"/>
-      <c r="P86" s="129"/>
-      <c r="Q86" s="150"/>
-      <c r="R86" s="151"/>
-      <c r="S86" s="151"/>
-      <c r="T86" s="131"/>
+      <c r="M86" s="128"/>
+      <c r="N86" s="128"/>
+      <c r="O86" s="128"/>
+      <c r="P86" s="128"/>
+      <c r="Q86" s="149"/>
+      <c r="R86" s="150"/>
+      <c r="S86" s="150"/>
+      <c r="T86" s="130"/>
     </row>
     <row r="87" s="13" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A87" s="127">
+      <c r="A87" s="126">
         <v>30380002</v>
       </c>
-      <c r="B87" s="128">
+      <c r="B87" s="127">
         <v>103800</v>
       </c>
-      <c r="C87" s="128" t="s">
+      <c r="C87" s="127" t="s">
         <v>183</v>
       </c>
-      <c r="D87" s="127">
+      <c r="D87" s="126">
         <v>303802</v>
       </c>
-      <c r="E87" s="129" t="s">
+      <c r="E87" s="128" t="s">
         <v>188</v>
       </c>
-      <c r="F87" s="129" t="s">
+      <c r="F87" s="128" t="s">
         <v>36</v>
       </c>
-      <c r="G87" s="127">
+      <c r="G87" s="126">
         <v>2038001</v>
       </c>
-      <c r="H87" s="129" t="s">
-        <v>63</v>
-      </c>
-      <c r="I87" s="129"/>
-      <c r="J87" s="129"/>
-      <c r="K87" s="130"/>
-      <c r="L87" s="129"/>
-      <c r="M87" s="129" t="s">
+      <c r="H87" s="128" t="s">
+        <v>63</v>
+      </c>
+      <c r="I87" s="128"/>
+      <c r="J87" s="128"/>
+      <c r="K87" s="129"/>
+      <c r="L87" s="128"/>
+      <c r="M87" s="128" t="s">
         <v>56</v>
       </c>
-      <c r="N87" s="129"/>
-      <c r="O87" s="129" t="s">
+      <c r="N87" s="128"/>
+      <c r="O87" s="128" t="s">
         <v>189</v>
       </c>
-      <c r="P87" s="129"/>
-      <c r="Q87" s="150"/>
-      <c r="R87" s="151"/>
-      <c r="S87" s="151"/>
-      <c r="T87" s="131"/>
+      <c r="P87" s="128"/>
+      <c r="Q87" s="149"/>
+      <c r="R87" s="150"/>
+      <c r="S87" s="150"/>
+      <c r="T87" s="130"/>
     </row>
     <row r="88" s="17" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A88" s="152">
+      <c r="A88" s="151">
         <v>30270001</v>
       </c>
-      <c r="B88" s="153">
+      <c r="B88" s="152">
         <v>102700</v>
       </c>
-      <c r="C88" s="153" t="s">
+      <c r="C88" s="152" t="s">
         <v>190</v>
       </c>
-      <c r="D88" s="152">
+      <c r="D88" s="151">
         <v>302701</v>
       </c>
-      <c r="E88" s="154" t="s">
+      <c r="E88" s="153" t="s">
         <v>191</v>
       </c>
-      <c r="F88" s="154" t="s">
+      <c r="F88" s="153" t="s">
         <v>82</v>
       </c>
-      <c r="G88" s="152">
+      <c r="G88" s="151">
         <v>2027001</v>
       </c>
-      <c r="H88" s="154" t="s">
-        <v>63</v>
-      </c>
-      <c r="I88" s="154" t="s">
+      <c r="H88" s="153" t="s">
+        <v>63</v>
+      </c>
+      <c r="I88" s="153" t="s">
         <v>83</v>
       </c>
-      <c r="J88" s="154"/>
-      <c r="K88" s="155" t="s">
+      <c r="J88" s="153"/>
+      <c r="K88" s="154" t="s">
         <v>192</v>
       </c>
-      <c r="L88" s="154" t="s">
+      <c r="L88" s="153" t="s">
         <v>193</v>
       </c>
-      <c r="M88" s="154"/>
-      <c r="N88" s="154"/>
-      <c r="O88" s="154"/>
-      <c r="P88" s="154"/>
-      <c r="Q88" s="156"/>
-      <c r="R88" s="157"/>
-      <c r="S88" s="157"/>
-      <c r="T88" s="158"/>
+      <c r="M88" s="153"/>
+      <c r="N88" s="153"/>
+      <c r="O88" s="153"/>
+      <c r="P88" s="153"/>
+      <c r="Q88" s="155"/>
+      <c r="R88" s="156"/>
+      <c r="S88" s="156"/>
+      <c r="T88" s="157"/>
     </row>
     <row r="89" s="17" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A89" s="152">
+      <c r="A89" s="151">
         <v>30270002</v>
       </c>
-      <c r="B89" s="153">
+      <c r="B89" s="152">
         <v>102700</v>
       </c>
-      <c r="C89" s="153" t="s">
+      <c r="C89" s="152" t="s">
         <v>190</v>
       </c>
-      <c r="D89" s="152">
+      <c r="D89" s="151">
         <v>302702</v>
       </c>
-      <c r="E89" s="154" t="s">
+      <c r="E89" s="153" t="s">
         <v>194</v>
       </c>
-      <c r="F89" s="154" t="s">
+      <c r="F89" s="153" t="s">
         <v>124</v>
       </c>
-      <c r="G89" s="152">
+      <c r="G89" s="151">
         <v>2027001</v>
       </c>
-      <c r="H89" s="154" t="s">
-        <v>63</v>
-      </c>
-      <c r="I89" s="154" t="s">
+      <c r="H89" s="153" t="s">
+        <v>63</v>
+      </c>
+      <c r="I89" s="153" t="s">
         <v>83</v>
       </c>
-      <c r="J89" s="154"/>
-      <c r="K89" s="155" t="s">
+      <c r="J89" s="153"/>
+      <c r="K89" s="154" t="s">
         <v>192</v>
       </c>
-      <c r="L89" s="154" t="s">
+      <c r="L89" s="153" t="s">
         <v>193</v>
       </c>
-      <c r="M89" s="154"/>
-      <c r="N89" s="154"/>
-      <c r="O89" s="154"/>
-      <c r="P89" s="154"/>
-      <c r="Q89" s="156"/>
-      <c r="R89" s="157"/>
-      <c r="S89" s="157"/>
-      <c r="T89" s="158"/>
+      <c r="M89" s="153"/>
+      <c r="N89" s="153"/>
+      <c r="O89" s="153"/>
+      <c r="P89" s="153"/>
+      <c r="Q89" s="155"/>
+      <c r="R89" s="156"/>
+      <c r="S89" s="156"/>
+      <c r="T89" s="157"/>
     </row>
     <row r="90" s="17" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A90" s="152">
+      <c r="A90" s="151">
         <v>30270003</v>
       </c>
-      <c r="B90" s="153">
+      <c r="B90" s="152">
         <v>102700</v>
       </c>
-      <c r="C90" s="153" t="s">
+      <c r="C90" s="152" t="s">
         <v>190</v>
       </c>
-      <c r="D90" s="152">
+      <c r="D90" s="151">
         <v>302703</v>
       </c>
-      <c r="E90" s="154" t="s">
+      <c r="E90" s="153" t="s">
         <v>195</v>
       </c>
-      <c r="F90" s="154" t="s">
+      <c r="F90" s="153" t="s">
         <v>196</v>
       </c>
-      <c r="G90" s="152">
+      <c r="G90" s="151">
         <v>2027001</v>
       </c>
-      <c r="H90" s="154" t="s">
-        <v>63</v>
-      </c>
-      <c r="I90" s="154" t="s">
+      <c r="H90" s="153" t="s">
+        <v>63</v>
+      </c>
+      <c r="I90" s="153" t="s">
         <v>83</v>
       </c>
-      <c r="J90" s="154"/>
-      <c r="K90" s="155" t="s">
+      <c r="J90" s="153"/>
+      <c r="K90" s="154" t="s">
         <v>192</v>
       </c>
-      <c r="L90" s="154" t="s">
+      <c r="L90" s="153" t="s">
         <v>193</v>
       </c>
-      <c r="M90" s="154"/>
-      <c r="N90" s="154"/>
-      <c r="O90" s="154"/>
-      <c r="P90" s="154"/>
-      <c r="Q90" s="156"/>
-      <c r="R90" s="157"/>
-      <c r="S90" s="157"/>
-      <c r="T90" s="158"/>
+      <c r="M90" s="153"/>
+      <c r="N90" s="153"/>
+      <c r="O90" s="153"/>
+      <c r="P90" s="153"/>
+      <c r="Q90" s="155"/>
+      <c r="R90" s="156"/>
+      <c r="S90" s="156"/>
+      <c r="T90" s="157"/>
     </row>
     <row r="91" s="18" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A91" s="159">
+      <c r="A91" s="158">
         <v>30310001</v>
       </c>
-      <c r="B91" s="160">
+      <c r="B91" s="159">
         <v>103100</v>
       </c>
-      <c r="C91" s="160" t="s">
+      <c r="C91" s="159" t="s">
         <v>197</v>
       </c>
-      <c r="D91" s="159">
+      <c r="D91" s="158">
         <v>303101</v>
       </c>
-      <c r="E91" s="161" t="s">
+      <c r="E91" s="160" t="s">
         <v>198</v>
       </c>
-      <c r="F91" s="161" t="s">
+      <c r="F91" s="160" t="s">
         <v>199</v>
       </c>
-      <c r="G91" s="159">
+      <c r="G91" s="158">
         <v>2031001</v>
       </c>
-      <c r="H91" s="161" t="s">
-        <v>63</v>
-      </c>
-      <c r="I91" s="161"/>
-      <c r="J91" s="161"/>
-      <c r="K91" s="162">
+      <c r="H91" s="160" t="s">
+        <v>63</v>
+      </c>
+      <c r="I91" s="160"/>
+      <c r="J91" s="160"/>
+      <c r="K91" s="161">
         <v>10310005</v>
       </c>
-      <c r="L91" s="161" t="s">
+      <c r="L91" s="160" t="s">
         <v>200</v>
       </c>
-      <c r="M91" s="161"/>
-      <c r="N91" s="161"/>
-      <c r="O91" s="161"/>
-      <c r="P91" s="161"/>
-      <c r="Q91" s="163"/>
-      <c r="R91" s="164"/>
-      <c r="S91" s="164"/>
-      <c r="T91" s="165"/>
+      <c r="M91" s="160"/>
+      <c r="N91" s="160"/>
+      <c r="O91" s="160"/>
+      <c r="P91" s="160"/>
+      <c r="Q91" s="162"/>
+      <c r="R91" s="163"/>
+      <c r="S91" s="163"/>
+      <c r="T91" s="164"/>
     </row>
     <row r="92" s="18" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A92" s="159">
+      <c r="A92" s="158">
         <v>30310002</v>
       </c>
-      <c r="B92" s="160">
+      <c r="B92" s="159">
         <v>103100</v>
       </c>
-      <c r="C92" s="160" t="s">
+      <c r="C92" s="159" t="s">
         <v>197</v>
       </c>
-      <c r="D92" s="159">
+      <c r="D92" s="158">
         <v>303102</v>
       </c>
-      <c r="E92" s="161" t="s">
+      <c r="E92" s="160" t="s">
         <v>201</v>
       </c>
-      <c r="F92" s="161" t="s">
+      <c r="F92" s="160" t="s">
         <v>56</v>
       </c>
-      <c r="G92" s="159">
+      <c r="G92" s="158">
         <v>2031001</v>
       </c>
-      <c r="H92" s="161" t="s">
-        <v>63</v>
-      </c>
-      <c r="I92" s="161"/>
-      <c r="J92" s="161"/>
-      <c r="K92" s="162">
+      <c r="H92" s="160" t="s">
+        <v>63</v>
+      </c>
+      <c r="I92" s="160"/>
+      <c r="J92" s="160"/>
+      <c r="K92" s="161">
         <v>10310006</v>
       </c>
-      <c r="L92" s="161" t="s">
+      <c r="L92" s="160" t="s">
         <v>202</v>
       </c>
-      <c r="M92" s="161"/>
-      <c r="N92" s="161"/>
-      <c r="O92" s="161"/>
-      <c r="P92" s="161"/>
-      <c r="Q92" s="163"/>
-      <c r="R92" s="164"/>
-      <c r="S92" s="164"/>
-      <c r="T92" s="165"/>
+      <c r="M92" s="160"/>
+      <c r="N92" s="160"/>
+      <c r="O92" s="160"/>
+      <c r="P92" s="160"/>
+      <c r="Q92" s="162"/>
+      <c r="R92" s="163"/>
+      <c r="S92" s="163"/>
+      <c r="T92" s="164"/>
     </row>
     <row r="93" s="18" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A93" s="159">
+      <c r="A93" s="158">
         <v>30310003</v>
       </c>
-      <c r="B93" s="160">
+      <c r="B93" s="159">
         <v>103100</v>
       </c>
-      <c r="C93" s="160" t="s">
+      <c r="C93" s="159" t="s">
         <v>197</v>
       </c>
-      <c r="D93" s="159">
+      <c r="D93" s="158">
         <v>303103</v>
       </c>
-      <c r="E93" s="161" t="s">
+      <c r="E93" s="160" t="s">
         <v>123</v>
       </c>
-      <c r="F93" s="161" t="s">
+      <c r="F93" s="160" t="s">
         <v>124</v>
       </c>
-      <c r="G93" s="159">
+      <c r="G93" s="158">
         <v>2031001</v>
       </c>
-      <c r="H93" s="161" t="s">
-        <v>63</v>
-      </c>
-      <c r="I93" s="161" t="s">
+      <c r="H93" s="160" t="s">
+        <v>63</v>
+      </c>
+      <c r="I93" s="160" t="s">
         <v>83</v>
       </c>
-      <c r="J93" s="161" t="s">
+      <c r="J93" s="160" t="s">
         <v>203</v>
       </c>
-      <c r="K93" s="162" t="s">
+      <c r="K93" s="161" t="s">
         <v>204</v>
       </c>
-      <c r="L93" s="161" t="s">
+      <c r="L93" s="160" t="s">
         <v>205</v>
       </c>
-      <c r="M93" s="161"/>
-      <c r="N93" s="161"/>
-      <c r="O93" s="161"/>
-      <c r="P93" s="161"/>
-      <c r="Q93" s="163"/>
-      <c r="R93" s="164"/>
-      <c r="S93" s="164"/>
-      <c r="T93" s="165"/>
+      <c r="M93" s="160"/>
+      <c r="N93" s="160"/>
+      <c r="O93" s="160"/>
+      <c r="P93" s="160"/>
+      <c r="Q93" s="162"/>
+      <c r="R93" s="163"/>
+      <c r="S93" s="163"/>
+      <c r="T93" s="164"/>
     </row>
     <row r="94" s="18" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A94" s="159">
+      <c r="A94" s="158">
         <v>30310004</v>
       </c>
-      <c r="B94" s="160">
+      <c r="B94" s="159">
         <v>103100</v>
       </c>
-      <c r="C94" s="160" t="s">
+      <c r="C94" s="159" t="s">
         <v>197</v>
       </c>
-      <c r="D94" s="159">
+      <c r="D94" s="158">
         <v>303104</v>
       </c>
-      <c r="E94" s="161" t="s">
+      <c r="E94" s="160" t="s">
         <v>206</v>
       </c>
-      <c r="F94" s="161" t="s">
+      <c r="F94" s="160" t="s">
         <v>36</v>
       </c>
-      <c r="G94" s="159">
+      <c r="G94" s="158">
         <v>2031001</v>
       </c>
-      <c r="H94" s="161" t="s">
-        <v>63</v>
-      </c>
-      <c r="I94" s="161" t="s">
+      <c r="H94" s="160" t="s">
+        <v>63</v>
+      </c>
+      <c r="I94" s="160" t="s">
         <v>207</v>
       </c>
-      <c r="J94" s="161"/>
-      <c r="K94" s="162"/>
-      <c r="L94" s="161"/>
-      <c r="M94" s="161" t="s">
+      <c r="J94" s="160"/>
+      <c r="K94" s="161"/>
+      <c r="L94" s="160"/>
+      <c r="M94" s="160" t="s">
         <v>208</v>
       </c>
-      <c r="N94" s="161" t="s">
+      <c r="N94" s="160" t="s">
         <v>209</v>
       </c>
-      <c r="O94" s="161"/>
-      <c r="P94" s="161"/>
-      <c r="Q94" s="163" t="s">
+      <c r="O94" s="160"/>
+      <c r="P94" s="160"/>
+      <c r="Q94" s="162" t="s">
         <v>210</v>
       </c>
-      <c r="R94" s="164" t="s">
+      <c r="R94" s="163" t="s">
         <v>211</v>
       </c>
-      <c r="S94" s="164" t="s">
+      <c r="S94" s="163" t="s">
         <v>42</v>
       </c>
-      <c r="T94" s="165"/>
+      <c r="T94" s="164"/>
     </row>
     <row r="95" s="19" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A95" s="166">
+      <c r="A95" s="165">
         <v>30400001</v>
       </c>
-      <c r="B95" s="167">
+      <c r="B95" s="166">
         <v>104000</v>
       </c>
-      <c r="C95" s="167" t="s">
+      <c r="C95" s="166" t="s">
         <v>212</v>
       </c>
-      <c r="D95" s="166">
+      <c r="D95" s="165">
         <v>304001</v>
       </c>
-      <c r="E95" s="168" t="s">
+      <c r="E95" s="167" t="s">
         <v>213</v>
       </c>
-      <c r="F95" s="168" t="s">
+      <c r="F95" s="167" t="s">
         <v>214</v>
       </c>
-      <c r="G95" s="166">
+      <c r="G95" s="165">
         <v>2040001</v>
       </c>
-      <c r="H95" s="168" t="s">
-        <v>63</v>
-      </c>
-      <c r="I95" s="168" t="s">
+      <c r="H95" s="167" t="s">
+        <v>63</v>
+      </c>
+      <c r="I95" s="167" t="s">
         <v>83</v>
       </c>
-      <c r="J95" s="168"/>
-      <c r="K95" s="169" t="s">
+      <c r="J95" s="167"/>
+      <c r="K95" s="168" t="s">
         <v>215</v>
       </c>
-      <c r="L95" s="168" t="s">
+      <c r="L95" s="167" t="s">
         <v>193</v>
       </c>
-      <c r="M95" s="168"/>
-      <c r="N95" s="168"/>
-      <c r="O95" s="168"/>
-      <c r="P95" s="168"/>
-      <c r="Q95" s="170"/>
-      <c r="R95" s="171"/>
-      <c r="S95" s="171"/>
-      <c r="T95" s="172"/>
+      <c r="M95" s="167"/>
+      <c r="N95" s="167"/>
+      <c r="O95" s="167"/>
+      <c r="P95" s="167"/>
+      <c r="Q95" s="169"/>
+      <c r="R95" s="170"/>
+      <c r="S95" s="170"/>
+      <c r="T95" s="171"/>
     </row>
     <row r="96" s="20" customFormat="1" ht="16.5" spans="1:20">
       <c r="A96" s="80">
@@ -6887,7 +6866,7 @@
       <c r="B96" s="80">
         <v>103900</v>
       </c>
-      <c r="C96" s="173" t="s">
+      <c r="C96" s="80" t="s">
         <v>216</v>
       </c>
       <c r="D96" s="80">
@@ -6908,13 +6887,13 @@
       <c r="I96" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="K96" s="100">
+      <c r="K96" s="99">
         <v>10390001</v>
       </c>
       <c r="L96" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="T96" s="174"/>
+      <c r="T96" s="172"/>
     </row>
     <row r="97" s="20" customFormat="1" ht="16.5" spans="1:20">
       <c r="A97" s="80">
@@ -6923,7 +6902,7 @@
       <c r="B97" s="80">
         <v>103900</v>
       </c>
-      <c r="C97" s="173" t="s">
+      <c r="C97" s="80" t="s">
         <v>216</v>
       </c>
       <c r="D97" s="80">
@@ -6944,13 +6923,13 @@
       <c r="I97" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="K97" s="100">
+      <c r="K97" s="99">
         <v>10390001</v>
       </c>
       <c r="L97" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="T97" s="174"/>
+      <c r="T97" s="172"/>
     </row>
     <row r="98" s="20" customFormat="1" ht="16.5" spans="1:20">
       <c r="A98" s="80">
@@ -6959,7 +6938,7 @@
       <c r="B98" s="80">
         <v>103900</v>
       </c>
-      <c r="C98" s="173" t="s">
+      <c r="C98" s="80" t="s">
         <v>216</v>
       </c>
       <c r="D98" s="80">
@@ -6980,13 +6959,13 @@
       <c r="I98" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="K98" s="100">
+      <c r="K98" s="99">
         <v>10390001</v>
       </c>
       <c r="L98" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="T98" s="174"/>
+      <c r="T98" s="172"/>
     </row>
     <row r="99" s="20" customFormat="1" ht="16.5" spans="1:20">
       <c r="A99" s="80">
@@ -6995,7 +6974,7 @@
       <c r="B99" s="80">
         <v>103900</v>
       </c>
-      <c r="C99" s="173" t="s">
+      <c r="C99" s="80" t="s">
         <v>216</v>
       </c>
       <c r="D99" s="80">
@@ -7013,13 +6992,13 @@
       <c r="H99" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="K99" s="100">
+      <c r="K99" s="99">
         <v>10390002</v>
       </c>
       <c r="L99" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="T99" s="174"/>
+      <c r="T99" s="172"/>
     </row>
     <row r="100" s="21" customFormat="1" ht="16.5" spans="1:20">
       <c r="A100" s="56">
@@ -7028,7 +7007,7 @@
       <c r="B100" s="56">
         <v>101600</v>
       </c>
-      <c r="C100" s="175" t="s">
+      <c r="C100" s="56" t="s">
         <v>220</v>
       </c>
       <c r="D100" s="56">
@@ -7058,7 +7037,7 @@
       <c r="L100" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="T100" s="176"/>
+      <c r="T100" s="173"/>
     </row>
     <row r="101" s="21" customFormat="1" ht="16.5" spans="1:20">
       <c r="A101" s="56">
@@ -7067,7 +7046,7 @@
       <c r="B101" s="56">
         <v>101600</v>
       </c>
-      <c r="C101" s="175" t="s">
+      <c r="C101" s="56" t="s">
         <v>220</v>
       </c>
       <c r="D101" s="56">
@@ -7097,7 +7076,7 @@
       <c r="L101" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="T101" s="176"/>
+      <c r="T101" s="173"/>
     </row>
     <row r="102" s="21" customFormat="1" ht="16.5" spans="1:20">
       <c r="A102" s="56">
@@ -7106,7 +7085,7 @@
       <c r="B102" s="56">
         <v>101600</v>
       </c>
-      <c r="C102" s="175" t="s">
+      <c r="C102" s="56" t="s">
         <v>220</v>
       </c>
       <c r="D102" s="56">
@@ -7136,19 +7115,19 @@
       <c r="L102" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="T102" s="176"/>
+      <c r="T102" s="173"/>
     </row>
     <row r="103" s="22" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A103" s="177">
+      <c r="A103" s="174">
         <v>30150001</v>
       </c>
-      <c r="B103" s="177">
+      <c r="B103" s="174">
         <v>101500</v>
       </c>
-      <c r="C103" s="178" t="s">
+      <c r="C103" s="174" t="s">
         <v>226</v>
       </c>
-      <c r="D103" s="177">
+      <c r="D103" s="174">
         <v>301501</v>
       </c>
       <c r="E103" s="22" t="s">
@@ -7157,7 +7136,7 @@
       <c r="F103" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="G103" s="177">
+      <c r="G103" s="174">
         <v>2015002</v>
       </c>
       <c r="H103" s="22" t="s">
@@ -7166,25 +7145,25 @@
       <c r="I103" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="K103" s="179" t="s">
+      <c r="K103" s="175" t="s">
         <v>228</v>
       </c>
       <c r="L103" s="22" t="s">
         <v>229</v>
       </c>
-      <c r="T103" s="180"/>
+      <c r="T103" s="176"/>
     </row>
     <row r="104" s="22" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A104" s="177">
+      <c r="A104" s="174">
         <v>30150002</v>
       </c>
-      <c r="B104" s="177">
+      <c r="B104" s="174">
         <v>101500</v>
       </c>
-      <c r="C104" s="178" t="s">
+      <c r="C104" s="174" t="s">
         <v>226</v>
       </c>
-      <c r="D104" s="177">
+      <c r="D104" s="174">
         <v>301502</v>
       </c>
       <c r="E104" s="22" t="s">
@@ -7193,7 +7172,7 @@
       <c r="F104" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="G104" s="177">
+      <c r="G104" s="174">
         <v>2015001</v>
       </c>
       <c r="H104" s="22" t="s">
@@ -7205,25 +7184,25 @@
       <c r="J104" s="22" t="s">
         <v>231</v>
       </c>
-      <c r="K104" s="179">
+      <c r="K104" s="175">
         <v>10150030</v>
       </c>
       <c r="L104" s="22" t="s">
         <v>229</v>
       </c>
-      <c r="T104" s="180"/>
+      <c r="T104" s="176"/>
     </row>
     <row r="105" s="22" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A105" s="177">
+      <c r="A105" s="174">
         <v>30150003</v>
       </c>
-      <c r="B105" s="177">
+      <c r="B105" s="174">
         <v>101500</v>
       </c>
-      <c r="C105" s="178" t="s">
+      <c r="C105" s="174" t="s">
         <v>226</v>
       </c>
-      <c r="D105" s="177">
+      <c r="D105" s="174">
         <v>301503</v>
       </c>
       <c r="E105" s="22" t="s">
@@ -7232,7 +7211,7 @@
       <c r="F105" s="22" t="s">
         <v>214</v>
       </c>
-      <c r="G105" s="177">
+      <c r="G105" s="174">
         <v>2015001</v>
       </c>
       <c r="H105" s="22" t="s">
@@ -7241,13 +7220,13 @@
       <c r="I105" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="K105" s="179" t="s">
+      <c r="K105" s="175" t="s">
         <v>228</v>
       </c>
       <c r="L105" s="22" t="s">
         <v>229</v>
       </c>
-      <c r="T105" s="180"/>
+      <c r="T105" s="176"/>
     </row>
     <row r="106" s="23" customFormat="1" ht="16.5" spans="1:20">
       <c r="A106" s="74">
@@ -7277,13 +7256,13 @@
       <c r="I106" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="K106" s="181" t="s">
+      <c r="K106" s="177" t="s">
         <v>234</v>
       </c>
       <c r="L106" s="23" t="s">
         <v>235</v>
       </c>
-      <c r="T106" s="182"/>
+      <c r="T106" s="178"/>
     </row>
     <row r="107" s="23" customFormat="1" ht="16.5" spans="1:20">
       <c r="A107" s="74">
@@ -7313,13 +7292,13 @@
       <c r="I107" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="K107" s="181" t="s">
+      <c r="K107" s="177" t="s">
         <v>234</v>
       </c>
       <c r="L107" s="23" t="s">
         <v>235</v>
       </c>
-      <c r="T107" s="182"/>
+      <c r="T107" s="178"/>
     </row>
     <row r="108" s="23" customFormat="1" ht="16.5" spans="1:20">
       <c r="A108" s="74">
@@ -7349,25 +7328,25 @@
       <c r="I108" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="K108" s="181" t="s">
+      <c r="K108" s="177" t="s">
         <v>234</v>
       </c>
       <c r="L108" s="23" t="s">
         <v>235</v>
       </c>
-      <c r="T108" s="182"/>
+      <c r="T108" s="178"/>
     </row>
     <row r="109" s="24" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A109" s="183">
+      <c r="A109" s="179">
         <v>30500001</v>
       </c>
-      <c r="B109" s="183">
+      <c r="B109" s="179">
         <v>105000</v>
       </c>
-      <c r="C109" s="183" t="s">
+      <c r="C109" s="179" t="s">
         <v>236</v>
       </c>
-      <c r="D109" s="183">
+      <c r="D109" s="179">
         <v>305001</v>
       </c>
       <c r="E109" s="38" t="s">
@@ -7376,7 +7355,7 @@
       <c r="F109" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="G109" s="183">
+      <c r="G109" s="179">
         <v>2050001</v>
       </c>
       <c r="H109" s="38" t="s">
@@ -7402,16 +7381,16 @@
       <c r="T109" s="38"/>
     </row>
     <row r="110" s="24" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A110" s="183">
+      <c r="A110" s="179">
         <v>30500002</v>
       </c>
-      <c r="B110" s="183">
+      <c r="B110" s="179">
         <v>105000</v>
       </c>
-      <c r="C110" s="183" t="s">
+      <c r="C110" s="179" t="s">
         <v>236</v>
       </c>
-      <c r="D110" s="183">
+      <c r="D110" s="179">
         <v>305002</v>
       </c>
       <c r="E110" s="38" t="s">
@@ -7420,7 +7399,7 @@
       <c r="F110" s="38" t="s">
         <v>240</v>
       </c>
-      <c r="G110" s="183">
+      <c r="G110" s="179">
         <v>2050001</v>
       </c>
       <c r="H110" s="38" t="s">
@@ -7446,16 +7425,16 @@
       <c r="T110" s="38"/>
     </row>
     <row r="111" s="24" customFormat="1" ht="20.1" customHeight="1" spans="1:20">
-      <c r="A111" s="183">
+      <c r="A111" s="179">
         <v>30500003</v>
       </c>
-      <c r="B111" s="183">
+      <c r="B111" s="179">
         <v>105000</v>
       </c>
-      <c r="C111" s="183" t="s">
+      <c r="C111" s="179" t="s">
         <v>236</v>
       </c>
-      <c r="D111" s="183">
+      <c r="D111" s="179">
         <v>305003</v>
       </c>
       <c r="E111" s="38" t="s">
@@ -7464,7 +7443,7 @@
       <c r="F111" s="38" t="s">
         <v>242</v>
       </c>
-      <c r="G111" s="183">
+      <c r="G111" s="179">
         <v>2050001</v>
       </c>
       <c r="H111" s="38" t="s">
@@ -7490,118 +7469,118 @@
       <c r="T111" s="38"/>
     </row>
     <row r="112" s="25" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A112" s="184">
+      <c r="A112" s="180">
         <v>30510001</v>
       </c>
-      <c r="B112" s="184">
+      <c r="B112" s="180">
         <v>105100</v>
       </c>
-      <c r="C112" s="184" t="s">
+      <c r="C112" s="180" t="s">
         <v>243</v>
       </c>
-      <c r="D112" s="184">
+      <c r="D112" s="180">
         <v>305101</v>
       </c>
-      <c r="E112" s="185" t="s">
+      <c r="E112" s="181" t="s">
         <v>244</v>
       </c>
       <c r="F112" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="G112" s="184">
+      <c r="G112" s="180">
         <v>2051001</v>
       </c>
-      <c r="H112" s="185" t="s">
-        <v>63</v>
-      </c>
-      <c r="I112" s="185" t="s">
+      <c r="H112" s="181" t="s">
+        <v>63</v>
+      </c>
+      <c r="I112" s="181" t="s">
         <v>83</v>
       </c>
-      <c r="K112" s="186"/>
-      <c r="T112" s="187"/>
+      <c r="K112" s="182"/>
+      <c r="T112" s="183"/>
     </row>
     <row r="113" s="25" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A113" s="184">
+      <c r="A113" s="180">
         <v>30510002</v>
       </c>
-      <c r="B113" s="184">
+      <c r="B113" s="180">
         <v>105100</v>
       </c>
-      <c r="C113" s="184" t="s">
+      <c r="C113" s="180" t="s">
         <v>243</v>
       </c>
-      <c r="D113" s="184">
+      <c r="D113" s="180">
         <v>305102</v>
       </c>
-      <c r="E113" s="185" t="s">
+      <c r="E113" s="181" t="s">
         <v>245</v>
       </c>
       <c r="F113" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="G113" s="184">
+      <c r="G113" s="180">
         <v>2051001</v>
       </c>
-      <c r="H113" s="185" t="s">
-        <v>63</v>
-      </c>
-      <c r="I113" s="185" t="s">
+      <c r="H113" s="181" t="s">
+        <v>63</v>
+      </c>
+      <c r="I113" s="181" t="s">
         <v>83</v>
       </c>
-      <c r="K113" s="186"/>
-      <c r="T113" s="187"/>
+      <c r="K113" s="182"/>
+      <c r="T113" s="183"/>
     </row>
     <row r="114" s="25" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A114" s="184">
+      <c r="A114" s="180">
         <v>30510003</v>
       </c>
-      <c r="B114" s="184">
+      <c r="B114" s="180">
         <v>105100</v>
       </c>
-      <c r="C114" s="184" t="s">
+      <c r="C114" s="180" t="s">
         <v>243</v>
       </c>
-      <c r="D114" s="184">
+      <c r="D114" s="180">
         <v>305103</v>
       </c>
-      <c r="E114" s="185" t="s">
+      <c r="E114" s="181" t="s">
         <v>246</v>
       </c>
       <c r="F114" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="G114" s="184">
+      <c r="G114" s="180">
         <v>2051001</v>
       </c>
-      <c r="H114" s="185" t="s">
-        <v>63</v>
-      </c>
-      <c r="I114" s="185" t="s">
+      <c r="H114" s="181" t="s">
+        <v>63</v>
+      </c>
+      <c r="I114" s="181" t="s">
         <v>83</v>
       </c>
-      <c r="K114" s="186"/>
-      <c r="T114" s="187"/>
+      <c r="K114" s="182"/>
+      <c r="T114" s="183"/>
     </row>
     <row r="115" s="26" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A115" s="188">
+      <c r="A115" s="184">
         <v>30020001</v>
       </c>
-      <c r="B115" s="188">
+      <c r="B115" s="184">
         <v>400200</v>
       </c>
-      <c r="C115" s="188" t="s">
+      <c r="C115" s="184" t="s">
         <v>247</v>
       </c>
-      <c r="D115" s="188">
+      <c r="D115" s="184">
         <v>300201</v>
       </c>
-      <c r="E115" s="189" t="s">
+      <c r="E115" s="185" t="s">
         <v>248</v>
       </c>
       <c r="F115" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="G115" s="188">
+      <c r="G115" s="184">
         <v>2002001</v>
       </c>
       <c r="H115" s="26" t="s">
@@ -7610,34 +7589,34 @@
       <c r="I115" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="K115" s="190" t="s">
+      <c r="K115" s="186" t="s">
         <v>249</v>
       </c>
       <c r="L115" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="T115" s="191"/>
+      <c r="T115" s="187"/>
     </row>
     <row r="116" s="26" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A116" s="188">
+      <c r="A116" s="184">
         <v>30020002</v>
       </c>
-      <c r="B116" s="188">
+      <c r="B116" s="184">
         <v>400200</v>
       </c>
-      <c r="C116" s="188" t="s">
+      <c r="C116" s="184" t="s">
         <v>247</v>
       </c>
-      <c r="D116" s="188">
+      <c r="D116" s="184">
         <v>300202</v>
       </c>
-      <c r="E116" s="189" t="s">
+      <c r="E116" s="185" t="s">
         <v>110</v>
       </c>
       <c r="F116" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="G116" s="188">
+      <c r="G116" s="184">
         <v>2002001</v>
       </c>
       <c r="H116" s="26" t="s">
@@ -7646,34 +7625,34 @@
       <c r="I116" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="K116" s="190" t="s">
+      <c r="K116" s="186" t="s">
         <v>249</v>
       </c>
       <c r="L116" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="T116" s="191"/>
+      <c r="T116" s="187"/>
     </row>
     <row r="117" s="26" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A117" s="188">
+      <c r="A117" s="184">
         <v>30020003</v>
       </c>
-      <c r="B117" s="188">
+      <c r="B117" s="184">
         <v>400200</v>
       </c>
-      <c r="C117" s="188" t="s">
+      <c r="C117" s="184" t="s">
         <v>247</v>
       </c>
-      <c r="D117" s="188">
+      <c r="D117" s="184">
         <v>300203</v>
       </c>
-      <c r="E117" s="189" t="s">
+      <c r="E117" s="185" t="s">
         <v>130</v>
       </c>
       <c r="F117" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="G117" s="188">
+      <c r="G117" s="184">
         <v>2002001</v>
       </c>
       <c r="H117" s="26" t="s">
@@ -7682,121 +7661,121 @@
       <c r="I117" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="K117" s="190" t="s">
+      <c r="K117" s="186" t="s">
         <v>249</v>
       </c>
       <c r="L117" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="T117" s="191"/>
+      <c r="T117" s="187"/>
     </row>
     <row r="118" s="15" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A118" s="137">
+      <c r="A118" s="136">
         <v>30800001</v>
       </c>
-      <c r="B118" s="192">
+      <c r="B118" s="188">
         <v>100800</v>
       </c>
-      <c r="C118" s="192" t="s">
+      <c r="C118" s="188" t="s">
         <v>251</v>
       </c>
-      <c r="D118" s="192">
+      <c r="D118" s="188">
         <v>308001</v>
       </c>
-      <c r="E118" s="139" t="s">
+      <c r="E118" s="138" t="s">
         <v>110</v>
       </c>
       <c r="F118" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="G118" s="192">
+      <c r="G118" s="188">
         <v>2080001</v>
       </c>
-      <c r="H118" s="139" t="s">
-        <v>63</v>
-      </c>
-      <c r="I118" s="139" t="s">
+      <c r="H118" s="138" t="s">
+        <v>63</v>
+      </c>
+      <c r="I118" s="138" t="s">
         <v>83</v>
       </c>
-      <c r="K118" s="100" t="s">
+      <c r="K118" s="99" t="s">
         <v>252</v>
       </c>
       <c r="L118" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="T118" s="141"/>
+      <c r="T118" s="140"/>
     </row>
     <row r="119" s="15" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A119" s="137">
+      <c r="A119" s="136">
         <v>30800002</v>
       </c>
-      <c r="B119" s="192">
+      <c r="B119" s="188">
         <v>100800</v>
       </c>
-      <c r="C119" s="192" t="s">
+      <c r="C119" s="188" t="s">
         <v>251</v>
       </c>
-      <c r="D119" s="192">
+      <c r="D119" s="188">
         <v>308002</v>
       </c>
-      <c r="E119" s="139" t="s">
+      <c r="E119" s="138" t="s">
         <v>130</v>
       </c>
       <c r="F119" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G119" s="192">
+      <c r="G119" s="188">
         <v>2080001</v>
       </c>
-      <c r="H119" s="139" t="s">
-        <v>63</v>
-      </c>
-      <c r="I119" s="139" t="s">
+      <c r="H119" s="138" t="s">
+        <v>63</v>
+      </c>
+      <c r="I119" s="138" t="s">
         <v>83</v>
       </c>
-      <c r="K119" s="100" t="s">
+      <c r="K119" s="99" t="s">
         <v>252</v>
       </c>
       <c r="L119" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="T119" s="141"/>
+      <c r="T119" s="140"/>
     </row>
     <row r="120" s="15" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A120" s="137">
+      <c r="A120" s="136">
         <v>30800003</v>
       </c>
-      <c r="B120" s="192">
+      <c r="B120" s="188">
         <v>100800</v>
       </c>
-      <c r="C120" s="192" t="s">
+      <c r="C120" s="188" t="s">
         <v>251</v>
       </c>
-      <c r="D120" s="192">
+      <c r="D120" s="188">
         <v>308003</v>
       </c>
-      <c r="E120" s="139" t="s">
+      <c r="E120" s="138" t="s">
         <v>131</v>
       </c>
       <c r="F120" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="G120" s="192">
+      <c r="G120" s="188">
         <v>2080001</v>
       </c>
-      <c r="H120" s="139" t="s">
-        <v>63</v>
-      </c>
-      <c r="I120" s="139" t="s">
+      <c r="H120" s="138" t="s">
+        <v>63</v>
+      </c>
+      <c r="I120" s="138" t="s">
         <v>83</v>
       </c>
-      <c r="K120" s="100" t="s">
+      <c r="K120" s="99" t="s">
         <v>252</v>
       </c>
       <c r="L120" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="T120" s="141"/>
+      <c r="T120" s="140"/>
     </row>
     <row r="121" s="27" customFormat="1" ht="16.5" spans="1:20">
       <c r="A121" s="65">
@@ -7808,22 +7787,22 @@
       <c r="C121" s="65" t="s">
         <v>254</v>
       </c>
-      <c r="D121" s="193">
+      <c r="D121" s="189">
         <v>305301</v>
       </c>
       <c r="E121" s="67" t="s">
         <v>110</v>
       </c>
-      <c r="F121" s="194" t="s">
+      <c r="F121" s="190" t="s">
         <v>111</v>
       </c>
-      <c r="G121" s="193">
+      <c r="G121" s="189">
         <v>2053001</v>
       </c>
-      <c r="H121" s="195" t="s">
-        <v>63</v>
-      </c>
-      <c r="I121" s="195" t="s">
+      <c r="H121" s="191" t="s">
+        <v>63</v>
+      </c>
+      <c r="I121" s="191" t="s">
         <v>83</v>
       </c>
       <c r="K121" s="27" t="s">
@@ -7832,7 +7811,7 @@
       <c r="L121" s="67" t="s">
         <v>256</v>
       </c>
-      <c r="T121" s="196"/>
+      <c r="T121" s="192"/>
     </row>
     <row r="122" s="27" customFormat="1" ht="16.5" spans="1:20">
       <c r="A122" s="65">
@@ -7844,22 +7823,22 @@
       <c r="C122" s="65" t="s">
         <v>254</v>
       </c>
-      <c r="D122" s="193">
+      <c r="D122" s="189">
         <v>305302</v>
       </c>
       <c r="E122" s="67" t="s">
         <v>130</v>
       </c>
-      <c r="F122" s="194" t="s">
+      <c r="F122" s="190" t="s">
         <v>82</v>
       </c>
-      <c r="G122" s="193">
+      <c r="G122" s="189">
         <v>2053001</v>
       </c>
-      <c r="H122" s="195" t="s">
-        <v>63</v>
-      </c>
-      <c r="I122" s="195" t="s">
+      <c r="H122" s="191" t="s">
+        <v>63</v>
+      </c>
+      <c r="I122" s="191" t="s">
         <v>83</v>
       </c>
       <c r="K122" s="27" t="s">
@@ -7868,7 +7847,7 @@
       <c r="L122" s="67" t="s">
         <v>256</v>
       </c>
-      <c r="T122" s="196"/>
+      <c r="T122" s="192"/>
     </row>
     <row r="123" s="28" customFormat="1" ht="16.5" spans="1:20">
       <c r="A123" s="65">
@@ -7880,22 +7859,22 @@
       <c r="C123" s="65" t="s">
         <v>254</v>
       </c>
-      <c r="D123" s="193">
+      <c r="D123" s="189">
         <v>305303</v>
       </c>
       <c r="E123" s="67" t="s">
         <v>131</v>
       </c>
-      <c r="F123" s="194" t="s">
+      <c r="F123" s="190" t="s">
         <v>86</v>
       </c>
-      <c r="G123" s="193">
+      <c r="G123" s="189">
         <v>2053001</v>
       </c>
-      <c r="H123" s="195" t="s">
-        <v>63</v>
-      </c>
-      <c r="I123" s="195" t="s">
+      <c r="H123" s="191" t="s">
+        <v>63</v>
+      </c>
+      <c r="I123" s="191" t="s">
         <v>83</v>
       </c>
       <c r="K123" s="27" t="s">
@@ -7904,172 +7883,172 @@
       <c r="L123" s="67" t="s">
         <v>256</v>
       </c>
-      <c r="T123" s="197"/>
+      <c r="T123" s="193"/>
     </row>
     <row r="124" s="9" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A124" s="107">
+      <c r="A124" s="106">
         <v>30570001</v>
       </c>
-      <c r="B124" s="107">
+      <c r="B124" s="106">
         <v>105700</v>
       </c>
-      <c r="C124" s="107" t="s">
+      <c r="C124" s="106" t="s">
         <v>257</v>
       </c>
-      <c r="D124" s="198">
+      <c r="D124" s="194">
         <v>305701</v>
       </c>
-      <c r="E124" s="109" t="s">
+      <c r="E124" s="108" t="s">
         <v>110</v>
       </c>
-      <c r="F124" s="199" t="s">
+      <c r="F124" s="195" t="s">
         <v>111</v>
       </c>
-      <c r="G124" s="198">
+      <c r="G124" s="194">
         <v>2057001</v>
       </c>
-      <c r="H124" s="200" t="s">
-        <v>63</v>
-      </c>
-      <c r="I124" s="200" t="s">
+      <c r="H124" s="196" t="s">
+        <v>63</v>
+      </c>
+      <c r="I124" s="196" t="s">
         <v>83</v>
       </c>
-      <c r="K124" s="110" t="s">
+      <c r="K124" s="109" t="s">
         <v>258</v>
       </c>
-      <c r="L124" s="201" t="s">
+      <c r="L124" s="197" t="s">
         <v>259</v>
       </c>
-      <c r="T124" s="111"/>
+      <c r="T124" s="110"/>
     </row>
     <row r="125" s="9" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A125" s="107">
+      <c r="A125" s="106">
         <v>30570002</v>
       </c>
-      <c r="B125" s="107">
+      <c r="B125" s="106">
         <v>105700</v>
       </c>
-      <c r="C125" s="107" t="s">
+      <c r="C125" s="106" t="s">
         <v>257</v>
       </c>
-      <c r="D125" s="198">
+      <c r="D125" s="194">
         <v>305702</v>
       </c>
-      <c r="E125" s="109" t="s">
+      <c r="E125" s="108" t="s">
         <v>130</v>
       </c>
-      <c r="F125" s="199" t="s">
+      <c r="F125" s="195" t="s">
         <v>82</v>
       </c>
-      <c r="G125" s="198">
+      <c r="G125" s="194">
         <v>2057001</v>
       </c>
-      <c r="H125" s="200" t="s">
-        <v>63</v>
-      </c>
-      <c r="I125" s="200" t="s">
+      <c r="H125" s="196" t="s">
+        <v>63</v>
+      </c>
+      <c r="I125" s="196" t="s">
         <v>83</v>
       </c>
-      <c r="K125" s="110" t="s">
+      <c r="K125" s="109" t="s">
         <v>258</v>
       </c>
-      <c r="L125" s="201" t="s">
+      <c r="L125" s="197" t="s">
         <v>259</v>
       </c>
-      <c r="T125" s="111"/>
+      <c r="T125" s="110"/>
     </row>
     <row r="126" s="9" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A126" s="107">
+      <c r="A126" s="106">
         <v>30570003</v>
       </c>
-      <c r="B126" s="107">
+      <c r="B126" s="106">
         <v>105700</v>
       </c>
-      <c r="C126" s="107" t="s">
+      <c r="C126" s="106" t="s">
         <v>257</v>
       </c>
-      <c r="D126" s="198">
+      <c r="D126" s="194">
         <v>305703</v>
       </c>
-      <c r="E126" s="109" t="s">
+      <c r="E126" s="108" t="s">
         <v>131</v>
       </c>
-      <c r="F126" s="199" t="s">
+      <c r="F126" s="195" t="s">
         <v>86</v>
       </c>
-      <c r="G126" s="198">
+      <c r="G126" s="194">
         <v>2057001</v>
       </c>
-      <c r="H126" s="200" t="s">
-        <v>63</v>
-      </c>
-      <c r="I126" s="200" t="s">
+      <c r="H126" s="196" t="s">
+        <v>63</v>
+      </c>
+      <c r="I126" s="196" t="s">
         <v>83</v>
       </c>
-      <c r="K126" s="110" t="s">
+      <c r="K126" s="109" t="s">
         <v>258</v>
       </c>
-      <c r="L126" s="201" t="s">
+      <c r="L126" s="197" t="s">
         <v>259</v>
       </c>
-      <c r="T126" s="111"/>
+      <c r="T126" s="110"/>
     </row>
     <row r="127" s="29" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A127" s="202">
+      <c r="A127" s="198">
         <v>30580001</v>
       </c>
-      <c r="B127" s="202">
+      <c r="B127" s="198">
         <v>105800</v>
       </c>
-      <c r="C127" s="202" t="s">
+      <c r="C127" s="198" t="s">
         <v>260</v>
       </c>
-      <c r="D127" s="203">
+      <c r="D127" s="199">
         <v>305801</v>
       </c>
-      <c r="E127" s="204" t="s">
+      <c r="E127" s="200" t="s">
         <v>110</v>
       </c>
       <c r="F127" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="G127" s="203">
+      <c r="G127" s="199">
         <v>2058001</v>
       </c>
-      <c r="H127" s="205" t="s">
-        <v>63</v>
-      </c>
-      <c r="I127" s="205" t="s">
+      <c r="H127" s="201" t="s">
+        <v>63</v>
+      </c>
+      <c r="I127" s="201" t="s">
         <v>83</v>
       </c>
-      <c r="K127" s="206" t="s">
+      <c r="K127" s="202" t="s">
         <v>261</v>
       </c>
       <c r="L127" s="29" t="s">
         <v>262</v>
       </c>
-      <c r="T127" s="207"/>
+      <c r="T127" s="203"/>
     </row>
     <row r="128" s="30" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A128" s="208">
+      <c r="A128" s="204">
         <v>30480001</v>
       </c>
-      <c r="B128" s="208">
+      <c r="B128" s="204">
         <v>104800</v>
       </c>
-      <c r="C128" s="208" t="s">
+      <c r="C128" s="204" t="s">
         <v>263</v>
       </c>
-      <c r="D128" s="208">
+      <c r="D128" s="204">
         <v>304801</v>
       </c>
       <c r="E128" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="F128" s="209" t="s">
+      <c r="F128" s="205" t="s">
         <v>111</v>
       </c>
-      <c r="G128" s="210">
+      <c r="G128" s="204">
         <v>2048001</v>
       </c>
       <c r="H128" s="30" t="s">
@@ -8084,30 +8063,30 @@
       <c r="L128" s="30" t="s">
         <v>265</v>
       </c>
-      <c r="M128" s="211"/>
-      <c r="N128" s="211"/>
-      <c r="T128" s="212"/>
+      <c r="M128" s="206"/>
+      <c r="N128" s="206"/>
+      <c r="T128" s="207"/>
     </row>
     <row r="129" s="30" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A129" s="208">
+      <c r="A129" s="204">
         <v>30480002</v>
       </c>
-      <c r="B129" s="208">
+      <c r="B129" s="204">
         <v>104800</v>
       </c>
-      <c r="C129" s="208" t="s">
+      <c r="C129" s="204" t="s">
         <v>263</v>
       </c>
-      <c r="D129" s="208">
+      <c r="D129" s="204">
         <v>304802</v>
       </c>
       <c r="E129" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="F129" s="209" t="s">
+      <c r="F129" s="205" t="s">
         <v>82</v>
       </c>
-      <c r="G129" s="210">
+      <c r="G129" s="204">
         <v>2048001</v>
       </c>
       <c r="H129" s="30" t="s">
@@ -8122,28 +8101,28 @@
       <c r="L129" s="30" t="s">
         <v>265</v>
       </c>
-      <c r="T129" s="213"/>
+      <c r="T129" s="208"/>
     </row>
     <row r="130" s="30" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A130" s="208">
+      <c r="A130" s="204">
         <v>30480003</v>
       </c>
-      <c r="B130" s="208">
+      <c r="B130" s="204">
         <v>104800</v>
       </c>
-      <c r="C130" s="208" t="s">
+      <c r="C130" s="204" t="s">
         <v>263</v>
       </c>
-      <c r="D130" s="208">
+      <c r="D130" s="204">
         <v>304803</v>
       </c>
       <c r="E130" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="F130" s="209" t="s">
+      <c r="F130" s="205" t="s">
         <v>86</v>
       </c>
-      <c r="G130" s="210">
+      <c r="G130" s="204">
         <v>2048001</v>
       </c>
       <c r="H130" s="30" t="s">
@@ -8158,19 +8137,19 @@
       <c r="L130" s="30" t="s">
         <v>265</v>
       </c>
-      <c r="T130" s="213"/>
+      <c r="T130" s="208"/>
     </row>
     <row r="131" s="31" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A131" s="96">
+      <c r="A131" s="95">
         <v>30550101</v>
       </c>
-      <c r="B131" s="96">
+      <c r="B131" s="95">
         <v>105501</v>
       </c>
-      <c r="C131" s="96" t="s">
+      <c r="C131" s="95" t="s">
         <v>266</v>
       </c>
-      <c r="D131" s="96">
+      <c r="D131" s="95">
         <v>305501</v>
       </c>
       <c r="E131" s="31" t="s">
@@ -8179,23 +8158,23 @@
       <c r="F131" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="G131" s="96">
+      <c r="G131" s="95">
         <v>2055011</v>
       </c>
-      <c r="H131" s="214" t="s">
+      <c r="H131" s="209" t="s">
         <v>63</v>
       </c>
       <c r="I131" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="K131" s="98"/>
-      <c r="Q131" s="214" t="s">
+      <c r="K131" s="97"/>
+      <c r="Q131" s="209" t="s">
         <v>268</v>
       </c>
       <c r="S131" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="T131" s="215"/>
+      <c r="T131" s="210"/>
     </row>
     <row r="132" s="32" customFormat="1" ht="16.5" spans="1:20">
       <c r="A132" s="37">
@@ -8216,7 +8195,7 @@
       <c r="F132" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="G132" s="216">
+      <c r="G132" s="37">
         <v>2041001</v>
       </c>
       <c r="H132" s="32" t="s">
@@ -8228,24 +8207,24 @@
       <c r="K132" s="39" t="s">
         <v>270</v>
       </c>
-      <c r="L132" s="217" t="s">
+      <c r="L132" s="211" t="s">
         <v>271</v>
       </c>
-      <c r="M132" s="217"/>
-      <c r="N132" s="217"/>
+      <c r="M132" s="211"/>
+      <c r="N132" s="211"/>
       <c r="T132" s="44"/>
     </row>
     <row r="133" s="33" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A133" s="218">
+      <c r="A133" s="212">
         <v>30420001</v>
       </c>
-      <c r="B133" s="218">
+      <c r="B133" s="212">
         <v>104200</v>
       </c>
-      <c r="C133" s="218" t="s">
+      <c r="C133" s="212" t="s">
         <v>272</v>
       </c>
-      <c r="D133" s="218">
+      <c r="D133" s="212">
         <v>304201</v>
       </c>
       <c r="E133" s="33" t="s">
@@ -8254,7 +8233,7 @@
       <c r="F133" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="G133" s="219">
+      <c r="G133" s="212">
         <v>2042001</v>
       </c>
       <c r="H133" s="33" t="s">
@@ -8263,13 +8242,13 @@
       <c r="I133" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="K133" s="220" t="s">
+      <c r="K133" s="213" t="s">
         <v>273</v>
       </c>
       <c r="L133" s="33" t="s">
         <v>271</v>
       </c>
-      <c r="T133" s="221"/>
+      <c r="T133" s="214"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2">

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -1545,16 +1545,24 @@
     <font>
       <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -1568,15 +1576,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -7519,7 +7519,7 @@
         <v>111</v>
       </c>
       <c r="G113" s="180">
-        <v>2051001</v>
+        <v>2051002</v>
       </c>
       <c r="H113" s="181" t="s">
         <v>63</v>
@@ -7550,7 +7550,7 @@
         <v>111</v>
       </c>
       <c r="G114" s="180">
-        <v>2051001</v>
+        <v>2051003</v>
       </c>
       <c r="H114" s="181" t="s">
         <v>63</v>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="364">
   <si>
     <t>小游戏模式ID</t>
   </si>
@@ -1090,6 +1090,12 @@
   </si>
   <si>
     <t>10420001|10420003</t>
+  </si>
+  <si>
+    <t>德古拉黑暗财富</t>
+  </si>
+  <si>
+    <t>10190001|10190005|10190006|10190007</t>
   </si>
   <si>
     <t>typeID</t>
@@ -1550,12 +1556,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1568,13 +1568,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -1582,6 +1581,13 @@
     </font>
     <font>
       <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2871,7 +2877,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T133"/>
+  <dimension ref="A1:T136"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.125" style="34" customWidth="1"/>
@@ -7519,7 +7525,7 @@
         <v>111</v>
       </c>
       <c r="G113" s="180">
-        <v>2051001</v>
+        <v>2051002</v>
       </c>
       <c r="H113" s="181" t="s">
         <v>63</v>
@@ -7550,7 +7556,7 @@
         <v>111</v>
       </c>
       <c r="G114" s="180">
-        <v>2051001</v>
+        <v>2051003</v>
       </c>
       <c r="H114" s="181" t="s">
         <v>63</v>
@@ -8249,6 +8255,111 @@
         <v>271</v>
       </c>
       <c r="T133" s="214"/>
+    </row>
+    <row r="134" spans="1:20">
+      <c r="A134" s="34">
+        <v>30190001</v>
+      </c>
+      <c r="B134" s="34">
+        <v>101900</v>
+      </c>
+      <c r="C134" s="34" t="s">
+        <v>274</v>
+      </c>
+      <c r="D134" s="34">
+        <v>301901</v>
+      </c>
+      <c r="E134" t="s">
+        <v>130</v>
+      </c>
+      <c r="F134" t="s">
+        <v>82</v>
+      </c>
+      <c r="G134" s="34">
+        <v>2019001</v>
+      </c>
+      <c r="H134" t="s">
+        <v>63</v>
+      </c>
+      <c r="I134" t="s">
+        <v>83</v>
+      </c>
+      <c r="K134" s="35" t="s">
+        <v>275</v>
+      </c>
+      <c r="L134" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="135" spans="1:20">
+      <c r="A135" s="34">
+        <v>30190002</v>
+      </c>
+      <c r="B135" s="34">
+        <v>101900</v>
+      </c>
+      <c r="C135" s="34" t="s">
+        <v>274</v>
+      </c>
+      <c r="D135" s="34">
+        <v>301902</v>
+      </c>
+      <c r="E135" t="s">
+        <v>131</v>
+      </c>
+      <c r="F135" t="s">
+        <v>86</v>
+      </c>
+      <c r="G135" s="34">
+        <v>2019001</v>
+      </c>
+      <c r="H135" t="s">
+        <v>63</v>
+      </c>
+      <c r="I135" t="s">
+        <v>83</v>
+      </c>
+      <c r="K135" s="35" t="s">
+        <v>275</v>
+      </c>
+      <c r="L135" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="136" spans="1:20">
+      <c r="A136" s="34">
+        <v>30190003</v>
+      </c>
+      <c r="B136" s="34">
+        <v>101900</v>
+      </c>
+      <c r="C136" s="34" t="s">
+        <v>274</v>
+      </c>
+      <c r="D136" s="34">
+        <v>301903</v>
+      </c>
+      <c r="E136" t="s">
+        <v>224</v>
+      </c>
+      <c r="F136" t="s">
+        <v>225</v>
+      </c>
+      <c r="G136" s="34">
+        <v>2019001</v>
+      </c>
+      <c r="H136" t="s">
+        <v>63</v>
+      </c>
+      <c r="I136" t="s">
+        <v>83</v>
+      </c>
+      <c r="K136" s="35" t="s">
+        <v>275</v>
+      </c>
+      <c r="L136" t="s">
+        <v>265</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2">
@@ -8300,10 +8411,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -8311,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -8319,7 +8430,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:8">
@@ -8327,16 +8438,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:8">
@@ -8344,16 +8455,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:8">
@@ -8361,16 +8472,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:8">
@@ -8378,16 +8489,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:8">
@@ -8395,16 +8506,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:8">
@@ -8412,16 +8523,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:8">
@@ -8429,16 +8540,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:8">
@@ -8446,16 +8557,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:8">
@@ -8463,16 +8574,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F12" s="1">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:8">
@@ -8480,16 +8591,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F13" s="1">
         <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:8">
@@ -8497,16 +8608,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F14" s="1">
         <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:8">
@@ -8514,16 +8625,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F15" s="1">
         <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:8">
@@ -8531,16 +8642,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F16" s="1">
         <v>11</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:8">
@@ -8548,16 +8659,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F17" s="1">
         <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:8">
@@ -8565,7 +8676,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F18" s="1">
         <v>13</v>
@@ -8574,7 +8685,7 @@
         <v>188</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:8">
@@ -8582,16 +8693,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F19" s="1">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:8">
@@ -8599,16 +8710,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F20" s="1">
         <v>15</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:8">
@@ -8616,16 +8727,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F21" s="1">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:8">
@@ -8633,16 +8744,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F22" s="1">
         <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -8650,16 +8761,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F23" s="1">
         <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:8">
@@ -8667,16 +8778,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F24" s="1">
         <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -8684,7 +8795,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -8692,7 +8803,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -8700,7 +8811,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -8708,7 +8819,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -8716,7 +8827,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -8724,7 +8835,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -8732,7 +8843,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -8740,7 +8851,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -8748,7 +8859,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -8756,7 +8867,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -8764,7 +8875,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -8772,7 +8883,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -8780,7 +8891,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -8788,7 +8899,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -8796,7 +8907,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -8804,7 +8915,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -8812,7 +8923,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -8820,7 +8931,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -8828,7 +8939,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -8836,7 +8947,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -8844,7 +8955,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -8852,7 +8963,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -8860,7 +8971,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -846,7 +846,7 @@
     <t>免费游戏-免费旋转12局</t>
   </si>
   <si>
-    <t>10270001|10270004</t>
+    <t>10270007|10270004</t>
   </si>
   <si>
     <t>概率改出百搭符号+概率改出scatter符号</t>
@@ -1551,12 +1551,18 @@
     <font>
       <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1568,12 +1574,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>

--- a/slots/resources/sample/SpecialAuxiliary.xlsx
+++ b/slots/resources/sample/SpecialAuxiliary.xlsx
@@ -1035,7 +1035,7 @@
     <t>麻将胡了2</t>
   </si>
   <si>
-    <t>10530003|10530004|10530006</t>
+    <t>10530003|10530006</t>
   </si>
   <si>
     <t>概率改出SCATTER符号+第3轴必然出现金色符号+异形位置改为不中奖图案</t>
@@ -1044,10 +1044,10 @@
     <t>赏金大对决</t>
   </si>
   <si>
-    <t>10570001|10570004|10570006</t>
-  </si>
-  <si>
-    <t>概率改出SCATTER符号+概率改出金框符号+异形位置改为不中奖图案</t>
+    <t>10570001|10570004</t>
+  </si>
+  <si>
+    <t>概率改出SCATTER符号+概率改出金框符号</t>
   </si>
   <si>
     <t>极速糖果1000</t>
@@ -1551,18 +1551,18 @@
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1574,13 +1574,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1593,7 +1593,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1735,6 +1735,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1965,7 +1971,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1989,16 +1995,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2007,13 +2013,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2028,7 +2034,7 @@
     <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2037,24 +2043,24 @@
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -2076,13 +2082,13 @@
     <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2092,7 +2098,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="215">
+  <cellXfs count="219">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2129,6 +2135,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2196,18 +2203,18 @@
     <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2536,6 +2543,13 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2880,17 +2894,17 @@
   <dimension ref="A1:T136"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.125" style="34" customWidth="1"/>
-    <col min="2" max="2" width="9" style="34"/>
-    <col min="3" max="3" width="12" style="34" customWidth="1"/>
-    <col min="4" max="4" width="12.25" style="34" customWidth="1"/>
+    <col min="1" max="1" width="14.125" style="35" customWidth="1"/>
+    <col min="2" max="2" width="9" style="35"/>
+    <col min="3" max="3" width="12" style="35" customWidth="1"/>
+    <col min="4" max="4" width="12.25" style="35" customWidth="1"/>
     <col min="5" max="5" width="33.5" customWidth="1"/>
     <col min="6" max="6" width="15.125" customWidth="1"/>
-    <col min="7" max="7" width="9.875" style="34" customWidth="1"/>
+    <col min="7" max="7" width="9.875" style="35" customWidth="1"/>
     <col min="8" max="8" width="16.25" customWidth="1"/>
     <col min="9" max="9" width="29.375" customWidth="1"/>
     <col min="10" max="10" width="42.5" customWidth="1"/>
-    <col min="11" max="11" width="41.25" style="35" customWidth="1"/>
+    <col min="11" max="11" width="41.25" style="36" customWidth="1"/>
     <col min="12" max="12" width="45.25" customWidth="1"/>
     <col min="13" max="13" width="34.375" customWidth="1"/>
     <col min="14" max="14" width="7.875" customWidth="1"/>
@@ -2899,35 +2913,35 @@
     <col min="17" max="17" width="93.375" customWidth="1"/>
     <col min="18" max="18" width="22.625" customWidth="1"/>
     <col min="19" max="19" width="10.625" customWidth="1"/>
-    <col min="20" max="20" width="23.75" style="36" customWidth="1"/>
+    <col min="20" max="20" width="23.75" style="37" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:20">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37" t="s">
+      <c r="C1" s="38"/>
+      <c r="D1" s="38" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="32"/>
       <c r="F1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="37" t="s">
+      <c r="G1" s="38" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="32"/>
       <c r="I1" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="38" t="s">
+      <c r="J1" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="39" t="s">
+      <c r="K1" s="40" t="s">
         <v>7</v>
       </c>
       <c r="L1" s="32"/>
@@ -2944,42 +2958,42 @@
       <c r="Q1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="40" t="s">
+      <c r="R1" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>13</v>
       </c>
       <c r="T1"/>
     </row>
     <row r="2" ht="16.5" spans="1:20">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37" t="s">
+      <c r="C2" s="38"/>
+      <c r="D2" s="38" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="32"/>
       <c r="F2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="37" t="s">
+      <c r="G2" s="38" t="s">
         <v>14</v>
       </c>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="J2" s="40" t="s">
+      <c r="J2" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="42" t="s">
+      <c r="K2" s="43" t="s">
         <v>16</v>
       </c>
       <c r="L2" s="1"/>
-      <c r="M2" s="40" t="s">
+      <c r="M2" s="41" t="s">
         <v>15</v>
       </c>
       <c r="N2" s="32"/>
@@ -2989,48 +3003,48 @@
       <c r="P2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Q2" s="40" t="s">
+      <c r="Q2" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="R2" s="40" t="s">
+      <c r="R2" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="41" t="s">
+      <c r="S2" s="42" t="s">
         <v>20</v>
       </c>
       <c r="T2"/>
     </row>
     <row r="3" ht="16.5" spans="1:20">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43" t="s">
+      <c r="C3" s="44"/>
+      <c r="D3" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44" t="s">
+      <c r="E3" s="45"/>
+      <c r="F3" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="45" t="s">
+      <c r="G3" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="46" t="s">
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="47" t="s">
+      <c r="K3" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44" t="s">
+      <c r="L3" s="45"/>
+      <c r="M3" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="N3" s="44"/>
+      <c r="N3" s="45"/>
       <c r="O3" s="1" t="s">
         <v>29</v>
       </c>
@@ -3040,25 +3054,25 @@
       <c r="Q3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="R3" s="48" t="s">
+      <c r="R3" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="S3" s="49" t="s">
+      <c r="S3" s="50" t="s">
         <v>33</v>
       </c>
       <c r="T3"/>
     </row>
     <row r="4" ht="16.5" spans="1:20">
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
       <c r="E4" s="32"/>
       <c r="F4" s="32"/>
-      <c r="G4" s="37"/>
+      <c r="G4" s="38"/>
       <c r="H4" s="32"/>
       <c r="I4" s="32"/>
       <c r="J4" s="24"/>
-      <c r="K4" s="39"/>
+      <c r="K4" s="40"/>
       <c r="L4" s="32"/>
       <c r="M4" s="32"/>
       <c r="N4" s="32"/>
@@ -3070,199 +3084,199 @@
       <c r="T4"/>
     </row>
     <row r="5" ht="16.5" spans="1:20">
-      <c r="A5" s="50">
+      <c r="A5" s="51">
         <v>30010001</v>
       </c>
-      <c r="B5" s="51">
+      <c r="B5" s="52">
         <v>100100</v>
       </c>
-      <c r="C5" s="51" t="s">
+      <c r="C5" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="50">
+      <c r="D5" s="51">
         <v>31001</v>
       </c>
-      <c r="E5" s="52" t="s">
+      <c r="E5" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="52" t="s">
+      <c r="F5" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="50"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52" t="s">
+      <c r="G5" s="51"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="52"/>
-      <c r="K5" s="53"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="54"/>
       <c r="L5" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="M5" s="52" t="s">
+      <c r="M5" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="N5" s="52" t="s">
+      <c r="N5" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="52"/>
-      <c r="P5" s="52"/>
-      <c r="Q5" s="54" t="s">
+      <c r="O5" s="53"/>
+      <c r="P5" s="53"/>
+      <c r="Q5" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="R5" s="55"/>
-      <c r="S5" s="55" t="s">
+      <c r="R5" s="56"/>
+      <c r="S5" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="T5" s="36" t="s">
+      <c r="T5" s="37" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:20">
-      <c r="A6" s="50">
+      <c r="A6" s="51">
         <v>30010002</v>
       </c>
-      <c r="B6" s="51">
+      <c r="B6" s="52">
         <v>100100</v>
       </c>
-      <c r="C6" s="51" t="s">
+      <c r="C6" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="50">
+      <c r="D6" s="51">
         <v>31002</v>
       </c>
-      <c r="E6" s="52" t="s">
+      <c r="E6" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="52" t="s">
+      <c r="F6" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="50"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52" t="s">
+      <c r="G6" s="51"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="J6" s="52"/>
-      <c r="K6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="54"/>
       <c r="L6" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="M6" s="52" t="s">
+      <c r="M6" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="N6" s="52" t="s">
+      <c r="N6" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="O6" s="52"/>
-      <c r="P6" s="52"/>
-      <c r="Q6" s="54" t="s">
+      <c r="O6" s="53"/>
+      <c r="P6" s="53"/>
+      <c r="Q6" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="R6" s="55"/>
-      <c r="S6" s="55" t="s">
+      <c r="R6" s="56"/>
+      <c r="S6" s="56" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:20">
-      <c r="A7" s="50">
+      <c r="A7" s="51">
         <v>30010003</v>
       </c>
-      <c r="B7" s="51">
+      <c r="B7" s="52">
         <v>100100</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="C7" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="50">
+      <c r="D7" s="51">
         <v>31003</v>
       </c>
-      <c r="E7" s="52" t="s">
+      <c r="E7" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="52" t="s">
+      <c r="F7" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="50"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52" t="s">
+      <c r="G7" s="51"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53" t="s">
         <v>49</v>
       </c>
-      <c r="J7" s="52"/>
-      <c r="K7" s="53"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54"/>
       <c r="L7" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="M7" s="52" t="s">
+      <c r="M7" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="N7" s="52" t="s">
+      <c r="N7" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="O7" s="52"/>
-      <c r="P7" s="52"/>
-      <c r="Q7" s="54" t="s">
+      <c r="O7" s="53"/>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="R7" s="55"/>
-      <c r="S7" s="55" t="s">
+      <c r="R7" s="56"/>
+      <c r="S7" s="56" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:20">
-      <c r="A8" s="50">
+      <c r="A8" s="51">
         <v>30010004</v>
       </c>
-      <c r="B8" s="51">
+      <c r="B8" s="52">
         <v>100100</v>
       </c>
-      <c r="C8" s="51" t="s">
+      <c r="C8" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="50">
+      <c r="D8" s="51">
         <v>31004</v>
       </c>
-      <c r="E8" s="52" t="s">
+      <c r="E8" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="52" t="s">
+      <c r="F8" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="50"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52" t="s">
+      <c r="G8" s="51"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="52"/>
-      <c r="K8" s="53"/>
+      <c r="J8" s="53"/>
+      <c r="K8" s="54"/>
       <c r="L8" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="M8" s="52" t="s">
+      <c r="M8" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="N8" s="52" t="s">
+      <c r="N8" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="O8" s="52"/>
-      <c r="P8" s="52"/>
-      <c r="Q8" s="54" t="s">
+      <c r="O8" s="53"/>
+      <c r="P8" s="53"/>
+      <c r="Q8" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="R8" s="55"/>
-      <c r="S8" s="55" t="s">
+      <c r="R8" s="56"/>
+      <c r="S8" s="56" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:20">
-      <c r="A9" s="37">
+      <c r="A9" s="38">
         <v>30010005</v>
       </c>
-      <c r="B9" s="49">
+      <c r="B9" s="50">
         <v>100100</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="C9" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="37">
+      <c r="D9" s="38">
         <v>31101</v>
       </c>
       <c r="E9" s="32" t="s">
@@ -3271,13 +3285,13 @@
       <c r="F9" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="37"/>
+      <c r="G9" s="38"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32" t="s">
         <v>55</v>
       </c>
       <c r="J9" s="32"/>
-      <c r="K9" s="39"/>
+      <c r="K9" s="40"/>
       <c r="L9" s="32" t="s">
         <v>46</v>
       </c>
@@ -3294,16 +3308,16 @@
       <c r="S9" s="1"/>
     </row>
     <row r="10" ht="16.5" spans="1:20">
-      <c r="A10" s="56">
+      <c r="A10" s="57">
         <v>30010006</v>
       </c>
-      <c r="B10" s="57">
+      <c r="B10" s="58">
         <v>100100</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C10" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="56">
+      <c r="D10" s="57">
         <v>31102</v>
       </c>
       <c r="E10" s="21" t="s">
@@ -3312,13 +3326,13 @@
       <c r="F10" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="56"/>
+      <c r="G10" s="57"/>
       <c r="H10" s="21"/>
       <c r="I10" s="21" t="s">
         <v>59</v>
       </c>
       <c r="J10" s="21"/>
-      <c r="K10" s="58"/>
+      <c r="K10" s="59"/>
       <c r="L10" s="21" t="s">
         <v>46</v>
       </c>
@@ -3337,168 +3351,168 @@
       <c r="S10" s="32"/>
     </row>
     <row r="11" ht="16.5" spans="1:20">
-      <c r="A11" s="59">
+      <c r="A11" s="60">
         <v>30010007</v>
       </c>
-      <c r="B11" s="60">
+      <c r="B11" s="61">
         <v>100100</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="C11" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="61">
+      <c r="D11" s="62">
         <v>31201</v>
       </c>
-      <c r="E11" s="62" t="s">
+      <c r="E11" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="63" t="s">
+      <c r="F11" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="G11" s="59">
+      <c r="G11" s="60">
         <v>2001001</v>
       </c>
-      <c r="H11" s="63" t="s">
-        <v>63</v>
-      </c>
-      <c r="I11" s="63" t="s">
+      <c r="H11" s="64" t="s">
+        <v>63</v>
+      </c>
+      <c r="I11" s="64" t="s">
         <v>64</v>
       </c>
-      <c r="J11" s="63"/>
-      <c r="K11" s="64">
+      <c r="J11" s="64"/>
+      <c r="K11" s="65">
         <v>10010091</v>
       </c>
-      <c r="L11" s="63"/>
-      <c r="M11" s="63"/>
-      <c r="N11" s="63"/>
-      <c r="O11" s="63"/>
-      <c r="P11" s="63"/>
-      <c r="Q11" s="63"/>
+      <c r="L11" s="64"/>
+      <c r="M11" s="64"/>
+      <c r="N11" s="64"/>
+      <c r="O11" s="64"/>
+      <c r="P11" s="64"/>
+      <c r="Q11" s="64"/>
       <c r="R11" s="32"/>
       <c r="S11" s="32"/>
     </row>
     <row r="12" ht="16.5" spans="1:20">
-      <c r="A12" s="65">
+      <c r="A12" s="66">
         <v>30010008</v>
       </c>
-      <c r="B12" s="66">
+      <c r="B12" s="67">
         <v>100100</v>
       </c>
-      <c r="C12" s="51" t="s">
+      <c r="C12" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="61">
+      <c r="D12" s="62">
         <v>31202</v>
       </c>
-      <c r="E12" s="62" t="s">
+      <c r="E12" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="67" t="s">
+      <c r="F12" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="G12" s="65">
+      <c r="G12" s="66">
         <v>2001001</v>
       </c>
-      <c r="H12" s="67" t="s">
-        <v>63</v>
-      </c>
-      <c r="I12" s="67" t="s">
+      <c r="H12" s="68" t="s">
+        <v>63</v>
+      </c>
+      <c r="I12" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="J12" s="67"/>
-      <c r="K12" s="68" t="s">
+      <c r="J12" s="68"/>
+      <c r="K12" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="L12" s="67"/>
-      <c r="M12" s="67"/>
-      <c r="N12" s="67"/>
-      <c r="O12" s="67"/>
-      <c r="P12" s="67"/>
-      <c r="Q12" s="67"/>
+      <c r="L12" s="68"/>
+      <c r="M12" s="68"/>
+      <c r="N12" s="68"/>
+      <c r="O12" s="68"/>
+      <c r="P12" s="68"/>
+      <c r="Q12" s="68"/>
       <c r="R12" s="32"/>
       <c r="S12" s="32"/>
     </row>
     <row r="13" ht="16.5" spans="1:20">
-      <c r="A13" s="69">
+      <c r="A13" s="70">
         <v>30010009</v>
       </c>
-      <c r="B13" s="70">
+      <c r="B13" s="71">
         <v>100100</v>
       </c>
-      <c r="C13" s="51" t="s">
+      <c r="C13" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="61">
+      <c r="D13" s="62">
         <v>31203</v>
       </c>
-      <c r="E13" s="62" t="s">
+      <c r="E13" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="F13" s="71" t="s">
+      <c r="F13" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="G13" s="69">
+      <c r="G13" s="70">
         <v>2001001</v>
       </c>
-      <c r="H13" s="71" t="s">
-        <v>63</v>
-      </c>
-      <c r="I13" s="71" t="s">
+      <c r="H13" s="72" t="s">
+        <v>63</v>
+      </c>
+      <c r="I13" s="72" t="s">
         <v>69</v>
       </c>
-      <c r="J13" s="71"/>
-      <c r="K13" s="72" t="s">
+      <c r="J13" s="72"/>
+      <c r="K13" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="L13" s="71"/>
-      <c r="M13" s="71"/>
-      <c r="N13" s="71"/>
-      <c r="O13" s="71"/>
-      <c r="P13" s="71"/>
-      <c r="Q13" s="71"/>
+      <c r="L13" s="72"/>
+      <c r="M13" s="72"/>
+      <c r="N13" s="72"/>
+      <c r="O13" s="72"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="72"/>
       <c r="R13" s="32"/>
       <c r="S13" s="32"/>
     </row>
     <row r="14" ht="16.5" spans="1:20">
-      <c r="A14" s="61">
+      <c r="A14" s="62">
         <v>30010010</v>
       </c>
-      <c r="B14" s="73">
+      <c r="B14" s="74">
         <v>100100</v>
       </c>
-      <c r="C14" s="51" t="s">
+      <c r="C14" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="74">
+      <c r="D14" s="75">
         <v>31301</v>
       </c>
       <c r="E14" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="F14" s="62" t="s">
+      <c r="F14" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="G14" s="61"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62" t="s">
+      <c r="G14" s="62"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="63" t="s">
         <v>72</v>
       </c>
-      <c r="J14" s="62"/>
-      <c r="K14" s="75"/>
-      <c r="L14" s="62" t="s">
+      <c r="J14" s="63"/>
+      <c r="K14" s="76"/>
+      <c r="L14" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="M14" s="62" t="s">
+      <c r="M14" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="N14" s="62"/>
-      <c r="O14" s="62"/>
-      <c r="P14" s="62"/>
-      <c r="Q14" s="76" t="s">
+      <c r="N14" s="63"/>
+      <c r="O14" s="63"/>
+      <c r="P14" s="63"/>
+      <c r="Q14" s="77" t="s">
         <v>74</v>
       </c>
-      <c r="R14" s="77"/>
-      <c r="S14" s="77" t="s">
+      <c r="R14" s="78"/>
+      <c r="S14" s="78" t="s">
         <v>75</v>
       </c>
       <c r="T14" s="1" t="s">
@@ -3506,105 +3520,105 @@
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:20">
-      <c r="A15" s="69">
+      <c r="A15" s="70">
         <v>30010011</v>
       </c>
-      <c r="B15" s="70">
+      <c r="B15" s="71">
         <v>100100</v>
       </c>
-      <c r="C15" s="51" t="s">
+      <c r="C15" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="74">
+      <c r="D15" s="75">
         <v>31302</v>
       </c>
       <c r="E15" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="F15" s="71" t="s">
+      <c r="F15" s="72" t="s">
         <v>36</v>
       </c>
-      <c r="G15" s="69"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="71" t="s">
+      <c r="G15" s="70"/>
+      <c r="H15" s="72"/>
+      <c r="I15" s="72" t="s">
         <v>78</v>
       </c>
-      <c r="J15" s="71"/>
-      <c r="K15" s="72"/>
-      <c r="L15" s="71" t="s">
+      <c r="J15" s="72"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="M15" s="71" t="s">
+      <c r="M15" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="N15" s="71"/>
-      <c r="O15" s="71"/>
-      <c r="P15" s="71"/>
-      <c r="Q15" s="71"/>
+      <c r="N15" s="72"/>
+      <c r="O15" s="72"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
       <c r="R15" s="32"/>
       <c r="S15" s="32"/>
     </row>
     <row r="16" ht="16.5" spans="1:20">
-      <c r="A16" s="69">
+      <c r="A16" s="70">
         <v>30010012</v>
       </c>
-      <c r="B16" s="70">
+      <c r="B16" s="71">
         <v>100100</v>
       </c>
-      <c r="C16" s="51" t="s">
+      <c r="C16" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="74">
+      <c r="D16" s="75">
         <v>31303</v>
       </c>
       <c r="E16" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="F16" s="71" t="s">
+      <c r="F16" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="69">
+      <c r="G16" s="70">
         <v>2001001</v>
       </c>
-      <c r="H16" s="71" t="s">
-        <v>63</v>
-      </c>
-      <c r="I16" s="71" t="s">
+      <c r="H16" s="72" t="s">
+        <v>63</v>
+      </c>
+      <c r="I16" s="72" t="s">
         <v>69</v>
       </c>
-      <c r="J16" s="71"/>
-      <c r="K16" s="72" t="s">
+      <c r="J16" s="72"/>
+      <c r="K16" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="L16" s="71"/>
-      <c r="M16" s="71"/>
-      <c r="N16" s="71"/>
-      <c r="O16" s="71"/>
-      <c r="P16" s="71"/>
-      <c r="Q16" s="71"/>
+      <c r="L16" s="72"/>
+      <c r="M16" s="72"/>
+      <c r="N16" s="72"/>
+      <c r="O16" s="72"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
       <c r="R16" s="32"/>
       <c r="S16" s="32"/>
     </row>
     <row r="17" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A17" s="37">
+      <c r="A17" s="38">
         <v>30070001</v>
       </c>
-      <c r="B17" s="34">
+      <c r="B17" s="35">
         <v>100700</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="59">
+      <c r="D17" s="60">
         <v>34001</v>
       </c>
-      <c r="E17" s="63" t="s">
+      <c r="E17" s="64" t="s">
         <v>81</v>
       </c>
-      <c r="F17" s="63" t="s">
+      <c r="F17" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="G17" s="49">
+      <c r="G17" s="50">
         <v>2007001</v>
       </c>
       <c r="H17" s="32" t="s">
@@ -3613,30 +3627,30 @@
       <c r="I17" t="s">
         <v>83</v>
       </c>
-      <c r="K17" s="35" t="s">
+      <c r="K17" s="36" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="18" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A18" s="37">
+      <c r="A18" s="38">
         <v>30070002</v>
       </c>
-      <c r="B18" s="34">
+      <c r="B18" s="35">
         <v>100700</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="D18" s="59">
+      <c r="D18" s="60">
         <v>34002</v>
       </c>
-      <c r="E18" s="63" t="s">
+      <c r="E18" s="64" t="s">
         <v>85</v>
       </c>
-      <c r="F18" s="63" t="s">
+      <c r="F18" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="G18" s="49">
+      <c r="G18" s="50">
         <v>2007001</v>
       </c>
       <c r="H18" s="32" t="s">
@@ -3645,231 +3659,231 @@
       <c r="I18" t="s">
         <v>83</v>
       </c>
-      <c r="K18" s="35" t="s">
+      <c r="K18" s="36" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="19" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A19" s="61">
+      <c r="A19" s="62">
         <v>30120001</v>
       </c>
-      <c r="B19" s="78">
+      <c r="B19" s="79">
         <v>101200</v>
       </c>
-      <c r="C19" s="78" t="s">
+      <c r="C19" s="79" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="61">
+      <c r="D19" s="62">
         <v>32001</v>
       </c>
-      <c r="E19" s="62" t="s">
+      <c r="E19" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="F19" s="62" t="s">
+      <c r="F19" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G19" s="73">
+      <c r="G19" s="74">
         <v>2012001</v>
       </c>
-      <c r="H19" s="62" t="s">
-        <v>63</v>
-      </c>
-      <c r="I19" s="62" t="s">
+      <c r="H19" s="63" t="s">
+        <v>63</v>
+      </c>
+      <c r="I19" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="J19" s="62" t="s">
+      <c r="J19" s="63" t="s">
         <v>89</v>
       </c>
-      <c r="K19" s="79">
+      <c r="K19" s="80">
         <v>10120041</v>
       </c>
     </row>
     <row r="20" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A20" s="61">
+      <c r="A20" s="62">
         <v>30120002</v>
       </c>
-      <c r="B20" s="78">
+      <c r="B20" s="79">
         <v>101200</v>
       </c>
-      <c r="C20" s="78" t="s">
+      <c r="C20" s="79" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="61">
+      <c r="D20" s="62">
         <v>32002</v>
       </c>
-      <c r="E20" s="62" t="s">
+      <c r="E20" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="F20" s="62" t="s">
+      <c r="F20" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G20" s="73">
+      <c r="G20" s="74">
         <v>2012001</v>
       </c>
-      <c r="H20" s="62" t="s">
-        <v>63</v>
-      </c>
-      <c r="I20" s="62" t="s">
+      <c r="H20" s="63" t="s">
+        <v>63</v>
+      </c>
+      <c r="I20" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="J20" s="62" t="s">
+      <c r="J20" s="63" t="s">
         <v>89</v>
       </c>
-      <c r="K20" s="79">
+      <c r="K20" s="80">
         <v>10120042</v>
       </c>
     </row>
     <row r="21" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A21" s="61">
+      <c r="A21" s="62">
         <v>30120003</v>
       </c>
-      <c r="B21" s="78">
+      <c r="B21" s="79">
         <v>101200</v>
       </c>
-      <c r="C21" s="78" t="s">
+      <c r="C21" s="79" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="61">
+      <c r="D21" s="62">
         <v>32003</v>
       </c>
-      <c r="E21" s="62" t="s">
+      <c r="E21" s="63" t="s">
         <v>91</v>
       </c>
-      <c r="F21" s="62" t="s">
+      <c r="F21" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G21" s="73">
+      <c r="G21" s="74">
         <v>2012001</v>
       </c>
-      <c r="H21" s="62" t="s">
-        <v>63</v>
-      </c>
-      <c r="I21" s="62" t="s">
+      <c r="H21" s="63" t="s">
+        <v>63</v>
+      </c>
+      <c r="I21" s="63" t="s">
         <v>91</v>
       </c>
-      <c r="J21" s="62" t="s">
+      <c r="J21" s="63" t="s">
         <v>89</v>
       </c>
-      <c r="K21" s="79">
+      <c r="K21" s="80">
         <v>10120043</v>
       </c>
     </row>
     <row r="22" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A22" s="61">
+      <c r="A22" s="62">
         <v>30120004</v>
       </c>
-      <c r="B22" s="78">
+      <c r="B22" s="79">
         <v>101200</v>
       </c>
-      <c r="C22" s="78" t="s">
+      <c r="C22" s="79" t="s">
         <v>87</v>
       </c>
-      <c r="D22" s="61">
+      <c r="D22" s="62">
         <v>32004</v>
       </c>
-      <c r="E22" s="62" t="s">
+      <c r="E22" s="63" t="s">
         <v>92</v>
       </c>
-      <c r="F22" s="62" t="s">
+      <c r="F22" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G22" s="73">
+      <c r="G22" s="74">
         <v>2012001</v>
       </c>
-      <c r="H22" s="62" t="s">
-        <v>63</v>
-      </c>
-      <c r="I22" s="62" t="s">
+      <c r="H22" s="63" t="s">
+        <v>63</v>
+      </c>
+      <c r="I22" s="63" t="s">
         <v>92</v>
       </c>
-      <c r="J22" s="62" t="s">
+      <c r="J22" s="63" t="s">
         <v>89</v>
       </c>
-      <c r="K22" s="79">
+      <c r="K22" s="80">
         <v>10120044</v>
       </c>
     </row>
     <row r="23" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A23" s="61">
+      <c r="A23" s="62">
         <v>30120005</v>
       </c>
-      <c r="B23" s="78">
+      <c r="B23" s="79">
         <v>101200</v>
       </c>
-      <c r="C23" s="78" t="s">
+      <c r="C23" s="79" t="s">
         <v>87</v>
       </c>
-      <c r="D23" s="61">
+      <c r="D23" s="62">
         <v>32005</v>
       </c>
-      <c r="E23" s="62" t="s">
+      <c r="E23" s="63" t="s">
         <v>92</v>
       </c>
-      <c r="F23" s="62" t="s">
+      <c r="F23" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G23" s="73">
+      <c r="G23" s="74">
         <v>2012001</v>
       </c>
-      <c r="H23" s="62" t="s">
-        <v>63</v>
-      </c>
-      <c r="I23" s="62" t="s">
+      <c r="H23" s="63" t="s">
+        <v>63</v>
+      </c>
+      <c r="I23" s="63" t="s">
         <v>92</v>
       </c>
-      <c r="J23" s="62" t="s">
+      <c r="J23" s="63" t="s">
         <v>89</v>
       </c>
-      <c r="K23" s="79">
+      <c r="K23" s="80">
         <v>10120045</v>
       </c>
     </row>
     <row r="24" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A24" s="61">
+      <c r="A24" s="62">
         <v>30120006</v>
       </c>
-      <c r="B24" s="78">
+      <c r="B24" s="79">
         <v>101200</v>
       </c>
-      <c r="C24" s="78" t="s">
+      <c r="C24" s="79" t="s">
         <v>87</v>
       </c>
-      <c r="D24" s="61">
+      <c r="D24" s="62">
         <v>32006</v>
       </c>
-      <c r="E24" s="62" t="s">
+      <c r="E24" s="63" t="s">
         <v>92</v>
       </c>
-      <c r="F24" s="62" t="s">
+      <c r="F24" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G24" s="73">
+      <c r="G24" s="74">
         <v>2012001</v>
       </c>
-      <c r="H24" s="62" t="s">
-        <v>63</v>
-      </c>
-      <c r="I24" s="62" t="s">
+      <c r="H24" s="63" t="s">
+        <v>63</v>
+      </c>
+      <c r="I24" s="63" t="s">
         <v>92</v>
       </c>
-      <c r="J24" s="62" t="s">
+      <c r="J24" s="63" t="s">
         <v>89</v>
       </c>
-      <c r="K24" s="79">
+      <c r="K24" s="80">
         <v>10120046</v>
       </c>
     </row>
     <row r="25" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A25" s="80">
+      <c r="A25" s="81">
         <v>30120011</v>
       </c>
-      <c r="B25" s="81">
+      <c r="B25" s="82">
         <v>101200</v>
       </c>
-      <c r="C25" s="81" t="s">
+      <c r="C25" s="82" t="s">
         <v>93</v>
       </c>
-      <c r="D25" s="61">
+      <c r="D25" s="62">
         <v>32101</v>
       </c>
       <c r="E25" s="20" t="s">
@@ -3878,7 +3892,7 @@
       <c r="F25" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="G25" s="82">
+      <c r="G25" s="83">
         <v>2012001</v>
       </c>
       <c r="H25" s="20" t="s">
@@ -3890,21 +3904,21 @@
       <c r="J25" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="K25" s="83">
+      <c r="K25" s="84">
         <v>10120041</v>
       </c>
     </row>
     <row r="26" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A26" s="80">
+      <c r="A26" s="81">
         <v>30120012</v>
       </c>
-      <c r="B26" s="81">
+      <c r="B26" s="82">
         <v>101200</v>
       </c>
-      <c r="C26" s="81" t="s">
+      <c r="C26" s="82" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="61">
+      <c r="D26" s="62">
         <v>32102</v>
       </c>
       <c r="E26" s="20" t="s">
@@ -3913,7 +3927,7 @@
       <c r="F26" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="G26" s="82">
+      <c r="G26" s="83">
         <v>2012001</v>
       </c>
       <c r="H26" s="20" t="s">
@@ -3925,21 +3939,21 @@
       <c r="J26" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="K26" s="83">
+      <c r="K26" s="84">
         <v>10120042</v>
       </c>
     </row>
     <row r="27" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A27" s="80">
+      <c r="A27" s="81">
         <v>30120013</v>
       </c>
-      <c r="B27" s="81">
+      <c r="B27" s="82">
         <v>101200</v>
       </c>
-      <c r="C27" s="81" t="s">
+      <c r="C27" s="82" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="61">
+      <c r="D27" s="62">
         <v>32103</v>
       </c>
       <c r="E27" s="20" t="s">
@@ -3948,7 +3962,7 @@
       <c r="F27" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="G27" s="82">
+      <c r="G27" s="83">
         <v>2012001</v>
       </c>
       <c r="H27" s="20" t="s">
@@ -3960,21 +3974,21 @@
       <c r="J27" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="K27" s="83">
+      <c r="K27" s="84">
         <v>10120043</v>
       </c>
     </row>
     <row r="28" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A28" s="80">
+      <c r="A28" s="81">
         <v>30120014</v>
       </c>
-      <c r="B28" s="81">
+      <c r="B28" s="82">
         <v>101200</v>
       </c>
-      <c r="C28" s="81" t="s">
+      <c r="C28" s="82" t="s">
         <v>93</v>
       </c>
-      <c r="D28" s="61">
+      <c r="D28" s="62">
         <v>32104</v>
       </c>
       <c r="E28" s="20" t="s">
@@ -3983,7 +3997,7 @@
       <c r="F28" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="G28" s="82">
+      <c r="G28" s="83">
         <v>2012001</v>
       </c>
       <c r="H28" s="20" t="s">
@@ -3995,21 +4009,21 @@
       <c r="J28" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="K28" s="83">
+      <c r="K28" s="84">
         <v>10120044</v>
       </c>
     </row>
     <row r="29" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A29" s="80">
+      <c r="A29" s="81">
         <v>30120015</v>
       </c>
-      <c r="B29" s="81">
+      <c r="B29" s="82">
         <v>101200</v>
       </c>
-      <c r="C29" s="81" t="s">
+      <c r="C29" s="82" t="s">
         <v>93</v>
       </c>
-      <c r="D29" s="61">
+      <c r="D29" s="62">
         <v>32105</v>
       </c>
       <c r="E29" s="20" t="s">
@@ -4018,7 +4032,7 @@
       <c r="F29" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="G29" s="82">
+      <c r="G29" s="83">
         <v>2012001</v>
       </c>
       <c r="H29" s="20" t="s">
@@ -4030,21 +4044,21 @@
       <c r="J29" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="K29" s="83">
+      <c r="K29" s="84">
         <v>10120045</v>
       </c>
     </row>
     <row r="30" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A30" s="80">
+      <c r="A30" s="81">
         <v>30120016</v>
       </c>
-      <c r="B30" s="81">
+      <c r="B30" s="82">
         <v>101200</v>
       </c>
-      <c r="C30" s="81" t="s">
+      <c r="C30" s="82" t="s">
         <v>93</v>
       </c>
-      <c r="D30" s="61">
+      <c r="D30" s="62">
         <v>32106</v>
       </c>
       <c r="E30" s="20" t="s">
@@ -4053,7 +4067,7 @@
       <c r="F30" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="G30" s="82">
+      <c r="G30" s="83">
         <v>2012001</v>
       </c>
       <c r="H30" s="20" t="s">
@@ -4065,21 +4079,21 @@
       <c r="J30" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="K30" s="83">
+      <c r="K30" s="84">
         <v>10120046</v>
       </c>
     </row>
     <row r="31" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A31" s="74">
+      <c r="A31" s="75">
         <v>30120021</v>
       </c>
-      <c r="B31" s="77">
+      <c r="B31" s="78">
         <v>101200</v>
       </c>
-      <c r="C31" s="77" t="s">
+      <c r="C31" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="D31" s="74">
+      <c r="D31" s="75">
         <v>32201</v>
       </c>
       <c r="E31" s="23" t="s">
@@ -4088,7 +4102,7 @@
       <c r="F31" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="84">
+      <c r="G31" s="85">
         <v>2012001</v>
       </c>
       <c r="H31" s="23" t="s">
@@ -4098,21 +4112,21 @@
         <v>88</v>
       </c>
       <c r="J31" s="23"/>
-      <c r="K31" s="85">
+      <c r="K31" s="86">
         <v>10120041</v>
       </c>
     </row>
     <row r="32" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A32" s="74">
+      <c r="A32" s="75">
         <v>30120022</v>
       </c>
-      <c r="B32" s="77">
+      <c r="B32" s="78">
         <v>101200</v>
       </c>
-      <c r="C32" s="77" t="s">
+      <c r="C32" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="D32" s="74">
+      <c r="D32" s="75">
         <v>32202</v>
       </c>
       <c r="E32" s="23" t="s">
@@ -4121,7 +4135,7 @@
       <c r="F32" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="G32" s="84">
+      <c r="G32" s="85">
         <v>2012001</v>
       </c>
       <c r="H32" s="23" t="s">
@@ -4131,21 +4145,21 @@
         <v>90</v>
       </c>
       <c r="J32" s="23"/>
-      <c r="K32" s="85">
+      <c r="K32" s="86">
         <v>10120042</v>
       </c>
     </row>
     <row r="33" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A33" s="74">
+      <c r="A33" s="75">
         <v>30120023</v>
       </c>
-      <c r="B33" s="77">
+      <c r="B33" s="78">
         <v>101200</v>
       </c>
-      <c r="C33" s="77" t="s">
+      <c r="C33" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="D33" s="74">
+      <c r="D33" s="75">
         <v>32203</v>
       </c>
       <c r="E33" s="23" t="s">
@@ -4154,7 +4168,7 @@
       <c r="F33" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="G33" s="84">
+      <c r="G33" s="85">
         <v>2012001</v>
       </c>
       <c r="H33" s="23" t="s">
@@ -4164,21 +4178,21 @@
         <v>91</v>
       </c>
       <c r="J33" s="23"/>
-      <c r="K33" s="85">
+      <c r="K33" s="86">
         <v>10120043</v>
       </c>
     </row>
     <row r="34" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A34" s="74">
+      <c r="A34" s="75">
         <v>30120024</v>
       </c>
-      <c r="B34" s="77">
+      <c r="B34" s="78">
         <v>101200</v>
       </c>
-      <c r="C34" s="77" t="s">
+      <c r="C34" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="D34" s="74">
+      <c r="D34" s="75">
         <v>32204</v>
       </c>
       <c r="E34" s="23" t="s">
@@ -4187,7 +4201,7 @@
       <c r="F34" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="G34" s="84">
+      <c r="G34" s="85">
         <v>2012001</v>
       </c>
       <c r="H34" s="23" t="s">
@@ -4197,21 +4211,21 @@
         <v>92</v>
       </c>
       <c r="J34" s="23"/>
-      <c r="K34" s="85">
+      <c r="K34" s="86">
         <v>10120044</v>
       </c>
     </row>
     <row r="35" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A35" s="74">
+      <c r="A35" s="75">
         <v>30120025</v>
       </c>
-      <c r="B35" s="77">
+      <c r="B35" s="78">
         <v>101200</v>
       </c>
-      <c r="C35" s="77" t="s">
+      <c r="C35" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="D35" s="74">
+      <c r="D35" s="75">
         <v>32205</v>
       </c>
       <c r="E35" s="23" t="s">
@@ -4220,7 +4234,7 @@
       <c r="F35" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="G35" s="84">
+      <c r="G35" s="85">
         <v>2012001</v>
       </c>
       <c r="H35" s="23" t="s">
@@ -4230,21 +4244,21 @@
         <v>92</v>
       </c>
       <c r="J35" s="23"/>
-      <c r="K35" s="85">
+      <c r="K35" s="86">
         <v>10120045</v>
       </c>
     </row>
     <row r="36" s="5" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A36" s="74">
+      <c r="A36" s="75">
         <v>30120026</v>
       </c>
-      <c r="B36" s="77">
+      <c r="B36" s="78">
         <v>101200</v>
       </c>
-      <c r="C36" s="77" t="s">
+      <c r="C36" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="D36" s="74">
+      <c r="D36" s="75">
         <v>32206</v>
       </c>
       <c r="E36" s="23" t="s">
@@ -4253,7 +4267,7 @@
       <c r="F36" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="G36" s="84">
+      <c r="G36" s="85">
         <v>2012001</v>
       </c>
       <c r="H36" s="23" t="s">
@@ -4263,547 +4277,547 @@
         <v>92</v>
       </c>
       <c r="J36" s="23"/>
-      <c r="K36" s="85">
+      <c r="K36" s="86">
         <v>10120046</v>
       </c>
     </row>
     <row r="37" s="6" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A37" s="86">
+      <c r="A37" s="87">
         <v>30240001</v>
       </c>
-      <c r="B37" s="87">
+      <c r="B37" s="88">
         <v>102400</v>
       </c>
-      <c r="C37" s="87" t="s">
+      <c r="C37" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="D37" s="86">
+      <c r="D37" s="87">
         <v>32401</v>
       </c>
-      <c r="E37" s="88" t="s">
+      <c r="E37" s="89" t="s">
         <v>35</v>
       </c>
-      <c r="F37" s="88" t="s">
+      <c r="F37" s="89" t="s">
         <v>36</v>
       </c>
-      <c r="G37" s="86"/>
-      <c r="H37" s="88"/>
-      <c r="I37" s="88" t="s">
+      <c r="G37" s="87"/>
+      <c r="H37" s="89"/>
+      <c r="I37" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="J37" s="88"/>
-      <c r="K37" s="89"/>
-      <c r="L37" s="88" t="s">
+      <c r="J37" s="89"/>
+      <c r="K37" s="90"/>
+      <c r="L37" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="M37" s="88" t="s">
+      <c r="M37" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="N37" s="88" t="s">
+      <c r="N37" s="89" t="s">
         <v>40</v>
       </c>
-      <c r="O37" s="88"/>
-      <c r="P37" s="88"/>
-      <c r="Q37" s="90" t="s">
+      <c r="O37" s="89"/>
+      <c r="P37" s="89"/>
+      <c r="Q37" s="91" t="s">
         <v>41</v>
       </c>
-      <c r="R37" s="91"/>
-      <c r="S37" s="91" t="s">
+      <c r="R37" s="92"/>
+      <c r="S37" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="T37" s="92" t="s">
+      <c r="T37" s="93" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="38" s="6" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A38" s="86">
+      <c r="A38" s="87">
         <v>30240002</v>
       </c>
-      <c r="B38" s="87">
+      <c r="B38" s="88">
         <v>102400</v>
       </c>
-      <c r="C38" s="87" t="s">
+      <c r="C38" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="D38" s="86">
+      <c r="D38" s="87">
         <v>32402</v>
       </c>
-      <c r="E38" s="88" t="s">
+      <c r="E38" s="89" t="s">
         <v>44</v>
       </c>
-      <c r="F38" s="88" t="s">
+      <c r="F38" s="89" t="s">
         <v>36</v>
       </c>
-      <c r="G38" s="86"/>
-      <c r="H38" s="88"/>
-      <c r="I38" s="88" t="s">
+      <c r="G38" s="87"/>
+      <c r="H38" s="89"/>
+      <c r="I38" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="J38" s="88"/>
-      <c r="K38" s="89"/>
-      <c r="L38" s="88" t="s">
+      <c r="J38" s="89"/>
+      <c r="K38" s="90"/>
+      <c r="L38" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="M38" s="88" t="s">
+      <c r="M38" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="N38" s="88" t="s">
+      <c r="N38" s="89" t="s">
         <v>40</v>
       </c>
-      <c r="O38" s="88"/>
-      <c r="P38" s="88"/>
-      <c r="Q38" s="90" t="s">
+      <c r="O38" s="89"/>
+      <c r="P38" s="89"/>
+      <c r="Q38" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="R38" s="91"/>
-      <c r="S38" s="91" t="s">
+      <c r="R38" s="92"/>
+      <c r="S38" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="T38" s="92"/>
+      <c r="T38" s="93"/>
     </row>
     <row r="39" s="6" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A39" s="86">
+      <c r="A39" s="87">
         <v>30240003</v>
       </c>
-      <c r="B39" s="87">
+      <c r="B39" s="88">
         <v>102400</v>
       </c>
-      <c r="C39" s="87" t="s">
+      <c r="C39" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="D39" s="86">
+      <c r="D39" s="87">
         <v>32403</v>
       </c>
-      <c r="E39" s="88" t="s">
+      <c r="E39" s="89" t="s">
         <v>48</v>
       </c>
-      <c r="F39" s="88" t="s">
+      <c r="F39" s="89" t="s">
         <v>36</v>
       </c>
-      <c r="G39" s="86"/>
-      <c r="H39" s="88"/>
-      <c r="I39" s="88" t="s">
+      <c r="G39" s="87"/>
+      <c r="H39" s="89"/>
+      <c r="I39" s="89" t="s">
         <v>49</v>
       </c>
-      <c r="J39" s="88"/>
-      <c r="K39" s="89"/>
-      <c r="L39" s="88" t="s">
+      <c r="J39" s="89"/>
+      <c r="K39" s="90"/>
+      <c r="L39" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="M39" s="88" t="s">
+      <c r="M39" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="N39" s="88" t="s">
+      <c r="N39" s="89" t="s">
         <v>40</v>
       </c>
-      <c r="O39" s="88"/>
-      <c r="P39" s="88"/>
-      <c r="Q39" s="90" t="s">
+      <c r="O39" s="89"/>
+      <c r="P39" s="89"/>
+      <c r="Q39" s="91" t="s">
         <v>50</v>
       </c>
-      <c r="R39" s="91"/>
-      <c r="S39" s="91" t="s">
+      <c r="R39" s="92"/>
+      <c r="S39" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="T39" s="92"/>
+      <c r="T39" s="93"/>
     </row>
     <row r="40" s="6" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A40" s="86">
+      <c r="A40" s="87">
         <v>30240004</v>
       </c>
-      <c r="B40" s="87">
+      <c r="B40" s="88">
         <v>102400</v>
       </c>
-      <c r="C40" s="87" t="s">
+      <c r="C40" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="D40" s="86">
+      <c r="D40" s="87">
         <v>32404</v>
       </c>
-      <c r="E40" s="88" t="s">
+      <c r="E40" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="F40" s="88" t="s">
+      <c r="F40" s="89" t="s">
         <v>36</v>
       </c>
-      <c r="G40" s="86"/>
-      <c r="H40" s="88"/>
-      <c r="I40" s="88" t="s">
+      <c r="G40" s="87"/>
+      <c r="H40" s="89"/>
+      <c r="I40" s="89" t="s">
         <v>52</v>
       </c>
-      <c r="J40" s="88"/>
-      <c r="K40" s="89"/>
-      <c r="L40" s="88" t="s">
+      <c r="J40" s="89"/>
+      <c r="K40" s="90"/>
+      <c r="L40" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="M40" s="88" t="s">
+      <c r="M40" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="N40" s="88" t="s">
+      <c r="N40" s="89" t="s">
         <v>40</v>
       </c>
-      <c r="O40" s="88"/>
-      <c r="P40" s="88"/>
-      <c r="Q40" s="90" t="s">
+      <c r="O40" s="89"/>
+      <c r="P40" s="89"/>
+      <c r="Q40" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="R40" s="91"/>
-      <c r="S40" s="91" t="s">
+      <c r="R40" s="92"/>
+      <c r="S40" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="T40" s="92"/>
+      <c r="T40" s="93"/>
     </row>
     <row r="41" s="6" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A41" s="86">
+      <c r="A41" s="87">
         <v>30240005</v>
       </c>
-      <c r="B41" s="87">
+      <c r="B41" s="88">
         <v>102400</v>
       </c>
-      <c r="C41" s="87" t="s">
+      <c r="C41" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="86">
+      <c r="D41" s="87">
         <v>32411</v>
       </c>
-      <c r="E41" s="88" t="s">
+      <c r="E41" s="89" t="s">
         <v>54</v>
       </c>
-      <c r="F41" s="88" t="s">
+      <c r="F41" s="89" t="s">
         <v>36</v>
       </c>
-      <c r="G41" s="86"/>
-      <c r="H41" s="88"/>
-      <c r="I41" s="88" t="s">
+      <c r="G41" s="87"/>
+      <c r="H41" s="89"/>
+      <c r="I41" s="89" t="s">
         <v>55</v>
       </c>
-      <c r="J41" s="88"/>
-      <c r="K41" s="89"/>
-      <c r="L41" s="88" t="s">
+      <c r="J41" s="89"/>
+      <c r="K41" s="90"/>
+      <c r="L41" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="M41" s="88" t="s">
+      <c r="M41" s="89" t="s">
         <v>56</v>
       </c>
-      <c r="N41" s="88"/>
-      <c r="O41" s="88" t="s">
+      <c r="N41" s="89"/>
+      <c r="O41" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="P41" s="88"/>
-      <c r="Q41" s="90"/>
-      <c r="R41" s="90"/>
-      <c r="S41" s="90"/>
-      <c r="T41" s="92"/>
+      <c r="P41" s="89"/>
+      <c r="Q41" s="91"/>
+      <c r="R41" s="91"/>
+      <c r="S41" s="91"/>
+      <c r="T41" s="93"/>
     </row>
     <row r="42" s="6" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A42" s="86">
+      <c r="A42" s="87">
         <v>30240006</v>
       </c>
-      <c r="B42" s="87">
+      <c r="B42" s="88">
         <v>102400</v>
       </c>
-      <c r="C42" s="87" t="s">
+      <c r="C42" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="D42" s="86">
+      <c r="D42" s="87">
         <v>32421</v>
       </c>
-      <c r="E42" s="88" t="s">
+      <c r="E42" s="89" t="s">
         <v>58</v>
       </c>
-      <c r="F42" s="88" t="s">
+      <c r="F42" s="89" t="s">
         <v>36</v>
       </c>
-      <c r="G42" s="86"/>
-      <c r="H42" s="88"/>
-      <c r="I42" s="88" t="s">
+      <c r="G42" s="87"/>
+      <c r="H42" s="89"/>
+      <c r="I42" s="89" t="s">
         <v>59</v>
       </c>
-      <c r="J42" s="88"/>
-      <c r="K42" s="89"/>
-      <c r="L42" s="88" t="s">
+      <c r="J42" s="89"/>
+      <c r="K42" s="90"/>
+      <c r="L42" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="M42" s="88" t="s">
+      <c r="M42" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="N42" s="88" t="s">
+      <c r="N42" s="89" t="s">
         <v>40</v>
       </c>
-      <c r="O42" s="88" t="s">
+      <c r="O42" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="P42" s="88"/>
-      <c r="Q42" s="88"/>
-      <c r="R42" s="88"/>
-      <c r="S42" s="88"/>
-      <c r="T42" s="92"/>
+      <c r="P42" s="89"/>
+      <c r="Q42" s="89"/>
+      <c r="R42" s="89"/>
+      <c r="S42" s="89"/>
+      <c r="T42" s="93"/>
     </row>
     <row r="43" s="6" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A43" s="86">
+      <c r="A43" s="87">
         <v>30240007</v>
       </c>
-      <c r="B43" s="87">
+      <c r="B43" s="88">
         <v>102400</v>
       </c>
-      <c r="C43" s="87" t="s">
+      <c r="C43" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="D43" s="86">
+      <c r="D43" s="87">
         <v>32431</v>
       </c>
-      <c r="E43" s="88" t="s">
+      <c r="E43" s="89" t="s">
         <v>61</v>
       </c>
-      <c r="F43" s="88" t="s">
+      <c r="F43" s="89" t="s">
         <v>62</v>
       </c>
-      <c r="G43" s="86">
+      <c r="G43" s="87">
         <v>2024001</v>
       </c>
-      <c r="H43" s="88" t="s">
-        <v>63</v>
-      </c>
-      <c r="I43" s="88" t="s">
+      <c r="H43" s="89" t="s">
+        <v>63</v>
+      </c>
+      <c r="I43" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="J43" s="88"/>
-      <c r="K43" s="89">
+      <c r="J43" s="89"/>
+      <c r="K43" s="90">
         <v>10240091</v>
       </c>
-      <c r="L43" s="88"/>
-      <c r="M43" s="88"/>
-      <c r="N43" s="88"/>
-      <c r="O43" s="88"/>
-      <c r="P43" s="88"/>
-      <c r="Q43" s="88"/>
-      <c r="R43" s="88"/>
-      <c r="S43" s="88"/>
-      <c r="T43" s="92"/>
+      <c r="L43" s="89"/>
+      <c r="M43" s="89"/>
+      <c r="N43" s="89"/>
+      <c r="O43" s="89"/>
+      <c r="P43" s="89"/>
+      <c r="Q43" s="89"/>
+      <c r="R43" s="89"/>
+      <c r="S43" s="89"/>
+      <c r="T43" s="93"/>
     </row>
     <row r="44" s="6" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A44" s="86">
+      <c r="A44" s="87">
         <v>30240008</v>
       </c>
-      <c r="B44" s="87">
+      <c r="B44" s="88">
         <v>102400</v>
       </c>
-      <c r="C44" s="87" t="s">
+      <c r="C44" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="D44" s="86">
+      <c r="D44" s="87">
         <v>32432</v>
       </c>
-      <c r="E44" s="88" t="s">
+      <c r="E44" s="89" t="s">
         <v>65</v>
       </c>
-      <c r="F44" s="88" t="s">
+      <c r="F44" s="89" t="s">
         <v>56</v>
       </c>
-      <c r="G44" s="86">
+      <c r="G44" s="87">
         <v>2024001</v>
       </c>
-      <c r="H44" s="88" t="s">
-        <v>63</v>
-      </c>
-      <c r="I44" s="88" t="s">
+      <c r="H44" s="89" t="s">
+        <v>63</v>
+      </c>
+      <c r="I44" s="89" t="s">
         <v>66</v>
       </c>
-      <c r="J44" s="88"/>
-      <c r="K44" s="93" t="s">
+      <c r="J44" s="89"/>
+      <c r="K44" s="94" t="s">
         <v>96</v>
       </c>
-      <c r="L44" s="88"/>
-      <c r="M44" s="88"/>
-      <c r="N44" s="88"/>
-      <c r="O44" s="88"/>
-      <c r="P44" s="88"/>
-      <c r="Q44" s="88"/>
-      <c r="R44" s="88"/>
-      <c r="S44" s="88"/>
-      <c r="T44" s="92"/>
+      <c r="L44" s="89"/>
+      <c r="M44" s="89"/>
+      <c r="N44" s="89"/>
+      <c r="O44" s="89"/>
+      <c r="P44" s="89"/>
+      <c r="Q44" s="89"/>
+      <c r="R44" s="89"/>
+      <c r="S44" s="89"/>
+      <c r="T44" s="93"/>
     </row>
     <row r="45" s="6" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A45" s="86">
+      <c r="A45" s="87">
         <v>30240009</v>
       </c>
-      <c r="B45" s="87">
+      <c r="B45" s="88">
         <v>102400</v>
       </c>
-      <c r="C45" s="87" t="s">
+      <c r="C45" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="D45" s="86">
+      <c r="D45" s="87">
         <v>32433</v>
       </c>
-      <c r="E45" s="88" t="s">
+      <c r="E45" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="F45" s="88" t="s">
+      <c r="F45" s="89" t="s">
         <v>56</v>
       </c>
-      <c r="G45" s="86">
+      <c r="G45" s="87">
         <v>2024001</v>
       </c>
-      <c r="H45" s="88" t="s">
-        <v>63</v>
-      </c>
-      <c r="I45" s="88" t="s">
+      <c r="H45" s="89" t="s">
+        <v>63</v>
+      </c>
+      <c r="I45" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="J45" s="88"/>
-      <c r="K45" s="89" t="s">
+      <c r="J45" s="89"/>
+      <c r="K45" s="90" t="s">
         <v>97</v>
       </c>
-      <c r="L45" s="88"/>
-      <c r="M45" s="88"/>
-      <c r="N45" s="88"/>
-      <c r="O45" s="88"/>
-      <c r="P45" s="88"/>
-      <c r="Q45" s="88"/>
-      <c r="R45" s="88"/>
-      <c r="S45" s="88"/>
-      <c r="T45" s="92"/>
+      <c r="L45" s="89"/>
+      <c r="M45" s="89"/>
+      <c r="N45" s="89"/>
+      <c r="O45" s="89"/>
+      <c r="P45" s="89"/>
+      <c r="Q45" s="89"/>
+      <c r="R45" s="89"/>
+      <c r="S45" s="89"/>
+      <c r="T45" s="93"/>
     </row>
     <row r="46" s="6" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A46" s="86">
+      <c r="A46" s="87">
         <v>30240010</v>
       </c>
-      <c r="B46" s="87">
+      <c r="B46" s="88">
         <v>102400</v>
       </c>
-      <c r="C46" s="87" t="s">
+      <c r="C46" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="D46" s="86">
+      <c r="D46" s="87">
         <v>32441</v>
       </c>
-      <c r="E46" s="88" t="s">
+      <c r="E46" s="89" t="s">
         <v>71</v>
       </c>
-      <c r="F46" s="88" t="s">
+      <c r="F46" s="89" t="s">
         <v>36</v>
       </c>
-      <c r="G46" s="86"/>
-      <c r="H46" s="88"/>
-      <c r="I46" s="88" t="s">
+      <c r="G46" s="87"/>
+      <c r="H46" s="89"/>
+      <c r="I46" s="89" t="s">
         <v>72</v>
       </c>
-      <c r="J46" s="88"/>
-      <c r="K46" s="93"/>
-      <c r="L46" s="88" t="s">
+      <c r="J46" s="89"/>
+      <c r="K46" s="94"/>
+      <c r="L46" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="M46" s="88" t="s">
+      <c r="M46" s="89" t="s">
         <v>73</v>
       </c>
-      <c r="N46" s="88"/>
-      <c r="O46" s="88"/>
-      <c r="P46" s="88"/>
-      <c r="Q46" s="90" t="s">
+      <c r="N46" s="89"/>
+      <c r="O46" s="89"/>
+      <c r="P46" s="89"/>
+      <c r="Q46" s="91" t="s">
         <v>74</v>
       </c>
-      <c r="R46" s="94"/>
-      <c r="S46" s="94" t="s">
+      <c r="R46" s="95"/>
+      <c r="S46" s="95" t="s">
         <v>75</v>
       </c>
-      <c r="T46" s="90" t="s">
+      <c r="T46" s="91" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="47" s="6" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A47" s="86">
+      <c r="A47" s="87">
         <v>30240011</v>
       </c>
-      <c r="B47" s="87">
+      <c r="B47" s="88">
         <v>102400</v>
       </c>
-      <c r="C47" s="87" t="s">
+      <c r="C47" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="D47" s="86">
+      <c r="D47" s="87">
         <v>32442</v>
       </c>
-      <c r="E47" s="88" t="s">
+      <c r="E47" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="F47" s="88" t="s">
+      <c r="F47" s="89" t="s">
         <v>36</v>
       </c>
-      <c r="G47" s="86"/>
-      <c r="H47" s="88"/>
-      <c r="I47" s="88" t="s">
+      <c r="G47" s="87"/>
+      <c r="H47" s="89"/>
+      <c r="I47" s="89" t="s">
         <v>78</v>
       </c>
-      <c r="J47" s="88"/>
-      <c r="K47" s="89"/>
-      <c r="L47" s="88" t="s">
+      <c r="J47" s="89"/>
+      <c r="K47" s="90"/>
+      <c r="L47" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="M47" s="88" t="s">
+      <c r="M47" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="N47" s="88"/>
-      <c r="O47" s="88"/>
-      <c r="P47" s="88"/>
-      <c r="Q47" s="88"/>
-      <c r="R47" s="88"/>
-      <c r="S47" s="88"/>
-      <c r="T47" s="92"/>
+      <c r="N47" s="89"/>
+      <c r="O47" s="89"/>
+      <c r="P47" s="89"/>
+      <c r="Q47" s="89"/>
+      <c r="R47" s="89"/>
+      <c r="S47" s="89"/>
+      <c r="T47" s="93"/>
     </row>
     <row r="48" s="6" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A48" s="86">
+      <c r="A48" s="87">
         <v>30240012</v>
       </c>
-      <c r="B48" s="87">
+      <c r="B48" s="88">
         <v>102400</v>
       </c>
-      <c r="C48" s="87" t="s">
+      <c r="C48" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="D48" s="86">
+      <c r="D48" s="87">
         <v>32443</v>
       </c>
-      <c r="E48" s="88" t="s">
+      <c r="E48" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="F48" s="88" t="s">
+      <c r="F48" s="89" t="s">
         <v>56</v>
       </c>
-      <c r="G48" s="86">
+      <c r="G48" s="87">
         <v>2024001</v>
       </c>
-      <c r="H48" s="88" t="s">
-        <v>63</v>
-      </c>
-      <c r="I48" s="88" t="s">
+      <c r="H48" s="89" t="s">
+        <v>63</v>
+      </c>
+      <c r="I48" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="J48" s="88"/>
-      <c r="K48" s="89" t="s">
+      <c r="J48" s="89"/>
+      <c r="K48" s="90" t="s">
         <v>97</v>
       </c>
-      <c r="L48" s="88"/>
-      <c r="M48" s="88"/>
-      <c r="N48" s="88"/>
-      <c r="O48" s="88"/>
-      <c r="P48" s="88"/>
-      <c r="Q48" s="88"/>
-      <c r="R48" s="88"/>
-      <c r="S48" s="88"/>
-      <c r="T48" s="92"/>
+      <c r="L48" s="89"/>
+      <c r="M48" s="89"/>
+      <c r="N48" s="89"/>
+      <c r="O48" s="89"/>
+      <c r="P48" s="89"/>
+      <c r="Q48" s="89"/>
+      <c r="R48" s="89"/>
+      <c r="S48" s="89"/>
+      <c r="T48" s="93"/>
     </row>
     <row r="49" s="7" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A49" s="95">
+      <c r="A49" s="96">
         <v>30170001</v>
       </c>
-      <c r="B49" s="96">
+      <c r="B49" s="97">
         <v>101700</v>
       </c>
-      <c r="C49" s="96" t="s">
+      <c r="C49" s="97" t="s">
         <v>98</v>
       </c>
-      <c r="D49" s="95">
+      <c r="D49" s="96">
         <v>301701</v>
       </c>
       <c r="E49" s="31" t="s">
@@ -4812,7 +4826,7 @@
       <c r="F49" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="G49" s="95">
+      <c r="G49" s="96">
         <v>2017001</v>
       </c>
       <c r="H49" s="31" t="s">
@@ -4822,7 +4836,7 @@
         <v>83</v>
       </c>
       <c r="J49" s="31"/>
-      <c r="K49" s="97" t="s">
+      <c r="K49" s="98" t="s">
         <v>100</v>
       </c>
       <c r="L49" s="31"/>
@@ -4833,19 +4847,19 @@
       <c r="Q49" s="31"/>
       <c r="R49" s="31"/>
       <c r="S49" s="31"/>
-      <c r="T49" s="98"/>
+      <c r="T49" s="99"/>
     </row>
     <row r="50" s="7" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A50" s="95">
+      <c r="A50" s="96">
         <v>30170002</v>
       </c>
-      <c r="B50" s="96">
+      <c r="B50" s="97">
         <v>101700</v>
       </c>
-      <c r="C50" s="96" t="s">
+      <c r="C50" s="97" t="s">
         <v>98</v>
       </c>
-      <c r="D50" s="95">
+      <c r="D50" s="96">
         <v>301702</v>
       </c>
       <c r="E50" s="31" t="s">
@@ -4854,7 +4868,7 @@
       <c r="F50" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="G50" s="95">
+      <c r="G50" s="96">
         <v>2017001</v>
       </c>
       <c r="H50" s="31" t="s">
@@ -4864,7 +4878,7 @@
         <v>83</v>
       </c>
       <c r="J50" s="31"/>
-      <c r="K50" s="97" t="s">
+      <c r="K50" s="98" t="s">
         <v>100</v>
       </c>
       <c r="L50" s="31"/>
@@ -4875,19 +4889,19 @@
       <c r="Q50" s="31"/>
       <c r="R50" s="31"/>
       <c r="S50" s="31"/>
-      <c r="T50" s="98"/>
+      <c r="T50" s="99"/>
     </row>
     <row r="51" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A51" s="80">
+      <c r="A51" s="81">
         <v>30220001</v>
       </c>
-      <c r="B51" s="82">
+      <c r="B51" s="83">
         <v>102200</v>
       </c>
-      <c r="C51" s="82" t="s">
+      <c r="C51" s="83" t="s">
         <v>102</v>
       </c>
-      <c r="D51" s="80">
+      <c r="D51" s="81">
         <v>302201</v>
       </c>
       <c r="E51" s="20" t="s">
@@ -4896,7 +4910,7 @@
       <c r="F51" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="G51" s="80">
+      <c r="G51" s="81">
         <v>2022001</v>
       </c>
       <c r="H51" s="20" t="s">
@@ -4904,7 +4918,7 @@
       </c>
       <c r="I51" s="20"/>
       <c r="J51" s="20"/>
-      <c r="K51" s="99" t="s">
+      <c r="K51" s="100" t="s">
         <v>105</v>
       </c>
       <c r="L51" s="20" t="s">
@@ -4917,19 +4931,19 @@
       <c r="Q51" s="20"/>
       <c r="R51" s="20"/>
       <c r="S51" s="20"/>
-      <c r="T51" s="100"/>
+      <c r="T51" s="101"/>
     </row>
     <row r="52" s="4" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A52" s="80">
+      <c r="A52" s="81">
         <v>30220002</v>
       </c>
-      <c r="B52" s="82">
+      <c r="B52" s="83">
         <v>102200</v>
       </c>
-      <c r="C52" s="82" t="s">
+      <c r="C52" s="83" t="s">
         <v>102</v>
       </c>
-      <c r="D52" s="80">
+      <c r="D52" s="81">
         <v>302202</v>
       </c>
       <c r="E52" s="20" t="s">
@@ -4938,7 +4952,7 @@
       <c r="F52" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="G52" s="80">
+      <c r="G52" s="81">
         <v>2022001</v>
       </c>
       <c r="H52" s="20" t="s">
@@ -4946,7 +4960,7 @@
       </c>
       <c r="I52" s="20"/>
       <c r="J52" s="20"/>
-      <c r="K52" s="99" t="s">
+      <c r="K52" s="100" t="s">
         <v>108</v>
       </c>
       <c r="L52" s="20" t="s">
@@ -4959,1923 +4973,1923 @@
       <c r="Q52" s="20"/>
       <c r="R52" s="20"/>
       <c r="S52" s="20"/>
-      <c r="T52" s="100"/>
+      <c r="T52" s="101"/>
     </row>
     <row r="53" s="8" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A53" s="101">
+      <c r="A53" s="102">
         <v>30210001</v>
       </c>
-      <c r="B53" s="102">
+      <c r="B53" s="103">
         <v>102100</v>
       </c>
-      <c r="C53" s="102" t="s">
+      <c r="C53" s="103" t="s">
         <v>109</v>
       </c>
-      <c r="D53" s="101">
+      <c r="D53" s="102">
         <v>302101</v>
       </c>
-      <c r="E53" s="103" t="s">
+      <c r="E53" s="104" t="s">
         <v>110</v>
       </c>
-      <c r="F53" s="103" t="s">
+      <c r="F53" s="104" t="s">
         <v>111</v>
       </c>
-      <c r="G53" s="101">
+      <c r="G53" s="102">
         <v>2021001</v>
       </c>
-      <c r="H53" s="103" t="s">
-        <v>63</v>
-      </c>
-      <c r="I53" s="103" t="s">
+      <c r="H53" s="104" t="s">
+        <v>63</v>
+      </c>
+      <c r="I53" s="104" t="s">
         <v>83</v>
       </c>
-      <c r="J53" s="103"/>
-      <c r="K53" s="104" t="s">
+      <c r="J53" s="104"/>
+      <c r="K53" s="105" t="s">
         <v>112</v>
       </c>
-      <c r="L53" s="103" t="s">
+      <c r="L53" s="104" t="s">
         <v>113</v>
       </c>
-      <c r="M53" s="103"/>
-      <c r="N53" s="103"/>
-      <c r="O53" s="103"/>
-      <c r="P53" s="103"/>
-      <c r="Q53" s="103"/>
-      <c r="R53" s="103"/>
-      <c r="S53" s="103"/>
-      <c r="T53" s="105"/>
+      <c r="M53" s="104"/>
+      <c r="N53" s="104"/>
+      <c r="O53" s="104"/>
+      <c r="P53" s="104"/>
+      <c r="Q53" s="104"/>
+      <c r="R53" s="104"/>
+      <c r="S53" s="104"/>
+      <c r="T53" s="106"/>
     </row>
     <row r="54" s="8" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A54" s="101">
+      <c r="A54" s="102">
         <v>30210002</v>
       </c>
-      <c r="B54" s="102">
+      <c r="B54" s="103">
         <v>102100</v>
       </c>
-      <c r="C54" s="102" t="s">
+      <c r="C54" s="103" t="s">
         <v>109</v>
       </c>
-      <c r="D54" s="101">
+      <c r="D54" s="102">
         <v>302102</v>
       </c>
-      <c r="E54" s="103" t="s">
+      <c r="E54" s="104" t="s">
         <v>114</v>
       </c>
-      <c r="F54" s="103" t="s">
+      <c r="F54" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="G54" s="101"/>
-      <c r="H54" s="103"/>
-      <c r="I54" s="103" t="s">
+      <c r="G54" s="102"/>
+      <c r="H54" s="104"/>
+      <c r="I54" s="104" t="s">
         <v>115</v>
       </c>
-      <c r="J54" s="103"/>
-      <c r="K54" s="104"/>
-      <c r="L54" s="103"/>
-      <c r="M54" s="103" t="s">
+      <c r="J54" s="104"/>
+      <c r="K54" s="105"/>
+      <c r="L54" s="104"/>
+      <c r="M54" s="104" t="s">
         <v>39</v>
       </c>
-      <c r="N54" s="103" t="s">
+      <c r="N54" s="104" t="s">
         <v>116</v>
       </c>
-      <c r="O54" s="103"/>
-      <c r="P54" s="103"/>
-      <c r="Q54" s="103" t="s">
+      <c r="O54" s="104"/>
+      <c r="P54" s="104"/>
+      <c r="Q54" s="104" t="s">
         <v>117</v>
       </c>
-      <c r="R54" s="103"/>
-      <c r="S54" s="103"/>
-      <c r="T54" s="105"/>
+      <c r="R54" s="104"/>
+      <c r="S54" s="104"/>
+      <c r="T54" s="106"/>
     </row>
     <row r="55" s="9" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A55" s="106">
+      <c r="A55" s="107">
         <v>30180001</v>
       </c>
-      <c r="B55" s="107">
+      <c r="B55" s="108">
         <v>101800</v>
       </c>
-      <c r="C55" s="107" t="s">
+      <c r="C55" s="108" t="s">
         <v>118</v>
       </c>
-      <c r="D55" s="106">
+      <c r="D55" s="107">
         <v>301801</v>
       </c>
-      <c r="E55" s="108" t="s">
+      <c r="E55" s="109" t="s">
         <v>83</v>
       </c>
-      <c r="F55" s="108" t="s">
+      <c r="F55" s="109" t="s">
         <v>119</v>
       </c>
-      <c r="G55" s="106">
+      <c r="G55" s="107">
         <v>2018002</v>
       </c>
-      <c r="H55" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="I55" s="108" t="s">
+      <c r="H55" s="109" t="s">
+        <v>63</v>
+      </c>
+      <c r="I55" s="109" t="s">
         <v>83</v>
       </c>
-      <c r="J55" s="108"/>
-      <c r="K55" s="109">
+      <c r="J55" s="109"/>
+      <c r="K55" s="110">
         <v>10180041</v>
       </c>
-      <c r="L55" s="108"/>
-      <c r="M55" s="108"/>
-      <c r="N55" s="108"/>
-      <c r="O55" s="108"/>
-      <c r="P55" s="108"/>
-      <c r="Q55" s="108"/>
-      <c r="R55" s="108"/>
-      <c r="S55" s="108"/>
-      <c r="T55" s="110"/>
+      <c r="L55" s="109"/>
+      <c r="M55" s="109"/>
+      <c r="N55" s="109"/>
+      <c r="O55" s="109"/>
+      <c r="P55" s="109"/>
+      <c r="Q55" s="109"/>
+      <c r="R55" s="109"/>
+      <c r="S55" s="109"/>
+      <c r="T55" s="111"/>
     </row>
     <row r="56" s="10" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A56" s="111">
+      <c r="A56" s="112">
         <v>30250001</v>
       </c>
-      <c r="B56" s="112">
+      <c r="B56" s="113">
         <v>102500</v>
       </c>
-      <c r="C56" s="112" t="s">
+      <c r="C56" s="113" t="s">
         <v>120</v>
       </c>
-      <c r="D56" s="111">
+      <c r="D56" s="112">
         <v>302501</v>
       </c>
-      <c r="E56" s="113" t="s">
+      <c r="E56" s="114" t="s">
         <v>110</v>
       </c>
-      <c r="F56" s="113" t="s">
+      <c r="F56" s="114" t="s">
         <v>111</v>
       </c>
-      <c r="G56" s="111">
+      <c r="G56" s="112">
         <v>2025001</v>
       </c>
-      <c r="H56" s="113" t="s">
-        <v>63</v>
-      </c>
-      <c r="I56" s="113" t="s">
+      <c r="H56" s="114" t="s">
+        <v>63</v>
+      </c>
+      <c r="I56" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="J56" s="113"/>
-      <c r="K56" s="114" t="s">
+      <c r="J56" s="114"/>
+      <c r="K56" s="115" t="s">
         <v>121</v>
       </c>
-      <c r="L56" s="113" t="s">
+      <c r="L56" s="114" t="s">
         <v>122</v>
       </c>
-      <c r="M56" s="113"/>
-      <c r="N56" s="113"/>
-      <c r="O56" s="113"/>
-      <c r="P56" s="113"/>
-      <c r="Q56" s="113"/>
-      <c r="R56" s="113"/>
-      <c r="S56" s="113"/>
-      <c r="T56" s="115"/>
+      <c r="M56" s="114"/>
+      <c r="N56" s="114"/>
+      <c r="O56" s="114"/>
+      <c r="P56" s="114"/>
+      <c r="Q56" s="114"/>
+      <c r="R56" s="114"/>
+      <c r="S56" s="114"/>
+      <c r="T56" s="116"/>
     </row>
     <row r="57" s="10" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A57" s="111">
+      <c r="A57" s="112">
         <v>30250002</v>
       </c>
-      <c r="B57" s="112">
+      <c r="B57" s="113">
         <v>102500</v>
       </c>
-      <c r="C57" s="112" t="s">
+      <c r="C57" s="113" t="s">
         <v>120</v>
       </c>
-      <c r="D57" s="111">
+      <c r="D57" s="112">
         <v>302502</v>
       </c>
-      <c r="E57" s="113" t="s">
+      <c r="E57" s="114" t="s">
         <v>123</v>
       </c>
-      <c r="F57" s="113" t="s">
+      <c r="F57" s="114" t="s">
         <v>124</v>
       </c>
-      <c r="G57" s="111">
+      <c r="G57" s="112">
         <v>2025001</v>
       </c>
-      <c r="H57" s="113" t="s">
-        <v>63</v>
-      </c>
-      <c r="I57" s="113" t="s">
+      <c r="H57" s="114" t="s">
+        <v>63</v>
+      </c>
+      <c r="I57" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="J57" s="113"/>
-      <c r="K57" s="114" t="s">
+      <c r="J57" s="114"/>
+      <c r="K57" s="115" t="s">
         <v>121</v>
       </c>
-      <c r="L57" s="113" t="s">
+      <c r="L57" s="114" t="s">
         <v>122</v>
       </c>
-      <c r="M57" s="113"/>
-      <c r="N57" s="113"/>
-      <c r="O57" s="113"/>
-      <c r="P57" s="113"/>
-      <c r="Q57" s="113"/>
-      <c r="R57" s="113"/>
-      <c r="S57" s="113"/>
-      <c r="T57" s="115"/>
+      <c r="M57" s="114"/>
+      <c r="N57" s="114"/>
+      <c r="O57" s="114"/>
+      <c r="P57" s="114"/>
+      <c r="Q57" s="114"/>
+      <c r="R57" s="114"/>
+      <c r="S57" s="114"/>
+      <c r="T57" s="116"/>
     </row>
     <row r="58" s="10" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A58" s="111">
+      <c r="A58" s="112">
         <v>30250003</v>
       </c>
-      <c r="B58" s="112">
+      <c r="B58" s="113">
         <v>102500</v>
       </c>
-      <c r="C58" s="112" t="s">
+      <c r="C58" s="113" t="s">
         <v>120</v>
       </c>
-      <c r="D58" s="111">
+      <c r="D58" s="112">
         <v>302503</v>
       </c>
-      <c r="E58" s="113" t="s">
+      <c r="E58" s="114" t="s">
         <v>125</v>
       </c>
-      <c r="F58" s="113" t="s">
+      <c r="F58" s="114" t="s">
         <v>126</v>
       </c>
-      <c r="G58" s="111">
+      <c r="G58" s="112">
         <v>2025001</v>
       </c>
-      <c r="H58" s="113" t="s">
-        <v>63</v>
-      </c>
-      <c r="I58" s="113" t="s">
+      <c r="H58" s="114" t="s">
+        <v>63</v>
+      </c>
+      <c r="I58" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="J58" s="113"/>
-      <c r="K58" s="114" t="s">
+      <c r="J58" s="114"/>
+      <c r="K58" s="115" t="s">
         <v>121</v>
       </c>
-      <c r="L58" s="113" t="s">
+      <c r="L58" s="114" t="s">
         <v>122</v>
       </c>
-      <c r="M58" s="113"/>
-      <c r="N58" s="113"/>
-      <c r="O58" s="113"/>
-      <c r="P58" s="113"/>
-      <c r="Q58" s="113"/>
-      <c r="R58" s="113"/>
-      <c r="S58" s="113"/>
-      <c r="T58" s="115"/>
+      <c r="M58" s="114"/>
+      <c r="N58" s="114"/>
+      <c r="O58" s="114"/>
+      <c r="P58" s="114"/>
+      <c r="Q58" s="114"/>
+      <c r="R58" s="114"/>
+      <c r="S58" s="114"/>
+      <c r="T58" s="116"/>
     </row>
     <row r="59" s="11" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A59" s="116">
+      <c r="A59" s="117">
         <v>30230001</v>
       </c>
-      <c r="B59" s="117">
+      <c r="B59" s="118">
         <v>102300</v>
       </c>
-      <c r="C59" s="117" t="s">
+      <c r="C59" s="118" t="s">
         <v>127</v>
       </c>
-      <c r="D59" s="116">
+      <c r="D59" s="117">
         <v>302301</v>
       </c>
-      <c r="E59" s="118" t="s">
+      <c r="E59" s="119" t="s">
         <v>110</v>
       </c>
-      <c r="F59" s="118" t="s">
+      <c r="F59" s="119" t="s">
         <v>111</v>
       </c>
-      <c r="G59" s="116">
+      <c r="G59" s="117">
         <v>2023001</v>
       </c>
-      <c r="H59" s="118" t="s">
-        <v>63</v>
-      </c>
-      <c r="I59" s="118" t="s">
+      <c r="H59" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="I59" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="J59" s="118"/>
-      <c r="K59" s="119" t="s">
+      <c r="J59" s="119"/>
+      <c r="K59" s="120" t="s">
         <v>128</v>
       </c>
-      <c r="L59" s="118" t="s">
+      <c r="L59" s="119" t="s">
         <v>129</v>
       </c>
-      <c r="M59" s="118"/>
-      <c r="N59" s="118"/>
-      <c r="O59" s="118"/>
-      <c r="P59" s="118"/>
-      <c r="Q59" s="118"/>
-      <c r="R59" s="118"/>
-      <c r="S59" s="118"/>
-      <c r="T59" s="120"/>
+      <c r="M59" s="119"/>
+      <c r="N59" s="119"/>
+      <c r="O59" s="119"/>
+      <c r="P59" s="119"/>
+      <c r="Q59" s="119"/>
+      <c r="R59" s="119"/>
+      <c r="S59" s="119"/>
+      <c r="T59" s="121"/>
     </row>
     <row r="60" s="11" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A60" s="116">
+      <c r="A60" s="117">
         <v>30230002</v>
       </c>
-      <c r="B60" s="117">
+      <c r="B60" s="118">
         <v>102300</v>
       </c>
-      <c r="C60" s="117" t="s">
+      <c r="C60" s="118" t="s">
         <v>127</v>
       </c>
-      <c r="D60" s="116">
+      <c r="D60" s="117">
         <v>302302</v>
       </c>
-      <c r="E60" s="118" t="s">
+      <c r="E60" s="119" t="s">
         <v>130</v>
       </c>
-      <c r="F60" s="118" t="s">
+      <c r="F60" s="119" t="s">
         <v>82</v>
       </c>
-      <c r="G60" s="116">
+      <c r="G60" s="117">
         <v>2023001</v>
       </c>
-      <c r="H60" s="118" t="s">
-        <v>63</v>
-      </c>
-      <c r="I60" s="118" t="s">
+      <c r="H60" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="I60" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="J60" s="118"/>
-      <c r="K60" s="119" t="s">
+      <c r="J60" s="119"/>
+      <c r="K60" s="120" t="s">
         <v>128</v>
       </c>
-      <c r="L60" s="118" t="s">
+      <c r="L60" s="119" t="s">
         <v>129</v>
       </c>
-      <c r="M60" s="118"/>
-      <c r="N60" s="118"/>
-      <c r="O60" s="118"/>
-      <c r="P60" s="118"/>
-      <c r="Q60" s="118"/>
-      <c r="R60" s="118"/>
-      <c r="S60" s="118"/>
-      <c r="T60" s="120"/>
+      <c r="M60" s="119"/>
+      <c r="N60" s="119"/>
+      <c r="O60" s="119"/>
+      <c r="P60" s="119"/>
+      <c r="Q60" s="119"/>
+      <c r="R60" s="119"/>
+      <c r="S60" s="119"/>
+      <c r="T60" s="121"/>
     </row>
     <row r="61" s="11" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A61" s="116">
+      <c r="A61" s="117">
         <v>30230003</v>
       </c>
-      <c r="B61" s="117">
+      <c r="B61" s="118">
         <v>102300</v>
       </c>
-      <c r="C61" s="117" t="s">
+      <c r="C61" s="118" t="s">
         <v>127</v>
       </c>
-      <c r="D61" s="116">
+      <c r="D61" s="117">
         <v>302303</v>
       </c>
-      <c r="E61" s="118" t="s">
+      <c r="E61" s="119" t="s">
         <v>131</v>
       </c>
-      <c r="F61" s="118" t="s">
+      <c r="F61" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="G61" s="116">
+      <c r="G61" s="117">
         <v>2023001</v>
       </c>
-      <c r="H61" s="118" t="s">
-        <v>63</v>
-      </c>
-      <c r="I61" s="118" t="s">
+      <c r="H61" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="I61" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="J61" s="118"/>
-      <c r="K61" s="119" t="s">
+      <c r="J61" s="119"/>
+      <c r="K61" s="120" t="s">
         <v>128</v>
       </c>
-      <c r="L61" s="118" t="s">
+      <c r="L61" s="119" t="s">
         <v>129</v>
       </c>
-      <c r="M61" s="118"/>
-      <c r="N61" s="118"/>
-      <c r="O61" s="118"/>
-      <c r="P61" s="118"/>
-      <c r="Q61" s="118"/>
-      <c r="R61" s="118"/>
-      <c r="S61" s="118"/>
-      <c r="T61" s="120"/>
+      <c r="M61" s="119"/>
+      <c r="N61" s="119"/>
+      <c r="O61" s="119"/>
+      <c r="P61" s="119"/>
+      <c r="Q61" s="119"/>
+      <c r="R61" s="119"/>
+      <c r="S61" s="119"/>
+      <c r="T61" s="121"/>
     </row>
     <row r="62" s="12" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A62" s="121">
+      <c r="A62" s="122">
         <v>30350001</v>
       </c>
-      <c r="B62" s="122">
+      <c r="B62" s="123">
         <v>103500</v>
       </c>
-      <c r="C62" s="122" t="s">
+      <c r="C62" s="123" t="s">
         <v>132</v>
       </c>
-      <c r="D62" s="121">
+      <c r="D62" s="122">
         <v>303501</v>
       </c>
-      <c r="E62" s="123" t="s">
+      <c r="E62" s="124" t="s">
         <v>133</v>
       </c>
-      <c r="F62" s="123" t="s">
+      <c r="F62" s="124" t="s">
         <v>62</v>
       </c>
-      <c r="G62" s="121">
+      <c r="G62" s="122">
         <v>2035002</v>
       </c>
-      <c r="H62" s="123" t="s">
-        <v>63</v>
-      </c>
-      <c r="I62" s="123" t="s">
+      <c r="H62" s="124" t="s">
+        <v>63</v>
+      </c>
+      <c r="I62" s="124" t="s">
         <v>134</v>
       </c>
-      <c r="J62" s="123"/>
-      <c r="K62" s="124" t="s">
+      <c r="J62" s="124"/>
+      <c r="K62" s="125" t="s">
         <v>135</v>
       </c>
-      <c r="L62" s="123" t="s">
+      <c r="L62" s="124" t="s">
         <v>136</v>
       </c>
-      <c r="M62" s="123"/>
-      <c r="N62" s="123"/>
-      <c r="O62" s="123"/>
-      <c r="P62" s="123"/>
-      <c r="Q62" s="123"/>
-      <c r="R62" s="123"/>
-      <c r="S62" s="123"/>
-      <c r="T62" s="125"/>
+      <c r="M62" s="124"/>
+      <c r="N62" s="124"/>
+      <c r="O62" s="124"/>
+      <c r="P62" s="124"/>
+      <c r="Q62" s="124"/>
+      <c r="R62" s="124"/>
+      <c r="S62" s="124"/>
+      <c r="T62" s="126"/>
     </row>
     <row r="63" s="12" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A63" s="121">
+      <c r="A63" s="122">
         <v>30350002</v>
       </c>
-      <c r="B63" s="122">
+      <c r="B63" s="123">
         <v>103500</v>
       </c>
-      <c r="C63" s="122" t="s">
+      <c r="C63" s="123" t="s">
         <v>132</v>
       </c>
-      <c r="D63" s="121">
+      <c r="D63" s="122">
         <v>303502</v>
       </c>
-      <c r="E63" s="123" t="s">
+      <c r="E63" s="124" t="s">
         <v>137</v>
       </c>
-      <c r="F63" s="123" t="s">
+      <c r="F63" s="124" t="s">
         <v>36</v>
       </c>
-      <c r="G63" s="121"/>
-      <c r="H63" s="123"/>
-      <c r="I63" s="123"/>
-      <c r="J63" s="123"/>
-      <c r="K63" s="124"/>
-      <c r="L63" s="123"/>
-      <c r="M63" s="123" t="s">
+      <c r="G63" s="122"/>
+      <c r="H63" s="124"/>
+      <c r="I63" s="124"/>
+      <c r="J63" s="124"/>
+      <c r="K63" s="125"/>
+      <c r="L63" s="124"/>
+      <c r="M63" s="124" t="s">
         <v>56</v>
       </c>
-      <c r="N63" s="123"/>
-      <c r="O63" s="123" t="s">
+      <c r="N63" s="124"/>
+      <c r="O63" s="124" t="s">
         <v>138</v>
       </c>
-      <c r="P63" s="123"/>
-      <c r="Q63" s="123"/>
-      <c r="R63" s="123"/>
-      <c r="S63" s="123"/>
-      <c r="T63" s="125"/>
+      <c r="P63" s="124"/>
+      <c r="Q63" s="124"/>
+      <c r="R63" s="124"/>
+      <c r="S63" s="124"/>
+      <c r="T63" s="126"/>
     </row>
     <row r="64" s="12" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A64" s="121">
+      <c r="A64" s="122">
         <v>30350101</v>
       </c>
-      <c r="B64" s="122">
+      <c r="B64" s="123">
         <v>103501</v>
       </c>
-      <c r="C64" s="122" t="s">
+      <c r="C64" s="123" t="s">
         <v>139</v>
       </c>
-      <c r="D64" s="121">
+      <c r="D64" s="122">
         <v>303503</v>
       </c>
-      <c r="E64" s="123" t="s">
+      <c r="E64" s="124" t="s">
         <v>133</v>
       </c>
-      <c r="F64" s="123" t="s">
+      <c r="F64" s="124" t="s">
         <v>62</v>
       </c>
-      <c r="G64" s="121">
+      <c r="G64" s="122">
         <v>2035012</v>
       </c>
-      <c r="H64" s="123" t="s">
-        <v>63</v>
-      </c>
-      <c r="I64" s="123" t="s">
+      <c r="H64" s="124" t="s">
+        <v>63</v>
+      </c>
+      <c r="I64" s="124" t="s">
         <v>134</v>
       </c>
-      <c r="J64" s="123"/>
-      <c r="K64" s="124" t="s">
+      <c r="J64" s="124"/>
+      <c r="K64" s="125" t="s">
         <v>140</v>
       </c>
-      <c r="L64" s="123" t="s">
+      <c r="L64" s="124" t="s">
         <v>136</v>
       </c>
-      <c r="M64" s="123"/>
-      <c r="N64" s="123"/>
-      <c r="O64" s="123"/>
-      <c r="P64" s="123"/>
-      <c r="Q64" s="123"/>
-      <c r="R64" s="123"/>
-      <c r="S64" s="123"/>
-      <c r="T64" s="125"/>
+      <c r="M64" s="124"/>
+      <c r="N64" s="124"/>
+      <c r="O64" s="124"/>
+      <c r="P64" s="124"/>
+      <c r="Q64" s="124"/>
+      <c r="R64" s="124"/>
+      <c r="S64" s="124"/>
+      <c r="T64" s="126"/>
     </row>
     <row r="65" s="12" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A65" s="121">
+      <c r="A65" s="122">
         <v>30350102</v>
       </c>
-      <c r="B65" s="122">
+      <c r="B65" s="123">
         <v>103501</v>
       </c>
-      <c r="C65" s="122" t="s">
+      <c r="C65" s="123" t="s">
         <v>139</v>
       </c>
-      <c r="D65" s="121">
+      <c r="D65" s="122">
         <v>303504</v>
       </c>
-      <c r="E65" s="123" t="s">
+      <c r="E65" s="124" t="s">
         <v>137</v>
       </c>
-      <c r="F65" s="123" t="s">
+      <c r="F65" s="124" t="s">
         <v>36</v>
       </c>
-      <c r="G65" s="121"/>
-      <c r="H65" s="123"/>
-      <c r="I65" s="123"/>
-      <c r="J65" s="123"/>
-      <c r="K65" s="124"/>
-      <c r="L65" s="123"/>
-      <c r="M65" s="123" t="s">
+      <c r="G65" s="122"/>
+      <c r="H65" s="124"/>
+      <c r="I65" s="124"/>
+      <c r="J65" s="124"/>
+      <c r="K65" s="125"/>
+      <c r="L65" s="124"/>
+      <c r="M65" s="124" t="s">
         <v>56</v>
       </c>
-      <c r="N65" s="123"/>
-      <c r="O65" s="123" t="s">
+      <c r="N65" s="124"/>
+      <c r="O65" s="124" t="s">
         <v>138</v>
       </c>
-      <c r="P65" s="123"/>
-      <c r="Q65" s="123"/>
-      <c r="R65" s="123"/>
-      <c r="S65" s="123"/>
-      <c r="T65" s="125"/>
+      <c r="P65" s="124"/>
+      <c r="Q65" s="124"/>
+      <c r="R65" s="124"/>
+      <c r="S65" s="124"/>
+      <c r="T65" s="126"/>
     </row>
     <row r="66" s="13" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A66" s="126">
+      <c r="A66" s="127">
         <v>30360001</v>
       </c>
-      <c r="B66" s="127">
+      <c r="B66" s="128">
         <v>103600</v>
       </c>
-      <c r="C66" s="127" t="s">
+      <c r="C66" s="128" t="s">
         <v>141</v>
       </c>
-      <c r="D66" s="126">
+      <c r="D66" s="127">
         <v>303601</v>
       </c>
-      <c r="E66" s="128" t="s">
+      <c r="E66" s="129" t="s">
         <v>142</v>
       </c>
-      <c r="F66" s="128" t="s">
+      <c r="F66" s="129" t="s">
         <v>111</v>
       </c>
-      <c r="G66" s="126">
+      <c r="G66" s="127">
         <v>2036002</v>
       </c>
-      <c r="H66" s="128" t="s">
-        <v>63</v>
-      </c>
-      <c r="I66" s="128" t="s">
+      <c r="H66" s="129" t="s">
+        <v>63</v>
+      </c>
+      <c r="I66" s="129" t="s">
         <v>142</v>
       </c>
-      <c r="J66" s="128"/>
-      <c r="K66" s="129">
+      <c r="J66" s="129"/>
+      <c r="K66" s="130">
         <v>10360005</v>
       </c>
-      <c r="L66" s="128" t="s">
+      <c r="L66" s="129" t="s">
         <v>143</v>
       </c>
-      <c r="M66" s="128"/>
-      <c r="N66" s="128"/>
-      <c r="O66" s="128"/>
-      <c r="P66" s="128"/>
-      <c r="Q66" s="128"/>
-      <c r="R66" s="128"/>
-      <c r="S66" s="128"/>
-      <c r="T66" s="130"/>
+      <c r="M66" s="129"/>
+      <c r="N66" s="129"/>
+      <c r="O66" s="129"/>
+      <c r="P66" s="129"/>
+      <c r="Q66" s="129"/>
+      <c r="R66" s="129"/>
+      <c r="S66" s="129"/>
+      <c r="T66" s="131"/>
     </row>
     <row r="67" s="14" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A67" s="131">
+      <c r="A67" s="132">
         <v>30280001</v>
       </c>
-      <c r="B67" s="132">
+      <c r="B67" s="133">
         <v>102800</v>
       </c>
-      <c r="C67" s="132" t="s">
+      <c r="C67" s="133" t="s">
         <v>144</v>
       </c>
-      <c r="D67" s="131">
+      <c r="D67" s="132">
         <v>302801</v>
       </c>
-      <c r="E67" s="133" t="s">
+      <c r="E67" s="134" t="s">
         <v>110</v>
       </c>
-      <c r="F67" s="133" t="s">
+      <c r="F67" s="134" t="s">
         <v>111</v>
       </c>
-      <c r="G67" s="131">
+      <c r="G67" s="132">
         <v>2028001</v>
       </c>
-      <c r="H67" s="133" t="s">
-        <v>63</v>
-      </c>
-      <c r="I67" s="133" t="s">
+      <c r="H67" s="134" t="s">
+        <v>63</v>
+      </c>
+      <c r="I67" s="134" t="s">
         <v>83</v>
       </c>
-      <c r="J67" s="133"/>
-      <c r="K67" s="134" t="s">
+      <c r="J67" s="134"/>
+      <c r="K67" s="135" t="s">
         <v>145</v>
       </c>
-      <c r="L67" s="133" t="s">
+      <c r="L67" s="134" t="s">
         <v>146</v>
       </c>
-      <c r="M67" s="133"/>
-      <c r="N67" s="133"/>
-      <c r="O67" s="133"/>
-      <c r="P67" s="133"/>
-      <c r="Q67" s="133"/>
-      <c r="R67" s="133"/>
-      <c r="S67" s="133"/>
-      <c r="T67" s="135"/>
+      <c r="M67" s="134"/>
+      <c r="N67" s="134"/>
+      <c r="O67" s="134"/>
+      <c r="P67" s="134"/>
+      <c r="Q67" s="134"/>
+      <c r="R67" s="134"/>
+      <c r="S67" s="134"/>
+      <c r="T67" s="136"/>
     </row>
     <row r="68" s="14" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A68" s="131">
+      <c r="A68" s="132">
         <v>30280002</v>
       </c>
-      <c r="B68" s="132">
+      <c r="B68" s="133">
         <v>102800</v>
       </c>
-      <c r="C68" s="132" t="s">
+      <c r="C68" s="133" t="s">
         <v>144</v>
       </c>
-      <c r="D68" s="131">
+      <c r="D68" s="132">
         <v>302802</v>
       </c>
-      <c r="E68" s="133" t="s">
+      <c r="E68" s="134" t="s">
         <v>130</v>
       </c>
-      <c r="F68" s="133" t="s">
+      <c r="F68" s="134" t="s">
         <v>82</v>
       </c>
-      <c r="G68" s="131">
+      <c r="G68" s="132">
         <v>2028001</v>
       </c>
-      <c r="H68" s="133" t="s">
-        <v>63</v>
-      </c>
-      <c r="I68" s="133" t="s">
+      <c r="H68" s="134" t="s">
+        <v>63</v>
+      </c>
+      <c r="I68" s="134" t="s">
         <v>83</v>
       </c>
-      <c r="J68" s="133"/>
-      <c r="K68" s="134" t="s">
+      <c r="J68" s="134"/>
+      <c r="K68" s="135" t="s">
         <v>145</v>
       </c>
-      <c r="L68" s="133" t="s">
+      <c r="L68" s="134" t="s">
         <v>146</v>
       </c>
-      <c r="M68" s="133"/>
-      <c r="N68" s="133"/>
-      <c r="O68" s="133"/>
-      <c r="P68" s="133"/>
-      <c r="Q68" s="133"/>
-      <c r="R68" s="133"/>
-      <c r="S68" s="133"/>
-      <c r="T68" s="135"/>
+      <c r="M68" s="134"/>
+      <c r="N68" s="134"/>
+      <c r="O68" s="134"/>
+      <c r="P68" s="134"/>
+      <c r="Q68" s="134"/>
+      <c r="R68" s="134"/>
+      <c r="S68" s="134"/>
+      <c r="T68" s="136"/>
     </row>
     <row r="69" s="14" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A69" s="131">
+      <c r="A69" s="132">
         <v>30280003</v>
       </c>
-      <c r="B69" s="132">
+      <c r="B69" s="133">
         <v>102800</v>
       </c>
-      <c r="C69" s="132" t="s">
+      <c r="C69" s="133" t="s">
         <v>144</v>
       </c>
-      <c r="D69" s="131">
+      <c r="D69" s="132">
         <v>302803</v>
       </c>
-      <c r="E69" s="133" t="s">
+      <c r="E69" s="134" t="s">
         <v>131</v>
       </c>
-      <c r="F69" s="133" t="s">
+      <c r="F69" s="134" t="s">
         <v>86</v>
       </c>
-      <c r="G69" s="131">
+      <c r="G69" s="132">
         <v>2028001</v>
       </c>
-      <c r="H69" s="133" t="s">
-        <v>63</v>
-      </c>
-      <c r="I69" s="133" t="s">
+      <c r="H69" s="134" t="s">
+        <v>63</v>
+      </c>
+      <c r="I69" s="134" t="s">
         <v>83</v>
       </c>
-      <c r="J69" s="133"/>
-      <c r="K69" s="134" t="s">
+      <c r="J69" s="134"/>
+      <c r="K69" s="135" t="s">
         <v>145</v>
       </c>
-      <c r="L69" s="133" t="s">
+      <c r="L69" s="134" t="s">
         <v>146</v>
       </c>
-      <c r="M69" s="133"/>
-      <c r="N69" s="133"/>
-      <c r="O69" s="133"/>
-      <c r="P69" s="133"/>
-      <c r="Q69" s="133"/>
-      <c r="R69" s="133"/>
-      <c r="S69" s="133"/>
-      <c r="T69" s="135"/>
+      <c r="M69" s="134"/>
+      <c r="N69" s="134"/>
+      <c r="O69" s="134"/>
+      <c r="P69" s="134"/>
+      <c r="Q69" s="134"/>
+      <c r="R69" s="134"/>
+      <c r="S69" s="134"/>
+      <c r="T69" s="136"/>
     </row>
     <row r="70" s="15" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A70" s="136">
+      <c r="A70" s="137">
         <v>30200003</v>
       </c>
-      <c r="B70" s="137">
+      <c r="B70" s="138">
         <v>102000</v>
       </c>
-      <c r="C70" s="137" t="s">
+      <c r="C70" s="138" t="s">
         <v>147</v>
       </c>
-      <c r="D70" s="136">
+      <c r="D70" s="137">
         <v>302003</v>
       </c>
-      <c r="E70" s="138" t="s">
+      <c r="E70" s="139" t="s">
         <v>148</v>
       </c>
-      <c r="F70" s="138" t="s">
+      <c r="F70" s="139" t="s">
         <v>36</v>
       </c>
-      <c r="G70" s="136">
+      <c r="G70" s="137">
         <v>2020001</v>
       </c>
-      <c r="H70" s="138" t="s">
-        <v>63</v>
-      </c>
-      <c r="I70" s="138" t="s">
+      <c r="H70" s="139" t="s">
+        <v>63</v>
+      </c>
+      <c r="I70" s="139" t="s">
         <v>149</v>
       </c>
-      <c r="J70" s="138"/>
-      <c r="K70" s="139">
+      <c r="J70" s="139"/>
+      <c r="K70" s="140">
         <v>10200011</v>
       </c>
       <c r="L70" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="M70" s="138"/>
-      <c r="N70" s="138"/>
-      <c r="O70" s="138"/>
-      <c r="P70" s="138"/>
-      <c r="Q70" s="138" t="s">
+      <c r="M70" s="139"/>
+      <c r="N70" s="139"/>
+      <c r="O70" s="139"/>
+      <c r="P70" s="139"/>
+      <c r="Q70" s="139" t="s">
         <v>151</v>
       </c>
-      <c r="R70" s="55"/>
-      <c r="S70" s="55" t="s">
+      <c r="R70" s="56"/>
+      <c r="S70" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="T70" s="140"/>
+      <c r="T70" s="141"/>
     </row>
     <row r="71" s="15" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A71" s="136">
+      <c r="A71" s="137">
         <v>30200004</v>
       </c>
-      <c r="B71" s="137">
+      <c r="B71" s="138">
         <v>102000</v>
       </c>
-      <c r="C71" s="137" t="s">
+      <c r="C71" s="138" t="s">
         <v>147</v>
       </c>
-      <c r="D71" s="136">
+      <c r="D71" s="137">
         <v>302004</v>
       </c>
-      <c r="E71" s="138" t="s">
+      <c r="E71" s="139" t="s">
         <v>152</v>
       </c>
-      <c r="F71" s="138" t="s">
+      <c r="F71" s="139" t="s">
         <v>36</v>
       </c>
-      <c r="G71" s="136">
+      <c r="G71" s="137">
         <v>2020001</v>
       </c>
-      <c r="H71" s="138" t="s">
-        <v>63</v>
-      </c>
-      <c r="I71" s="138" t="s">
+      <c r="H71" s="139" t="s">
+        <v>63</v>
+      </c>
+      <c r="I71" s="139" t="s">
         <v>149</v>
       </c>
-      <c r="J71" s="138"/>
-      <c r="K71" s="139">
+      <c r="J71" s="139"/>
+      <c r="K71" s="140">
         <v>10200012</v>
       </c>
       <c r="L71" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="M71" s="138"/>
-      <c r="N71" s="138"/>
-      <c r="O71" s="138"/>
-      <c r="P71" s="138"/>
-      <c r="Q71" s="138" t="s">
+      <c r="M71" s="139"/>
+      <c r="N71" s="139"/>
+      <c r="O71" s="139"/>
+      <c r="P71" s="139"/>
+      <c r="Q71" s="139" t="s">
         <v>151</v>
       </c>
-      <c r="R71" s="55"/>
-      <c r="S71" s="55" t="s">
+      <c r="R71" s="56"/>
+      <c r="S71" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="T71" s="140"/>
+      <c r="T71" s="141"/>
     </row>
     <row r="72" s="15" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A72" s="136">
+      <c r="A72" s="137">
         <v>30200005</v>
       </c>
-      <c r="B72" s="137">
+      <c r="B72" s="138">
         <v>102000</v>
       </c>
-      <c r="C72" s="137" t="s">
+      <c r="C72" s="138" t="s">
         <v>147</v>
       </c>
-      <c r="D72" s="136">
+      <c r="D72" s="137">
         <v>302005</v>
       </c>
-      <c r="E72" s="138" t="s">
+      <c r="E72" s="139" t="s">
         <v>154</v>
       </c>
-      <c r="F72" s="138" t="s">
+      <c r="F72" s="139" t="s">
         <v>36</v>
       </c>
-      <c r="G72" s="136">
+      <c r="G72" s="137">
         <v>2020001</v>
       </c>
-      <c r="H72" s="138" t="s">
-        <v>63</v>
-      </c>
-      <c r="I72" s="138" t="s">
+      <c r="H72" s="139" t="s">
+        <v>63</v>
+      </c>
+      <c r="I72" s="139" t="s">
         <v>149</v>
       </c>
-      <c r="J72" s="138"/>
-      <c r="K72" s="139">
+      <c r="J72" s="139"/>
+      <c r="K72" s="140">
         <v>10200013</v>
       </c>
       <c r="L72" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="M72" s="138"/>
-      <c r="N72" s="138"/>
-      <c r="O72" s="138"/>
-      <c r="P72" s="138"/>
-      <c r="Q72" s="138" t="s">
+      <c r="M72" s="139"/>
+      <c r="N72" s="139"/>
+      <c r="O72" s="139"/>
+      <c r="P72" s="139"/>
+      <c r="Q72" s="139" t="s">
         <v>151</v>
       </c>
-      <c r="R72" s="55"/>
-      <c r="S72" s="55" t="s">
+      <c r="R72" s="56"/>
+      <c r="S72" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="T72" s="140"/>
+      <c r="T72" s="141"/>
     </row>
     <row r="73" s="15" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A73" s="136">
+      <c r="A73" s="137">
         <v>30200006</v>
       </c>
-      <c r="B73" s="137">
+      <c r="B73" s="138">
         <v>102000</v>
       </c>
-      <c r="C73" s="137" t="s">
+      <c r="C73" s="138" t="s">
         <v>147</v>
       </c>
-      <c r="D73" s="136">
+      <c r="D73" s="137">
         <v>302006</v>
       </c>
-      <c r="E73" s="138" t="s">
+      <c r="E73" s="139" t="s">
         <v>156</v>
       </c>
-      <c r="F73" s="138" t="s">
+      <c r="F73" s="139" t="s">
         <v>36</v>
       </c>
-      <c r="G73" s="136">
+      <c r="G73" s="137">
         <v>2020001</v>
       </c>
-      <c r="H73" s="138" t="s">
-        <v>63</v>
-      </c>
-      <c r="I73" s="138" t="s">
+      <c r="H73" s="139" t="s">
+        <v>63</v>
+      </c>
+      <c r="I73" s="139" t="s">
         <v>149</v>
       </c>
-      <c r="J73" s="138"/>
-      <c r="K73" s="139">
+      <c r="J73" s="139"/>
+      <c r="K73" s="140">
         <v>10200014</v>
       </c>
       <c r="L73" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="M73" s="138"/>
-      <c r="N73" s="138"/>
-      <c r="O73" s="138"/>
-      <c r="P73" s="138"/>
-      <c r="Q73" s="138" t="s">
+      <c r="M73" s="139"/>
+      <c r="N73" s="139"/>
+      <c r="O73" s="139"/>
+      <c r="P73" s="139"/>
+      <c r="Q73" s="139" t="s">
         <v>151</v>
       </c>
-      <c r="R73" s="55"/>
-      <c r="S73" s="55" t="s">
+      <c r="R73" s="56"/>
+      <c r="S73" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="T73" s="140"/>
+      <c r="T73" s="141"/>
     </row>
     <row r="74" s="15" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A74" s="136">
+      <c r="A74" s="137">
         <v>30200007</v>
       </c>
-      <c r="B74" s="137">
+      <c r="B74" s="138">
         <v>102000</v>
       </c>
-      <c r="C74" s="137" t="s">
+      <c r="C74" s="138" t="s">
         <v>147</v>
       </c>
-      <c r="D74" s="136">
+      <c r="D74" s="137">
         <v>302007</v>
       </c>
-      <c r="E74" s="138" t="s">
+      <c r="E74" s="139" t="s">
         <v>158</v>
       </c>
-      <c r="F74" s="138" t="s">
+      <c r="F74" s="139" t="s">
         <v>56</v>
       </c>
-      <c r="G74" s="136">
+      <c r="G74" s="137">
         <v>2020001</v>
       </c>
-      <c r="H74" s="138" t="s">
-        <v>63</v>
-      </c>
-      <c r="I74" s="138"/>
-      <c r="J74" s="138"/>
-      <c r="K74" s="139"/>
+      <c r="H74" s="139" t="s">
+        <v>63</v>
+      </c>
+      <c r="I74" s="139"/>
+      <c r="J74" s="139"/>
+      <c r="K74" s="140"/>
       <c r="L74" s="4"/>
-      <c r="M74" s="138"/>
-      <c r="N74" s="138"/>
-      <c r="O74" s="138"/>
-      <c r="P74" s="138"/>
-      <c r="Q74" s="138" t="s">
+      <c r="M74" s="139"/>
+      <c r="N74" s="139"/>
+      <c r="O74" s="139"/>
+      <c r="P74" s="139"/>
+      <c r="Q74" s="139" t="s">
         <v>151</v>
       </c>
-      <c r="R74" s="138"/>
-      <c r="S74" s="138" t="s">
+      <c r="R74" s="139"/>
+      <c r="S74" s="139" t="s">
         <v>42</v>
       </c>
-      <c r="T74" s="140"/>
+      <c r="T74" s="141"/>
     </row>
     <row r="75" s="15" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A75" s="136">
+      <c r="A75" s="137">
         <v>30200008</v>
       </c>
-      <c r="B75" s="137">
+      <c r="B75" s="138">
         <v>102000</v>
       </c>
-      <c r="C75" s="137" t="s">
+      <c r="C75" s="138" t="s">
         <v>147</v>
       </c>
-      <c r="D75" s="136">
+      <c r="D75" s="137">
         <v>302008</v>
       </c>
-      <c r="E75" s="138" t="s">
+      <c r="E75" s="139" t="s">
         <v>159</v>
       </c>
-      <c r="F75" s="138" t="s">
+      <c r="F75" s="139" t="s">
         <v>36</v>
       </c>
-      <c r="G75" s="136">
+      <c r="G75" s="137">
         <v>2020001</v>
       </c>
-      <c r="H75" s="138" t="s">
-        <v>63</v>
-      </c>
-      <c r="I75" s="138"/>
-      <c r="J75" s="138"/>
-      <c r="K75" s="139"/>
+      <c r="H75" s="139" t="s">
+        <v>63</v>
+      </c>
+      <c r="I75" s="139"/>
+      <c r="J75" s="139"/>
+      <c r="K75" s="140"/>
       <c r="L75" s="4"/>
-      <c r="M75" s="138"/>
-      <c r="N75" s="138"/>
-      <c r="O75" s="138"/>
-      <c r="P75" s="138"/>
-      <c r="Q75" s="138" t="s">
+      <c r="M75" s="139"/>
+      <c r="N75" s="139"/>
+      <c r="O75" s="139"/>
+      <c r="P75" s="139"/>
+      <c r="Q75" s="139" t="s">
         <v>151</v>
       </c>
-      <c r="R75" s="138"/>
-      <c r="S75" s="138" t="s">
+      <c r="R75" s="139"/>
+      <c r="S75" s="139" t="s">
         <v>42</v>
       </c>
-      <c r="T75" s="140"/>
+      <c r="T75" s="141"/>
     </row>
     <row r="76" s="16" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A76" s="141">
+      <c r="A76" s="142">
         <v>30200009</v>
       </c>
-      <c r="B76" s="142">
+      <c r="B76" s="143">
         <v>102000</v>
       </c>
-      <c r="C76" s="142" t="s">
+      <c r="C76" s="143" t="s">
         <v>147</v>
       </c>
-      <c r="D76" s="141">
+      <c r="D76" s="142">
         <v>302009</v>
       </c>
-      <c r="E76" s="143" t="s">
+      <c r="E76" s="144" t="s">
         <v>160</v>
       </c>
-      <c r="F76" s="143" t="s">
+      <c r="F76" s="144" t="s">
         <v>111</v>
       </c>
-      <c r="G76" s="141">
+      <c r="G76" s="142">
         <v>2020002</v>
       </c>
-      <c r="H76" s="143" t="s">
-        <v>63</v>
-      </c>
-      <c r="I76" s="143" t="s">
+      <c r="H76" s="144" t="s">
+        <v>63</v>
+      </c>
+      <c r="I76" s="144" t="s">
         <v>83</v>
       </c>
-      <c r="J76" s="143"/>
-      <c r="K76" s="144" t="s">
+      <c r="J76" s="144"/>
+      <c r="K76" s="145" t="s">
         <v>161</v>
       </c>
-      <c r="L76" s="143" t="s">
+      <c r="L76" s="144" t="s">
         <v>162</v>
       </c>
-      <c r="M76" s="143"/>
-      <c r="N76" s="143"/>
-      <c r="O76" s="143"/>
-      <c r="P76" s="143"/>
-      <c r="Q76" s="54"/>
-      <c r="R76" s="55"/>
-      <c r="S76" s="55"/>
-      <c r="T76" s="145"/>
+      <c r="M76" s="144"/>
+      <c r="N76" s="144"/>
+      <c r="O76" s="144"/>
+      <c r="P76" s="144"/>
+      <c r="Q76" s="55"/>
+      <c r="R76" s="56"/>
+      <c r="S76" s="56"/>
+      <c r="T76" s="146"/>
     </row>
     <row r="77" s="16" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A77" s="141">
+      <c r="A77" s="142">
         <v>30200010</v>
       </c>
-      <c r="B77" s="142">
+      <c r="B77" s="143">
         <v>102000</v>
       </c>
-      <c r="C77" s="142" t="s">
+      <c r="C77" s="143" t="s">
         <v>147</v>
       </c>
-      <c r="D77" s="141">
+      <c r="D77" s="142">
         <v>302010</v>
       </c>
-      <c r="E77" s="143" t="s">
+      <c r="E77" s="144" t="s">
         <v>163</v>
       </c>
-      <c r="F77" s="143" t="s">
+      <c r="F77" s="144" t="s">
         <v>56</v>
       </c>
-      <c r="G77" s="141">
+      <c r="G77" s="142">
         <v>2020002</v>
       </c>
-      <c r="H77" s="143" t="s">
-        <v>63</v>
-      </c>
-      <c r="I77" s="143"/>
-      <c r="J77" s="143"/>
-      <c r="K77" s="53">
+      <c r="H77" s="144" t="s">
+        <v>63</v>
+      </c>
+      <c r="I77" s="144"/>
+      <c r="J77" s="144"/>
+      <c r="K77" s="54">
         <v>10200120</v>
       </c>
-      <c r="L77" s="146" t="s">
+      <c r="L77" s="147" t="s">
         <v>164</v>
       </c>
-      <c r="M77" s="143"/>
-      <c r="N77" s="143"/>
-      <c r="O77" s="143"/>
-      <c r="P77" s="143"/>
-      <c r="Q77" s="54" t="s">
+      <c r="M77" s="144"/>
+      <c r="N77" s="144"/>
+      <c r="O77" s="144"/>
+      <c r="P77" s="144"/>
+      <c r="Q77" s="55" t="s">
         <v>165</v>
       </c>
-      <c r="R77" s="55"/>
-      <c r="S77" s="55" t="s">
+      <c r="R77" s="56"/>
+      <c r="S77" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="T77" s="145"/>
+      <c r="T77" s="146"/>
     </row>
     <row r="78" s="16" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A78" s="141">
+      <c r="A78" s="142">
         <v>30200011</v>
       </c>
-      <c r="B78" s="142">
+      <c r="B78" s="143">
         <v>102000</v>
       </c>
-      <c r="C78" s="142" t="s">
+      <c r="C78" s="143" t="s">
         <v>147</v>
       </c>
-      <c r="D78" s="141">
+      <c r="D78" s="142">
         <v>302011</v>
       </c>
-      <c r="E78" s="143" t="s">
+      <c r="E78" s="144" t="s">
         <v>166</v>
       </c>
-      <c r="F78" s="143" t="s">
+      <c r="F78" s="144" t="s">
         <v>56</v>
       </c>
-      <c r="G78" s="141">
+      <c r="G78" s="142">
         <v>2020002</v>
       </c>
-      <c r="H78" s="143" t="s">
-        <v>63</v>
-      </c>
-      <c r="I78" s="143"/>
-      <c r="J78" s="143"/>
-      <c r="K78" s="53">
+      <c r="H78" s="144" t="s">
+        <v>63</v>
+      </c>
+      <c r="I78" s="144"/>
+      <c r="J78" s="144"/>
+      <c r="K78" s="54">
         <v>10200220</v>
       </c>
-      <c r="L78" s="146" t="s">
+      <c r="L78" s="147" t="s">
         <v>167</v>
       </c>
-      <c r="M78" s="143"/>
-      <c r="N78" s="143"/>
-      <c r="O78" s="143"/>
-      <c r="P78" s="143"/>
-      <c r="Q78" s="54" t="s">
+      <c r="M78" s="144"/>
+      <c r="N78" s="144"/>
+      <c r="O78" s="144"/>
+      <c r="P78" s="144"/>
+      <c r="Q78" s="55" t="s">
         <v>165</v>
       </c>
-      <c r="R78" s="55"/>
-      <c r="S78" s="55" t="s">
+      <c r="R78" s="56"/>
+      <c r="S78" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="T78" s="145"/>
+      <c r="T78" s="146"/>
     </row>
     <row r="79" s="16" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A79" s="141">
+      <c r="A79" s="142">
         <v>30200012</v>
       </c>
-      <c r="B79" s="142">
+      <c r="B79" s="143">
         <v>102000</v>
       </c>
-      <c r="C79" s="142" t="s">
+      <c r="C79" s="143" t="s">
         <v>147</v>
       </c>
-      <c r="D79" s="141">
+      <c r="D79" s="142">
         <v>302012</v>
       </c>
-      <c r="E79" s="143" t="s">
+      <c r="E79" s="144" t="s">
         <v>168</v>
       </c>
-      <c r="F79" s="143" t="s">
+      <c r="F79" s="144" t="s">
         <v>56</v>
       </c>
-      <c r="G79" s="141">
+      <c r="G79" s="142">
         <v>2020002</v>
       </c>
-      <c r="H79" s="143" t="s">
-        <v>63</v>
-      </c>
-      <c r="I79" s="143"/>
-      <c r="J79" s="143"/>
-      <c r="K79" s="53">
+      <c r="H79" s="144" t="s">
+        <v>63</v>
+      </c>
+      <c r="I79" s="144"/>
+      <c r="J79" s="144"/>
+      <c r="K79" s="54">
         <v>10200320</v>
       </c>
-      <c r="L79" s="146" t="s">
+      <c r="L79" s="147" t="s">
         <v>169</v>
       </c>
-      <c r="M79" s="143"/>
-      <c r="N79" s="143"/>
-      <c r="O79" s="143"/>
-      <c r="P79" s="143"/>
-      <c r="Q79" s="54" t="s">
+      <c r="M79" s="144"/>
+      <c r="N79" s="144"/>
+      <c r="O79" s="144"/>
+      <c r="P79" s="144"/>
+      <c r="Q79" s="55" t="s">
         <v>165</v>
       </c>
-      <c r="R79" s="55"/>
-      <c r="S79" s="55" t="s">
+      <c r="R79" s="56"/>
+      <c r="S79" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="T79" s="145"/>
+      <c r="T79" s="146"/>
     </row>
     <row r="80" s="16" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A80" s="141">
+      <c r="A80" s="142">
         <v>30200013</v>
       </c>
-      <c r="B80" s="142">
+      <c r="B80" s="143">
         <v>102000</v>
       </c>
-      <c r="C80" s="142" t="s">
+      <c r="C80" s="143" t="s">
         <v>147</v>
       </c>
-      <c r="D80" s="141">
+      <c r="D80" s="142">
         <v>302013</v>
       </c>
-      <c r="E80" s="143" t="s">
+      <c r="E80" s="144" t="s">
         <v>170</v>
       </c>
-      <c r="F80" s="143" t="s">
+      <c r="F80" s="144" t="s">
         <v>56</v>
       </c>
-      <c r="G80" s="141">
+      <c r="G80" s="142">
         <v>2020002</v>
       </c>
-      <c r="H80" s="143" t="s">
-        <v>63</v>
-      </c>
-      <c r="I80" s="143"/>
-      <c r="J80" s="143"/>
-      <c r="K80" s="53">
+      <c r="H80" s="144" t="s">
+        <v>63</v>
+      </c>
+      <c r="I80" s="144"/>
+      <c r="J80" s="144"/>
+      <c r="K80" s="54">
         <v>10200420</v>
       </c>
-      <c r="L80" s="146" t="s">
+      <c r="L80" s="147" t="s">
         <v>171</v>
       </c>
-      <c r="M80" s="143"/>
-      <c r="N80" s="143"/>
-      <c r="O80" s="143"/>
-      <c r="P80" s="143"/>
-      <c r="Q80" s="54" t="s">
+      <c r="M80" s="144"/>
+      <c r="N80" s="144"/>
+      <c r="O80" s="144"/>
+      <c r="P80" s="144"/>
+      <c r="Q80" s="55" t="s">
         <v>165</v>
       </c>
-      <c r="R80" s="55"/>
-      <c r="S80" s="55" t="s">
+      <c r="R80" s="56"/>
+      <c r="S80" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="T80" s="145"/>
+      <c r="T80" s="146"/>
     </row>
     <row r="81" s="10" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A81" s="111">
+      <c r="A81" s="112">
         <v>30200014</v>
       </c>
-      <c r="B81" s="112">
+      <c r="B81" s="113">
         <v>102000</v>
       </c>
-      <c r="C81" s="112" t="s">
+      <c r="C81" s="113" t="s">
         <v>147</v>
       </c>
-      <c r="D81" s="111">
+      <c r="D81" s="112">
         <v>302014</v>
       </c>
-      <c r="E81" s="113" t="s">
+      <c r="E81" s="114" t="s">
         <v>172</v>
       </c>
-      <c r="F81" s="113" t="s">
+      <c r="F81" s="114" t="s">
         <v>111</v>
       </c>
-      <c r="G81" s="111">
+      <c r="G81" s="112">
         <v>2020003</v>
       </c>
-      <c r="H81" s="113" t="s">
-        <v>63</v>
-      </c>
-      <c r="I81" s="113" t="s">
+      <c r="H81" s="114" t="s">
+        <v>63</v>
+      </c>
+      <c r="I81" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="J81" s="113"/>
-      <c r="K81" s="114" t="s">
+      <c r="J81" s="114"/>
+      <c r="K81" s="115" t="s">
         <v>173</v>
       </c>
-      <c r="L81" s="113" t="s">
+      <c r="L81" s="114" t="s">
         <v>174</v>
       </c>
-      <c r="M81" s="113"/>
-      <c r="N81" s="113"/>
-      <c r="O81" s="113"/>
-      <c r="P81" s="113"/>
-      <c r="Q81" s="113"/>
-      <c r="R81" s="113"/>
-      <c r="S81" s="113"/>
-      <c r="T81" s="115"/>
+      <c r="M81" s="114"/>
+      <c r="N81" s="114"/>
+      <c r="O81" s="114"/>
+      <c r="P81" s="114"/>
+      <c r="Q81" s="114"/>
+      <c r="R81" s="114"/>
+      <c r="S81" s="114"/>
+      <c r="T81" s="116"/>
     </row>
     <row r="82" s="10" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A82" s="111">
+      <c r="A82" s="112">
         <v>30200015</v>
       </c>
-      <c r="B82" s="112">
+      <c r="B82" s="113">
         <v>102000</v>
       </c>
-      <c r="C82" s="112" t="s">
+      <c r="C82" s="113" t="s">
         <v>147</v>
       </c>
-      <c r="D82" s="111">
+      <c r="D82" s="112">
         <v>302015</v>
       </c>
-      <c r="E82" s="113" t="s">
+      <c r="E82" s="114" t="s">
         <v>175</v>
       </c>
-      <c r="F82" s="113" t="s">
+      <c r="F82" s="114" t="s">
         <v>36</v>
       </c>
-      <c r="G82" s="111">
+      <c r="G82" s="112">
         <v>2020003</v>
       </c>
-      <c r="H82" s="113" t="s">
-        <v>63</v>
-      </c>
-      <c r="I82" s="113"/>
-      <c r="J82" s="113"/>
-      <c r="K82" s="114">
+      <c r="H82" s="114" t="s">
+        <v>63</v>
+      </c>
+      <c r="I82" s="114"/>
+      <c r="J82" s="114"/>
+      <c r="K82" s="115">
         <v>10200125</v>
       </c>
-      <c r="L82" s="113" t="s">
+      <c r="L82" s="114" t="s">
         <v>176</v>
       </c>
-      <c r="M82" s="113"/>
-      <c r="N82" s="113"/>
-      <c r="O82" s="113"/>
-      <c r="P82" s="113"/>
-      <c r="Q82" s="147" t="s">
+      <c r="M82" s="114"/>
+      <c r="N82" s="114"/>
+      <c r="O82" s="114"/>
+      <c r="P82" s="114"/>
+      <c r="Q82" s="148" t="s">
         <v>165</v>
       </c>
-      <c r="R82" s="148"/>
-      <c r="S82" s="148" t="s">
+      <c r="R82" s="149"/>
+      <c r="S82" s="149" t="s">
         <v>42</v>
       </c>
-      <c r="T82" s="115"/>
+      <c r="T82" s="116"/>
     </row>
     <row r="83" s="10" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A83" s="111">
+      <c r="A83" s="112">
         <v>30200016</v>
       </c>
-      <c r="B83" s="112">
+      <c r="B83" s="113">
         <v>102000</v>
       </c>
-      <c r="C83" s="112" t="s">
+      <c r="C83" s="113" t="s">
         <v>147</v>
       </c>
-      <c r="D83" s="111">
+      <c r="D83" s="112">
         <v>302016</v>
       </c>
-      <c r="E83" s="113" t="s">
+      <c r="E83" s="114" t="s">
         <v>177</v>
       </c>
-      <c r="F83" s="113" t="s">
+      <c r="F83" s="114" t="s">
         <v>36</v>
       </c>
-      <c r="G83" s="111">
+      <c r="G83" s="112">
         <v>2020003</v>
       </c>
-      <c r="H83" s="113" t="s">
-        <v>63</v>
-      </c>
-      <c r="I83" s="113"/>
-      <c r="J83" s="113"/>
-      <c r="K83" s="114">
+      <c r="H83" s="114" t="s">
+        <v>63</v>
+      </c>
+      <c r="I83" s="114"/>
+      <c r="J83" s="114"/>
+      <c r="K83" s="115">
         <v>10200225</v>
       </c>
-      <c r="L83" s="113" t="s">
+      <c r="L83" s="114" t="s">
         <v>178</v>
       </c>
-      <c r="M83" s="113"/>
-      <c r="N83" s="113"/>
-      <c r="O83" s="113"/>
-      <c r="P83" s="113"/>
-      <c r="Q83" s="147" t="s">
+      <c r="M83" s="114"/>
+      <c r="N83" s="114"/>
+      <c r="O83" s="114"/>
+      <c r="P83" s="114"/>
+      <c r="Q83" s="148" t="s">
         <v>165</v>
       </c>
-      <c r="R83" s="148"/>
-      <c r="S83" s="148" t="s">
+      <c r="R83" s="149"/>
+      <c r="S83" s="149" t="s">
         <v>42</v>
       </c>
-      <c r="T83" s="115"/>
+      <c r="T83" s="116"/>
     </row>
     <row r="84" s="10" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A84" s="111">
+      <c r="A84" s="112">
         <v>30200017</v>
       </c>
-      <c r="B84" s="112">
+      <c r="B84" s="113">
         <v>102000</v>
       </c>
-      <c r="C84" s="112" t="s">
+      <c r="C84" s="113" t="s">
         <v>147</v>
       </c>
-      <c r="D84" s="111">
+      <c r="D84" s="112">
         <v>302017</v>
       </c>
-      <c r="E84" s="113" t="s">
+      <c r="E84" s="114" t="s">
         <v>179</v>
       </c>
-      <c r="F84" s="113" t="s">
+      <c r="F84" s="114" t="s">
         <v>36</v>
       </c>
-      <c r="G84" s="111">
+      <c r="G84" s="112">
         <v>2020003</v>
       </c>
-      <c r="H84" s="113" t="s">
-        <v>63</v>
-      </c>
-      <c r="I84" s="113"/>
-      <c r="J84" s="113"/>
-      <c r="K84" s="114">
+      <c r="H84" s="114" t="s">
+        <v>63</v>
+      </c>
+      <c r="I84" s="114"/>
+      <c r="J84" s="114"/>
+      <c r="K84" s="115">
         <v>10200325</v>
       </c>
-      <c r="L84" s="113" t="s">
+      <c r="L84" s="114" t="s">
         <v>180</v>
       </c>
-      <c r="M84" s="113"/>
-      <c r="N84" s="113"/>
-      <c r="O84" s="113"/>
-      <c r="P84" s="113"/>
-      <c r="Q84" s="147" t="s">
+      <c r="M84" s="114"/>
+      <c r="N84" s="114"/>
+      <c r="O84" s="114"/>
+      <c r="P84" s="114"/>
+      <c r="Q84" s="148" t="s">
         <v>165</v>
       </c>
-      <c r="R84" s="148"/>
-      <c r="S84" s="148" t="s">
+      <c r="R84" s="149"/>
+      <c r="S84" s="149" t="s">
         <v>42</v>
       </c>
-      <c r="T84" s="115"/>
+      <c r="T84" s="116"/>
     </row>
     <row r="85" s="10" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A85" s="111">
+      <c r="A85" s="112">
         <v>30200018</v>
       </c>
-      <c r="B85" s="112">
+      <c r="B85" s="113">
         <v>102000</v>
       </c>
-      <c r="C85" s="112" t="s">
+      <c r="C85" s="113" t="s">
         <v>147</v>
       </c>
-      <c r="D85" s="111">
+      <c r="D85" s="112">
         <v>302018</v>
       </c>
-      <c r="E85" s="113" t="s">
+      <c r="E85" s="114" t="s">
         <v>181</v>
       </c>
-      <c r="F85" s="113" t="s">
+      <c r="F85" s="114" t="s">
         <v>36</v>
       </c>
-      <c r="G85" s="111">
+      <c r="G85" s="112">
         <v>2020003</v>
       </c>
-      <c r="H85" s="113" t="s">
-        <v>63</v>
-      </c>
-      <c r="I85" s="113"/>
-      <c r="J85" s="113"/>
-      <c r="K85" s="114">
+      <c r="H85" s="114" t="s">
+        <v>63</v>
+      </c>
+      <c r="I85" s="114"/>
+      <c r="J85" s="114"/>
+      <c r="K85" s="115">
         <v>10200425</v>
       </c>
-      <c r="L85" s="113" t="s">
+      <c r="L85" s="114" t="s">
         <v>182</v>
       </c>
-      <c r="M85" s="113"/>
-      <c r="N85" s="113"/>
-      <c r="O85" s="113"/>
-      <c r="P85" s="113"/>
-      <c r="Q85" s="147" t="s">
+      <c r="M85" s="114"/>
+      <c r="N85" s="114"/>
+      <c r="O85" s="114"/>
+      <c r="P85" s="114"/>
+      <c r="Q85" s="148" t="s">
         <v>165</v>
       </c>
-      <c r="R85" s="148"/>
-      <c r="S85" s="148" t="s">
+      <c r="R85" s="149"/>
+      <c r="S85" s="149" t="s">
         <v>42</v>
       </c>
-      <c r="T85" s="115"/>
+      <c r="T85" s="116"/>
     </row>
     <row r="86" s="13" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A86" s="126">
+      <c r="A86" s="127">
         <v>30380001</v>
       </c>
-      <c r="B86" s="127">
+      <c r="B86" s="128">
         <v>103800</v>
       </c>
-      <c r="C86" s="127" t="s">
+      <c r="C86" s="128" t="s">
         <v>183</v>
       </c>
-      <c r="D86" s="126">
+      <c r="D86" s="127">
         <v>303801</v>
       </c>
-      <c r="E86" s="128" t="s">
+      <c r="E86" s="129" t="s">
         <v>184</v>
       </c>
-      <c r="F86" s="128" t="s">
+      <c r="F86" s="129" t="s">
         <v>185</v>
       </c>
-      <c r="G86" s="126">
+      <c r="G86" s="127">
         <v>2038001</v>
       </c>
-      <c r="H86" s="128" t="s">
-        <v>63</v>
-      </c>
-      <c r="I86" s="128"/>
-      <c r="J86" s="128"/>
-      <c r="K86" s="129" t="s">
+      <c r="H86" s="129" t="s">
+        <v>63</v>
+      </c>
+      <c r="I86" s="129"/>
+      <c r="J86" s="129"/>
+      <c r="K86" s="130" t="s">
         <v>186</v>
       </c>
-      <c r="L86" s="128" t="s">
+      <c r="L86" s="129" t="s">
         <v>187</v>
       </c>
-      <c r="M86" s="128"/>
-      <c r="N86" s="128"/>
-      <c r="O86" s="128"/>
-      <c r="P86" s="128"/>
-      <c r="Q86" s="149"/>
-      <c r="R86" s="150"/>
-      <c r="S86" s="150"/>
-      <c r="T86" s="130"/>
+      <c r="M86" s="129"/>
+      <c r="N86" s="129"/>
+      <c r="O86" s="129"/>
+      <c r="P86" s="129"/>
+      <c r="Q86" s="150"/>
+      <c r="R86" s="151"/>
+      <c r="S86" s="151"/>
+      <c r="T86" s="131"/>
     </row>
     <row r="87" s="13" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A87" s="126">
+      <c r="A87" s="127">
         <v>30380002</v>
       </c>
-      <c r="B87" s="127">
+      <c r="B87" s="128">
         <v>103800</v>
       </c>
-      <c r="C87" s="127" t="s">
+      <c r="C87" s="128" t="s">
         <v>183</v>
       </c>
-      <c r="D87" s="126">
+      <c r="D87" s="127">
         <v>303802</v>
       </c>
-      <c r="E87" s="128" t="s">
+      <c r="E87" s="129" t="s">
         <v>188</v>
       </c>
-      <c r="F87" s="128" t="s">
+      <c r="F87" s="129" t="s">
         <v>36</v>
       </c>
-      <c r="G87" s="126">
+      <c r="G87" s="127">
         <v>2038001</v>
       </c>
-      <c r="H87" s="128" t="s">
-        <v>63</v>
-      </c>
-      <c r="I87" s="128"/>
-      <c r="J87" s="128"/>
-      <c r="K87" s="129"/>
-      <c r="L87" s="128"/>
-      <c r="M87" s="128" t="s">
+      <c r="H87" s="129" t="s">
+        <v>63</v>
+      </c>
+      <c r="I87" s="129"/>
+      <c r="J87" s="129"/>
+      <c r="K87" s="130"/>
+      <c r="L87" s="129"/>
+      <c r="M87" s="129" t="s">
         <v>56</v>
       </c>
-      <c r="N87" s="128"/>
-      <c r="O87" s="128" t="s">
+      <c r="N87" s="129"/>
+      <c r="O87" s="129" t="s">
         <v>189</v>
       </c>
-      <c r="P87" s="128"/>
-      <c r="Q87" s="149"/>
-      <c r="R87" s="150"/>
-      <c r="S87" s="150"/>
-      <c r="T87" s="130"/>
+      <c r="P87" s="129"/>
+      <c r="Q87" s="150"/>
+      <c r="R87" s="151"/>
+      <c r="S87" s="151"/>
+      <c r="T87" s="131"/>
     </row>
     <row r="88" s="17" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A88" s="151">
+      <c r="A88" s="152">
         <v>30270001</v>
       </c>
-      <c r="B88" s="152">
+      <c r="B88" s="153">
         <v>102700</v>
       </c>
-      <c r="C88" s="152" t="s">
+      <c r="C88" s="153" t="s">
         <v>190</v>
       </c>
-      <c r="D88" s="151">
+      <c r="D88" s="152">
         <v>302701</v>
       </c>
-      <c r="E88" s="153" t="s">
+      <c r="E88" s="154" t="s">
         <v>191</v>
       </c>
-      <c r="F88" s="153" t="s">
+      <c r="F88" s="154" t="s">
         <v>82</v>
       </c>
-      <c r="G88" s="151">
+      <c r="G88" s="152">
         <v>2027001</v>
       </c>
-      <c r="H88" s="153" t="s">
-        <v>63</v>
-      </c>
-      <c r="I88" s="153" t="s">
+      <c r="H88" s="154" t="s">
+        <v>63</v>
+      </c>
+      <c r="I88" s="154" t="s">
         <v>83</v>
       </c>
-      <c r="J88" s="153"/>
-      <c r="K88" s="154" t="s">
+      <c r="J88" s="154"/>
+      <c r="K88" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="L88" s="153" t="s">
+      <c r="L88" s="154" t="s">
         <v>193</v>
       </c>
-      <c r="M88" s="153"/>
-      <c r="N88" s="153"/>
-      <c r="O88" s="153"/>
-      <c r="P88" s="153"/>
-      <c r="Q88" s="155"/>
-      <c r="R88" s="156"/>
-      <c r="S88" s="156"/>
-      <c r="T88" s="157"/>
+      <c r="M88" s="154"/>
+      <c r="N88" s="154"/>
+      <c r="O88" s="154"/>
+      <c r="P88" s="154"/>
+      <c r="Q88" s="156"/>
+      <c r="R88" s="157"/>
+      <c r="S88" s="157"/>
+      <c r="T88" s="158"/>
     </row>
     <row r="89" s="17" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A89" s="151">
+      <c r="A89" s="152">
         <v>30270002</v>
       </c>
-      <c r="B89" s="152">
+      <c r="B89" s="153">
         <v>102700</v>
       </c>
-      <c r="C89" s="152" t="s">
+      <c r="C89" s="153" t="s">
         <v>190</v>
       </c>
-      <c r="D89" s="151">
+      <c r="D89" s="152">
         <v>302702</v>
       </c>
-      <c r="E89" s="153" t="s">
+      <c r="E89" s="154" t="s">
         <v>194</v>
       </c>
-      <c r="F89" s="153" t="s">
+      <c r="F89" s="154" t="s">
         <v>124</v>
       </c>
-      <c r="G89" s="151">
+      <c r="G89" s="152">
         <v>2027001</v>
       </c>
-      <c r="H89" s="153" t="s">
-        <v>63</v>
-      </c>
-      <c r="I89" s="153" t="s">
+      <c r="H89" s="154" t="s">
+        <v>63</v>
+      </c>
+      <c r="I89" s="154" t="s">
         <v>83</v>
       </c>
-      <c r="J89" s="153"/>
-      <c r="K89" s="154" t="s">
+      <c r="J89" s="154"/>
+      <c r="K89" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="L89" s="153" t="s">
+      <c r="L89" s="154" t="s">
         <v>193</v>
       </c>
-      <c r="M89" s="153"/>
-      <c r="N89" s="153"/>
-      <c r="O89" s="153"/>
-      <c r="P89" s="153"/>
-      <c r="Q89" s="155"/>
-      <c r="R89" s="156"/>
-      <c r="S89" s="156"/>
-      <c r="T89" s="157"/>
+      <c r="M89" s="154"/>
+      <c r="N89" s="154"/>
+      <c r="O89" s="154"/>
+      <c r="P89" s="154"/>
+      <c r="Q89" s="156"/>
+      <c r="R89" s="157"/>
+      <c r="S89" s="157"/>
+      <c r="T89" s="158"/>
     </row>
     <row r="90" s="17" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A90" s="151">
+      <c r="A90" s="152">
         <v>30270003</v>
       </c>
-      <c r="B90" s="152">
+      <c r="B90" s="153">
         <v>102700</v>
       </c>
-      <c r="C90" s="152" t="s">
+      <c r="C90" s="153" t="s">
         <v>190</v>
       </c>
-      <c r="D90" s="151">
+      <c r="D90" s="152">
         <v>302703</v>
       </c>
-      <c r="E90" s="153" t="s">
+      <c r="E90" s="154" t="s">
         <v>195</v>
       </c>
-      <c r="F90" s="153" t="s">
+      <c r="F90" s="154" t="s">
         <v>196</v>
       </c>
-      <c r="G90" s="151">
+      <c r="G90" s="152">
         <v>2027001</v>
       </c>
-      <c r="H90" s="153" t="s">
-        <v>63</v>
-      </c>
-      <c r="I90" s="153" t="s">
+      <c r="H90" s="154" t="s">
+        <v>63</v>
+      </c>
+      <c r="I90" s="154" t="s">
         <v>83</v>
       </c>
-      <c r="J90" s="153"/>
-      <c r="K90" s="154" t="s">
+      <c r="J90" s="154"/>
+      <c r="K90" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="L90" s="153" t="s">
+      <c r="L90" s="154" t="s">
         <v>193</v>
       </c>
-      <c r="M90" s="153"/>
-      <c r="N90" s="153"/>
-      <c r="O90" s="153"/>
-      <c r="P90" s="153"/>
-      <c r="Q90" s="155"/>
-      <c r="R90" s="156"/>
-      <c r="S90" s="156"/>
-      <c r="T90" s="157"/>
+      <c r="M90" s="154"/>
+      <c r="N90" s="154"/>
+      <c r="O90" s="154"/>
+      <c r="P90" s="154"/>
+      <c r="Q90" s="156"/>
+      <c r="R90" s="157"/>
+      <c r="S90" s="157"/>
+      <c r="T90" s="158"/>
     </row>
     <row r="91" s="18" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A91" s="158">
+      <c r="A91" s="159">
         <v>30310001</v>
       </c>
-      <c r="B91" s="159">
+      <c r="B91" s="160">
         <v>103100</v>
       </c>
-      <c r="C91" s="159" t="s">
+      <c r="C91" s="160" t="s">
         <v>197</v>
       </c>
-      <c r="D91" s="158">
+      <c r="D91" s="159">
         <v>303101</v>
       </c>
-      <c r="E91" s="160" t="s">
+      <c r="E91" s="161" t="s">
         <v>198</v>
       </c>
-      <c r="F91" s="160" t="s">
+      <c r="F91" s="161" t="s">
         <v>199</v>
       </c>
-      <c r="G91" s="158">
+      <c r="G91" s="159">
         <v>2031001</v>
       </c>
-      <c r="H91" s="160" t="s">
-        <v>63</v>
-      </c>
-      <c r="I91" s="160"/>
-      <c r="J91" s="160"/>
-      <c r="K91" s="161">
+      <c r="H91" s="161" t="s">
+        <v>63</v>
+      </c>
+      <c r="I91" s="161"/>
+      <c r="J91" s="161"/>
+      <c r="K91" s="162">
         <v>10310005</v>
       </c>
-      <c r="L91" s="160" t="s">
+      <c r="L91" s="161" t="s">
         <v>200</v>
       </c>
-      <c r="M91" s="160"/>
-      <c r="N91" s="160"/>
-      <c r="O91" s="160"/>
-      <c r="P91" s="160"/>
-      <c r="Q91" s="162"/>
-      <c r="R91" s="163"/>
-      <c r="S91" s="163"/>
-      <c r="T91" s="164"/>
+      <c r="M91" s="161"/>
+      <c r="N91" s="161"/>
+      <c r="O91" s="161"/>
+      <c r="P91" s="161"/>
+      <c r="Q91" s="163"/>
+      <c r="R91" s="164"/>
+      <c r="S91" s="164"/>
+      <c r="T91" s="165"/>
     </row>
     <row r="92" s="18" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A92" s="158">
+      <c r="A92" s="159">
         <v>30310002</v>
       </c>
-      <c r="B92" s="159">
+      <c r="B92" s="160">
         <v>103100</v>
       </c>
-      <c r="C92" s="159" t="s">
+      <c r="C92" s="160" t="s">
         <v>197</v>
       </c>
-      <c r="D92" s="158">
+      <c r="D92" s="159">
         <v>303102</v>
       </c>
-      <c r="E92" s="160" t="s">
+      <c r="E92" s="161" t="s">
         <v>201</v>
       </c>
-      <c r="F92" s="160" t="s">
+      <c r="F92" s="161" t="s">
         <v>56</v>
       </c>
-      <c r="G92" s="158">
+      <c r="G92" s="159">
         <v>2031001</v>
       </c>
-      <c r="H92" s="160" t="s">
-        <v>63</v>
-      </c>
-      <c r="I92" s="160"/>
-      <c r="J92" s="160"/>
-      <c r="K92" s="161">
+      <c r="H92" s="161" t="s">
+        <v>63</v>
+      </c>
+      <c r="I92" s="161"/>
+      <c r="J92" s="161"/>
+      <c r="K92" s="162">
         <v>10310006</v>
       </c>
-      <c r="L92" s="160" t="s">
+      <c r="L92" s="161" t="s">
         <v>202</v>
       </c>
-      <c r="M92" s="160"/>
-      <c r="N92" s="160"/>
-      <c r="O92" s="160"/>
-      <c r="P92" s="160"/>
-      <c r="Q92" s="162"/>
-      <c r="R92" s="163"/>
-      <c r="S92" s="163"/>
-      <c r="T92" s="164"/>
+      <c r="M92" s="161"/>
+      <c r="N92" s="161"/>
+      <c r="O92" s="161"/>
+      <c r="P92" s="161"/>
+      <c r="Q92" s="163"/>
+      <c r="R92" s="164"/>
+      <c r="S92" s="164"/>
+      <c r="T92" s="165"/>
     </row>
     <row r="93" s="18" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A93" s="158">
+      <c r="A93" s="159">
         <v>30310003</v>
       </c>
-      <c r="B93" s="159">
+      <c r="B93" s="160">
         <v>103100</v>
       </c>
-      <c r="C93" s="159" t="s">
+      <c r="C93" s="160" t="s">
         <v>197</v>
       </c>
-      <c r="D93" s="158">
+      <c r="D93" s="159">
         <v>303103</v>
       </c>
-      <c r="E93" s="160" t="s">
+      <c r="E93" s="161" t="s">
         <v>123</v>
       </c>
-      <c r="F93" s="160" t="s">
+      <c r="F93" s="161" t="s">
         <v>124</v>
       </c>
-      <c r="G93" s="158">
+      <c r="G93" s="159">
         <v>2031001</v>
       </c>
-      <c r="H93" s="160" t="s">
-        <v>63</v>
-      </c>
-      <c r="I93" s="160" t="s">
+      <c r="H93" s="161" t="s">
+        <v>63</v>
+      </c>
+      <c r="I93" s="161" t="s">
         <v>83</v>
       </c>
-      <c r="J93" s="160" t="s">
+      <c r="J93" s="161" t="s">
         <v>203</v>
       </c>
-      <c r="K93" s="161" t="s">
+      <c r="K93" s="162" t="s">
         <v>204</v>
       </c>
-      <c r="L93" s="160" t="s">
+      <c r="L93" s="161" t="s">
         <v>205</v>
       </c>
-      <c r="M93" s="160"/>
-      <c r="N93" s="160"/>
-      <c r="O93" s="160"/>
-      <c r="P93" s="160"/>
-      <c r="Q93" s="162"/>
-      <c r="R93" s="163"/>
-      <c r="S93" s="163"/>
-      <c r="T93" s="164"/>
+      <c r="M93" s="161"/>
+      <c r="N93" s="161"/>
+      <c r="O93" s="161"/>
+      <c r="P93" s="161"/>
+      <c r="Q93" s="163"/>
+      <c r="R93" s="164"/>
+      <c r="S93" s="164"/>
+      <c r="T93" s="165"/>
     </row>
     <row r="94" s="18" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A94" s="158">
+      <c r="A94" s="159">
         <v>30310004</v>
       </c>
-      <c r="B94" s="159">
+      <c r="B94" s="160">
         <v>103100</v>
       </c>
-      <c r="C94" s="159" t="s">
+      <c r="C94" s="160" t="s">
         <v>197</v>
       </c>
-      <c r="D94" s="158">
+      <c r="D94" s="159">
         <v>303104</v>
       </c>
-      <c r="E94" s="160" t="s">
+      <c r="E94" s="161" t="s">
         <v>206</v>
       </c>
-      <c r="F94" s="160" t="s">
+      <c r="F94" s="161" t="s">
         <v>36</v>
       </c>
-      <c r="G94" s="158">
+      <c r="G94" s="159">
         <v>2031001</v>
       </c>
-      <c r="H94" s="160" t="s">
-        <v>63</v>
-      </c>
-      <c r="I94" s="160" t="s">
+      <c r="H94" s="161" t="s">
+        <v>63</v>
+      </c>
+      <c r="I94" s="161" t="s">
         <v>207</v>
       </c>
-      <c r="J94" s="160"/>
-      <c r="K94" s="161"/>
-      <c r="L94" s="160"/>
-      <c r="M94" s="160" t="s">
+      <c r="J94" s="161"/>
+      <c r="K94" s="162"/>
+      <c r="L94" s="161"/>
+      <c r="M94" s="161" t="s">
         <v>208</v>
       </c>
-      <c r="N94" s="160" t="s">
+      <c r="N94" s="161" t="s">
         <v>209</v>
       </c>
-      <c r="O94" s="160"/>
-      <c r="P94" s="160"/>
-      <c r="Q94" s="162" t="s">
+      <c r="O94" s="161"/>
+      <c r="P94" s="161"/>
+      <c r="Q94" s="163" t="s">
         <v>210</v>
       </c>
-      <c r="R94" s="163" t="s">
+      <c r="R94" s="164" t="s">
         <v>211</v>
       </c>
-      <c r="S94" s="163" t="s">
+      <c r="S94" s="164" t="s">
         <v>42</v>
       </c>
-      <c r="T94" s="164"/>
+      <c r="T94" s="165"/>
     </row>
     <row r="95" s="19" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A95" s="165">
+      <c r="A95" s="166">
         <v>30400001</v>
       </c>
-      <c r="B95" s="166">
+      <c r="B95" s="167">
         <v>104000</v>
       </c>
-      <c r="C95" s="166" t="s">
+      <c r="C95" s="167" t="s">
         <v>212</v>
       </c>
-      <c r="D95" s="165">
+      <c r="D95" s="166">
         <v>304001</v>
       </c>
-      <c r="E95" s="167" t="s">
+      <c r="E95" s="168" t="s">
         <v>213</v>
       </c>
-      <c r="F95" s="167" t="s">
+      <c r="F95" s="168" t="s">
         <v>214</v>
       </c>
-      <c r="G95" s="165">
+      <c r="G95" s="166">
         <v>2040001</v>
       </c>
-      <c r="H95" s="167" t="s">
-        <v>63</v>
-      </c>
-      <c r="I95" s="167" t="s">
+      <c r="H95" s="168" t="s">
+        <v>63</v>
+      </c>
+      <c r="I95" s="168" t="s">
         <v>83</v>
       </c>
-      <c r="J95" s="167"/>
-      <c r="K95" s="168" t="s">
+      <c r="J95" s="168"/>
+      <c r="K95" s="169" t="s">
         <v>215</v>
       </c>
-      <c r="L95" s="167" t="s">
+      <c r="L95" s="168" t="s">
         <v>193</v>
       </c>
-      <c r="M95" s="167"/>
-      <c r="N95" s="167"/>
-      <c r="O95" s="167"/>
-      <c r="P95" s="167"/>
-      <c r="Q95" s="169"/>
-      <c r="R95" s="170"/>
-      <c r="S95" s="170"/>
-      <c r="T95" s="171"/>
+      <c r="M95" s="168"/>
+      <c r="N95" s="168"/>
+      <c r="O95" s="168"/>
+      <c r="P95" s="168"/>
+      <c r="Q95" s="170"/>
+      <c r="R95" s="171"/>
+      <c r="S95" s="171"/>
+      <c r="T95" s="172"/>
     </row>
     <row r="96" s="20" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A96" s="80">
+      <c r="A96" s="81">
         <v>30390001</v>
       </c>
-      <c r="B96" s="80">
+      <c r="B96" s="81">
         <v>103900</v>
       </c>
-      <c r="C96" s="80" t="s">
+      <c r="C96" s="81" t="s">
         <v>216</v>
       </c>
-      <c r="D96" s="80">
+      <c r="D96" s="81">
         <v>303901</v>
       </c>
       <c r="E96" s="20" t="s">
@@ -6884,7 +6898,7 @@
       <c r="F96" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="G96" s="80">
+      <c r="G96" s="81">
         <v>2039001</v>
       </c>
       <c r="H96" s="20" t="s">
@@ -6893,25 +6907,25 @@
       <c r="I96" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="K96" s="99">
+      <c r="K96" s="100">
         <v>10390001</v>
       </c>
       <c r="L96" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="T96" s="172"/>
+      <c r="T96" s="173"/>
     </row>
     <row r="97" s="20" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A97" s="80">
+      <c r="A97" s="81">
         <v>30390002</v>
       </c>
-      <c r="B97" s="80">
+      <c r="B97" s="81">
         <v>103900</v>
       </c>
-      <c r="C97" s="80" t="s">
+      <c r="C97" s="81" t="s">
         <v>216</v>
       </c>
-      <c r="D97" s="80">
+      <c r="D97" s="81">
         <v>303902</v>
       </c>
       <c r="E97" s="20" t="s">
@@ -6920,7 +6934,7 @@
       <c r="F97" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="G97" s="80">
+      <c r="G97" s="81">
         <v>2039001</v>
       </c>
       <c r="H97" s="20" t="s">
@@ -6929,25 +6943,25 @@
       <c r="I97" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="K97" s="99">
+      <c r="K97" s="100">
         <v>10390001</v>
       </c>
       <c r="L97" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="T97" s="172"/>
+      <c r="T97" s="173"/>
     </row>
     <row r="98" s="20" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A98" s="80">
+      <c r="A98" s="81">
         <v>30390003</v>
       </c>
-      <c r="B98" s="80">
+      <c r="B98" s="81">
         <v>103900</v>
       </c>
-      <c r="C98" s="80" t="s">
+      <c r="C98" s="81" t="s">
         <v>216</v>
       </c>
-      <c r="D98" s="80">
+      <c r="D98" s="81">
         <v>303903</v>
       </c>
       <c r="E98" s="20" t="s">
@@ -6956,7 +6970,7 @@
       <c r="F98" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="G98" s="80">
+      <c r="G98" s="81">
         <v>2039001</v>
       </c>
       <c r="H98" s="20" t="s">
@@ -6965,25 +6979,25 @@
       <c r="I98" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="K98" s="99">
+      <c r="K98" s="100">
         <v>10390001</v>
       </c>
       <c r="L98" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="T98" s="172"/>
+      <c r="T98" s="173"/>
     </row>
     <row r="99" s="20" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A99" s="80">
+      <c r="A99" s="81">
         <v>30390004</v>
       </c>
-      <c r="B99" s="80">
+      <c r="B99" s="81">
         <v>103900</v>
       </c>
-      <c r="C99" s="80" t="s">
+      <c r="C99" s="81" t="s">
         <v>216</v>
       </c>
-      <c r="D99" s="80">
+      <c r="D99" s="81">
         <v>303904</v>
       </c>
       <c r="E99" s="20" t="s">
@@ -6992,31 +7006,31 @@
       <c r="F99" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="G99" s="80">
+      <c r="G99" s="81">
         <v>2039001</v>
       </c>
       <c r="H99" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="K99" s="99">
+      <c r="K99" s="100">
         <v>10390002</v>
       </c>
       <c r="L99" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="T99" s="172"/>
+      <c r="T99" s="173"/>
     </row>
     <row r="100" s="21" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A100" s="56">
+      <c r="A100" s="57">
         <v>30160001</v>
       </c>
-      <c r="B100" s="56">
+      <c r="B100" s="57">
         <v>101600</v>
       </c>
-      <c r="C100" s="56" t="s">
+      <c r="C100" s="57" t="s">
         <v>220</v>
       </c>
-      <c r="D100" s="56">
+      <c r="D100" s="57">
         <v>301601</v>
       </c>
       <c r="E100" s="21" t="s">
@@ -7025,7 +7039,7 @@
       <c r="F100" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="G100" s="56">
+      <c r="G100" s="57">
         <v>2016001</v>
       </c>
       <c r="H100" s="21" t="s">
@@ -7037,25 +7051,25 @@
       <c r="J100" s="21" t="s">
         <v>221</v>
       </c>
-      <c r="K100" s="58" t="s">
+      <c r="K100" s="59" t="s">
         <v>222</v>
       </c>
       <c r="L100" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="T100" s="173"/>
+      <c r="T100" s="174"/>
     </row>
     <row r="101" s="21" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A101" s="56">
+      <c r="A101" s="57">
         <v>30160002</v>
       </c>
-      <c r="B101" s="56">
+      <c r="B101" s="57">
         <v>101600</v>
       </c>
-      <c r="C101" s="56" t="s">
+      <c r="C101" s="57" t="s">
         <v>220</v>
       </c>
-      <c r="D101" s="56">
+      <c r="D101" s="57">
         <v>301602</v>
       </c>
       <c r="E101" s="21" t="s">
@@ -7064,7 +7078,7 @@
       <c r="F101" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="G101" s="56">
+      <c r="G101" s="57">
         <v>2016001</v>
       </c>
       <c r="H101" s="21" t="s">
@@ -7076,25 +7090,25 @@
       <c r="J101" s="21" t="s">
         <v>221</v>
       </c>
-      <c r="K101" s="58" t="s">
+      <c r="K101" s="59" t="s">
         <v>222</v>
       </c>
       <c r="L101" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="T101" s="173"/>
+      <c r="T101" s="174"/>
     </row>
     <row r="102" s="21" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A102" s="56">
+      <c r="A102" s="57">
         <v>30160003</v>
       </c>
-      <c r="B102" s="56">
+      <c r="B102" s="57">
         <v>101600</v>
       </c>
-      <c r="C102" s="56" t="s">
+      <c r="C102" s="57" t="s">
         <v>220</v>
       </c>
-      <c r="D102" s="56">
+      <c r="D102" s="57">
         <v>301603</v>
       </c>
       <c r="E102" s="21" t="s">
@@ -7103,7 +7117,7 @@
       <c r="F102" s="21" t="s">
         <v>225</v>
       </c>
-      <c r="G102" s="56">
+      <c r="G102" s="57">
         <v>2016001</v>
       </c>
       <c r="H102" s="21" t="s">
@@ -7115,25 +7129,25 @@
       <c r="J102" s="21" t="s">
         <v>221</v>
       </c>
-      <c r="K102" s="58" t="s">
+      <c r="K102" s="59" t="s">
         <v>222</v>
       </c>
       <c r="L102" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="T102" s="173"/>
+      <c r="T102" s="174"/>
     </row>
     <row r="103" s="22" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A103" s="174">
+      <c r="A103" s="175">
         <v>30150001</v>
       </c>
-      <c r="B103" s="174">
+      <c r="B103" s="175">
         <v>101500</v>
       </c>
-      <c r="C103" s="174" t="s">
+      <c r="C103" s="175" t="s">
         <v>226</v>
       </c>
-      <c r="D103" s="174">
+      <c r="D103" s="175">
         <v>301501</v>
       </c>
       <c r="E103" s="22" t="s">
@@ -7142,7 +7156,7 @@
       <c r="F103" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="G103" s="174">
+      <c r="G103" s="175">
         <v>2015002</v>
       </c>
       <c r="H103" s="22" t="s">
@@ -7151,25 +7165,25 @@
       <c r="I103" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="K103" s="175" t="s">
+      <c r="K103" s="176" t="s">
         <v>228</v>
       </c>
       <c r="L103" s="22" t="s">
         <v>229</v>
       </c>
-      <c r="T103" s="176"/>
+      <c r="T103" s="177"/>
     </row>
     <row r="104" s="22" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A104" s="174">
+      <c r="A104" s="175">
         <v>30150002</v>
       </c>
-      <c r="B104" s="174">
+      <c r="B104" s="175">
         <v>101500</v>
       </c>
-      <c r="C104" s="174" t="s">
+      <c r="C104" s="175" t="s">
         <v>226</v>
       </c>
-      <c r="D104" s="174">
+      <c r="D104" s="175">
         <v>301502</v>
       </c>
       <c r="E104" s="22" t="s">
@@ -7178,7 +7192,7 @@
       <c r="F104" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="G104" s="174">
+      <c r="G104" s="175">
         <v>2015001</v>
       </c>
       <c r="H104" s="22" t="s">
@@ -7190,25 +7204,25 @@
       <c r="J104" s="22" t="s">
         <v>231</v>
       </c>
-      <c r="K104" s="175">
+      <c r="K104" s="176">
         <v>10150030</v>
       </c>
       <c r="L104" s="22" t="s">
         <v>229</v>
       </c>
-      <c r="T104" s="176"/>
+      <c r="T104" s="177"/>
     </row>
     <row r="105" s="22" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A105" s="174">
+      <c r="A105" s="175">
         <v>30150003</v>
       </c>
-      <c r="B105" s="174">
+      <c r="B105" s="175">
         <v>101500</v>
       </c>
-      <c r="C105" s="174" t="s">
+      <c r="C105" s="175" t="s">
         <v>226</v>
       </c>
-      <c r="D105" s="174">
+      <c r="D105" s="175">
         <v>301503</v>
       </c>
       <c r="E105" s="22" t="s">
@@ -7217,7 +7231,7 @@
       <c r="F105" s="22" t="s">
         <v>214</v>
       </c>
-      <c r="G105" s="174">
+      <c r="G105" s="175">
         <v>2015001</v>
       </c>
       <c r="H105" s="22" t="s">
@@ -7226,25 +7240,25 @@
       <c r="I105" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="K105" s="175" t="s">
+      <c r="K105" s="176" t="s">
         <v>228</v>
       </c>
       <c r="L105" s="22" t="s">
         <v>229</v>
       </c>
-      <c r="T105" s="176"/>
+      <c r="T105" s="177"/>
     </row>
     <row r="106" s="23" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A106" s="74">
+      <c r="A106" s="75">
         <v>30260001</v>
       </c>
-      <c r="B106" s="74">
+      <c r="B106" s="75">
         <v>102600</v>
       </c>
-      <c r="C106" s="74" t="s">
+      <c r="C106" s="75" t="s">
         <v>233</v>
       </c>
-      <c r="D106" s="74">
+      <c r="D106" s="75">
         <v>302601</v>
       </c>
       <c r="E106" s="23" t="s">
@@ -7253,7 +7267,7 @@
       <c r="F106" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="G106" s="74">
+      <c r="G106" s="75">
         <v>2026001</v>
       </c>
       <c r="H106" s="23" t="s">
@@ -7262,25 +7276,25 @@
       <c r="I106" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="K106" s="177" t="s">
+      <c r="K106" s="178" t="s">
         <v>234</v>
       </c>
       <c r="L106" s="23" t="s">
         <v>235</v>
       </c>
-      <c r="T106" s="178"/>
+      <c r="T106" s="179"/>
     </row>
     <row r="107" s="23" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A107" s="74">
+      <c r="A107" s="75">
         <v>30260002</v>
       </c>
-      <c r="B107" s="74">
+      <c r="B107" s="75">
         <v>102600</v>
       </c>
-      <c r="C107" s="74" t="s">
+      <c r="C107" s="75" t="s">
         <v>233</v>
       </c>
-      <c r="D107" s="74">
+      <c r="D107" s="75">
         <v>302602</v>
       </c>
       <c r="E107" s="23" t="s">
@@ -7289,7 +7303,7 @@
       <c r="F107" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="G107" s="74">
+      <c r="G107" s="75">
         <v>2026001</v>
       </c>
       <c r="H107" s="23" t="s">
@@ -7298,25 +7312,25 @@
       <c r="I107" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="K107" s="177" t="s">
+      <c r="K107" s="178" t="s">
         <v>234</v>
       </c>
       <c r="L107" s="23" t="s">
         <v>235</v>
       </c>
-      <c r="T107" s="178"/>
+      <c r="T107" s="179"/>
     </row>
     <row r="108" s="23" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A108" s="74">
+      <c r="A108" s="75">
         <v>30260003</v>
       </c>
-      <c r="B108" s="74">
+      <c r="B108" s="75">
         <v>102600</v>
       </c>
-      <c r="C108" s="74" t="s">
+      <c r="C108" s="75" t="s">
         <v>233</v>
       </c>
-      <c r="D108" s="74">
+      <c r="D108" s="75">
         <v>302603</v>
       </c>
       <c r="E108" s="23" t="s">
@@ -7325,7 +7339,7 @@
       <c r="F108" s="23" t="s">
         <v>225</v>
       </c>
-      <c r="G108" s="74">
+      <c r="G108" s="75">
         <v>2026001</v>
       </c>
       <c r="H108" s="23" t="s">
@@ -7334,259 +7348,259 @@
       <c r="I108" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="K108" s="177" t="s">
+      <c r="K108" s="178" t="s">
         <v>234</v>
       </c>
       <c r="L108" s="23" t="s">
         <v>235</v>
       </c>
-      <c r="T108" s="178"/>
+      <c r="T108" s="179"/>
     </row>
     <row r="109" s="24" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A109" s="179">
+      <c r="A109" s="180">
         <v>30500001</v>
       </c>
-      <c r="B109" s="179">
+      <c r="B109" s="180">
         <v>105000</v>
       </c>
-      <c r="C109" s="179" t="s">
+      <c r="C109" s="180" t="s">
         <v>236</v>
       </c>
-      <c r="D109" s="179">
+      <c r="D109" s="180">
         <v>305001</v>
       </c>
-      <c r="E109" s="38" t="s">
+      <c r="E109" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="F109" s="38" t="s">
+      <c r="F109" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="G109" s="179">
+      <c r="G109" s="180">
         <v>2050001</v>
       </c>
-      <c r="H109" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="I109" s="38" t="s">
+      <c r="H109" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="I109" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="J109" s="38"/>
-      <c r="K109" s="38" t="s">
+      <c r="J109" s="39"/>
+      <c r="K109" s="39" t="s">
         <v>237</v>
       </c>
-      <c r="L109" s="38" t="s">
+      <c r="L109" s="39" t="s">
         <v>238</v>
       </c>
-      <c r="M109" s="38"/>
-      <c r="N109" s="38"/>
-      <c r="O109" s="38"/>
-      <c r="P109" s="38"/>
-      <c r="Q109" s="38"/>
-      <c r="R109" s="38"/>
-      <c r="S109" s="38"/>
-      <c r="T109" s="38"/>
+      <c r="M109" s="39"/>
+      <c r="N109" s="39"/>
+      <c r="O109" s="39"/>
+      <c r="P109" s="39"/>
+      <c r="Q109" s="39"/>
+      <c r="R109" s="39"/>
+      <c r="S109" s="39"/>
+      <c r="T109" s="39"/>
     </row>
     <row r="110" s="24" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A110" s="179">
+      <c r="A110" s="180">
         <v>30500002</v>
       </c>
-      <c r="B110" s="179">
+      <c r="B110" s="180">
         <v>105000</v>
       </c>
-      <c r="C110" s="179" t="s">
+      <c r="C110" s="180" t="s">
         <v>236</v>
       </c>
-      <c r="D110" s="179">
+      <c r="D110" s="180">
         <v>305002</v>
       </c>
-      <c r="E110" s="38" t="s">
+      <c r="E110" s="39" t="s">
         <v>239</v>
       </c>
-      <c r="F110" s="38" t="s">
+      <c r="F110" s="39" t="s">
         <v>240</v>
       </c>
-      <c r="G110" s="179">
+      <c r="G110" s="180">
         <v>2050001</v>
       </c>
-      <c r="H110" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="I110" s="38" t="s">
+      <c r="H110" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="I110" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="J110" s="38"/>
-      <c r="K110" s="38" t="s">
+      <c r="J110" s="39"/>
+      <c r="K110" s="39" t="s">
         <v>237</v>
       </c>
-      <c r="L110" s="38" t="s">
+      <c r="L110" s="39" t="s">
         <v>238</v>
       </c>
-      <c r="M110" s="38"/>
-      <c r="N110" s="38"/>
-      <c r="O110" s="38"/>
-      <c r="P110" s="38"/>
-      <c r="Q110" s="38"/>
-      <c r="R110" s="38"/>
-      <c r="S110" s="38"/>
-      <c r="T110" s="38"/>
+      <c r="M110" s="39"/>
+      <c r="N110" s="39"/>
+      <c r="O110" s="39"/>
+      <c r="P110" s="39"/>
+      <c r="Q110" s="39"/>
+      <c r="R110" s="39"/>
+      <c r="S110" s="39"/>
+      <c r="T110" s="39"/>
     </row>
     <row r="111" s="24" customFormat="1" ht="20.1" customHeight="1" spans="1:20">
-      <c r="A111" s="179">
+      <c r="A111" s="180">
         <v>30500003</v>
       </c>
-      <c r="B111" s="179">
+      <c r="B111" s="180">
         <v>105000</v>
       </c>
-      <c r="C111" s="179" t="s">
+      <c r="C111" s="180" t="s">
         <v>236</v>
       </c>
-      <c r="D111" s="179">
+      <c r="D111" s="180">
         <v>305003</v>
       </c>
-      <c r="E111" s="38" t="s">
+      <c r="E111" s="39" t="s">
         <v>241</v>
       </c>
-      <c r="F111" s="38" t="s">
+      <c r="F111" s="39" t="s">
         <v>242</v>
       </c>
-      <c r="G111" s="179">
+      <c r="G111" s="180">
         <v>2050001</v>
       </c>
-      <c r="H111" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="I111" s="38" t="s">
+      <c r="H111" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="I111" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="J111" s="38"/>
-      <c r="K111" s="38" t="s">
+      <c r="J111" s="39"/>
+      <c r="K111" s="39" t="s">
         <v>237</v>
       </c>
-      <c r="L111" s="38" t="s">
+      <c r="L111" s="39" t="s">
         <v>238</v>
       </c>
-      <c r="M111" s="38"/>
-      <c r="N111" s="38"/>
-      <c r="O111" s="38"/>
-      <c r="P111" s="38"/>
-      <c r="Q111" s="38"/>
-      <c r="R111" s="38"/>
-      <c r="S111" s="38"/>
-      <c r="T111" s="38"/>
+      <c r="M111" s="39"/>
+      <c r="N111" s="39"/>
+      <c r="O111" s="39"/>
+      <c r="P111" s="39"/>
+      <c r="Q111" s="39"/>
+      <c r="R111" s="39"/>
+      <c r="S111" s="39"/>
+      <c r="T111" s="39"/>
     </row>
     <row r="112" s="25" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A112" s="180">
+      <c r="A112" s="181">
         <v>30510001</v>
       </c>
-      <c r="B112" s="180">
+      <c r="B112" s="181">
         <v>105100</v>
       </c>
-      <c r="C112" s="180" t="s">
+      <c r="C112" s="181" t="s">
         <v>243</v>
       </c>
-      <c r="D112" s="180">
+      <c r="D112" s="181">
         <v>305101</v>
       </c>
-      <c r="E112" s="181" t="s">
+      <c r="E112" s="182" t="s">
         <v>244</v>
       </c>
       <c r="F112" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="G112" s="180">
+      <c r="G112" s="181">
         <v>2051001</v>
       </c>
-      <c r="H112" s="181" t="s">
-        <v>63</v>
-      </c>
-      <c r="I112" s="181" t="s">
+      <c r="H112" s="182" t="s">
+        <v>63</v>
+      </c>
+      <c r="I112" s="182" t="s">
         <v>83</v>
       </c>
-      <c r="K112" s="182"/>
-      <c r="T112" s="183"/>
+      <c r="K112" s="183"/>
+      <c r="T112" s="184"/>
     </row>
     <row r="113" s="25" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A113" s="180">
+      <c r="A113" s="181">
         <v>30510002</v>
       </c>
-      <c r="B113" s="180">
+      <c r="B113" s="181">
         <v>105100</v>
       </c>
-      <c r="C113" s="180" t="s">
+      <c r="C113" s="181" t="s">
         <v>243</v>
       </c>
-      <c r="D113" s="180">
+      <c r="D113" s="181">
         <v>305102</v>
       </c>
-      <c r="E113" s="181" t="s">
+      <c r="E113" s="182" t="s">
         <v>245</v>
       </c>
       <c r="F113" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="G113" s="180">
+      <c r="G113" s="181">
         <v>2051002</v>
       </c>
-      <c r="H113" s="181" t="s">
-        <v>63</v>
-      </c>
-      <c r="I113" s="181" t="s">
+      <c r="H113" s="182" t="s">
+        <v>63</v>
+      </c>
+      <c r="I113" s="182" t="s">
         <v>83</v>
       </c>
-      <c r="K113" s="182"/>
-      <c r="T113" s="183"/>
+      <c r="K113" s="183"/>
+      <c r="T113" s="184"/>
     </row>
     <row r="114" s="25" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A114" s="180">
+      <c r="A114" s="181">
         <v>30510003</v>
       </c>
-      <c r="B114" s="180">
+      <c r="B114" s="181">
         <v>105100</v>
       </c>
-      <c r="C114" s="180" t="s">
+      <c r="C114" s="181" t="s">
         <v>243</v>
       </c>
-      <c r="D114" s="180">
+      <c r="D114" s="181">
         <v>305103</v>
       </c>
-      <c r="E114" s="181" t="s">
+      <c r="E114" s="182" t="s">
         <v>246</v>
       </c>
       <c r="F114" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="G114" s="180">
+      <c r="G114" s="181">
         <v>2051003</v>
       </c>
-      <c r="H114" s="181" t="s">
-        <v>63</v>
-      </c>
-      <c r="I114" s="181" t="s">
+      <c r="H114" s="182" t="s">
+        <v>63</v>
+      </c>
+      <c r="I114" s="182" t="s">
         <v>83</v>
       </c>
-      <c r="K114" s="182"/>
-      <c r="T114" s="183"/>
+      <c r="K114" s="183"/>
+      <c r="T114" s="184"/>
     </row>
     <row r="115" s="26" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A115" s="184">
+      <c r="A115" s="185">
         <v>30020001</v>
       </c>
-      <c r="B115" s="184">
+      <c r="B115" s="185">
         <v>400200</v>
       </c>
-      <c r="C115" s="184" t="s">
+      <c r="C115" s="185" t="s">
         <v>247</v>
       </c>
-      <c r="D115" s="184">
+      <c r="D115" s="185">
         <v>300201</v>
       </c>
-      <c r="E115" s="185" t="s">
+      <c r="E115" s="186" t="s">
         <v>248</v>
       </c>
       <c r="F115" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="G115" s="184">
+      <c r="G115" s="185">
         <v>2002001</v>
       </c>
       <c r="H115" s="26" t="s">
@@ -7595,34 +7609,34 @@
       <c r="I115" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="K115" s="186" t="s">
+      <c r="K115" s="187" t="s">
         <v>249</v>
       </c>
       <c r="L115" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="T115" s="187"/>
+      <c r="T115" s="188"/>
     </row>
     <row r="116" s="26" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A116" s="184">
+      <c r="A116" s="185">
         <v>30020002</v>
       </c>
-      <c r="B116" s="184">
+      <c r="B116" s="185">
         <v>400200</v>
       </c>
-      <c r="C116" s="184" t="s">
+      <c r="C116" s="185" t="s">
         <v>247</v>
       </c>
-      <c r="D116" s="184">
+      <c r="D116" s="185">
         <v>300202</v>
       </c>
-      <c r="E116" s="185" t="s">
+      <c r="E116" s="186" t="s">
         <v>110</v>
       </c>
       <c r="F116" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="G116" s="184">
+      <c r="G116" s="185">
         <v>2002001</v>
       </c>
       <c r="H116" s="26" t="s">
@@ -7631,34 +7645,34 @@
       <c r="I116" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="K116" s="186" t="s">
+      <c r="K116" s="187" t="s">
         <v>249</v>
       </c>
       <c r="L116" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="T116" s="187"/>
+      <c r="T116" s="188"/>
     </row>
     <row r="117" s="26" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A117" s="184">
+      <c r="A117" s="185">
         <v>30020003</v>
       </c>
-      <c r="B117" s="184">
+      <c r="B117" s="185">
         <v>400200</v>
       </c>
-      <c r="C117" s="184" t="s">
+      <c r="C117" s="185" t="s">
         <v>247</v>
       </c>
-      <c r="D117" s="184">
+      <c r="D117" s="185">
         <v>300203</v>
       </c>
-      <c r="E117" s="185" t="s">
+      <c r="E117" s="186" t="s">
         <v>130</v>
       </c>
       <c r="F117" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="G117" s="184">
+      <c r="G117" s="185">
         <v>2002001</v>
       </c>
       <c r="H117" s="26" t="s">
@@ -7667,394 +7681,394 @@
       <c r="I117" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="K117" s="186" t="s">
+      <c r="K117" s="187" t="s">
         <v>249</v>
       </c>
       <c r="L117" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="T117" s="187"/>
+      <c r="T117" s="188"/>
     </row>
     <row r="118" s="15" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A118" s="136">
+      <c r="A118" s="137">
         <v>30800001</v>
       </c>
-      <c r="B118" s="188">
+      <c r="B118" s="189">
         <v>100800</v>
       </c>
-      <c r="C118" s="188" t="s">
+      <c r="C118" s="189" t="s">
         <v>251</v>
       </c>
-      <c r="D118" s="188">
+      <c r="D118" s="189">
         <v>308001</v>
       </c>
-      <c r="E118" s="138" t="s">
+      <c r="E118" s="139" t="s">
         <v>110</v>
       </c>
       <c r="F118" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="G118" s="188">
+      <c r="G118" s="189">
         <v>2080001</v>
       </c>
-      <c r="H118" s="138" t="s">
-        <v>63</v>
-      </c>
-      <c r="I118" s="138" t="s">
+      <c r="H118" s="139" t="s">
+        <v>63</v>
+      </c>
+      <c r="I118" s="139" t="s">
         <v>83</v>
       </c>
-      <c r="K118" s="99" t="s">
+      <c r="K118" s="100" t="s">
         <v>252</v>
       </c>
       <c r="L118" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="T118" s="140"/>
+      <c r="T118" s="141"/>
     </row>
     <row r="119" s="15" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A119" s="136">
+      <c r="A119" s="137">
         <v>30800002</v>
       </c>
-      <c r="B119" s="188">
+      <c r="B119" s="189">
         <v>100800</v>
       </c>
-      <c r="C119" s="188" t="s">
+      <c r="C119" s="189" t="s">
         <v>251</v>
       </c>
-      <c r="D119" s="188">
+      <c r="D119" s="189">
         <v>308002</v>
       </c>
-      <c r="E119" s="138" t="s">
+      <c r="E119" s="139" t="s">
         <v>130</v>
       </c>
       <c r="F119" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G119" s="188">
+      <c r="G119" s="189">
         <v>2080001</v>
       </c>
-      <c r="H119" s="138" t="s">
-        <v>63</v>
-      </c>
-      <c r="I119" s="138" t="s">
+      <c r="H119" s="139" t="s">
+        <v>63</v>
+      </c>
+      <c r="I119" s="139" t="s">
         <v>83</v>
       </c>
-      <c r="K119" s="99" t="s">
+      <c r="K119" s="100" t="s">
         <v>252</v>
       </c>
       <c r="L119" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="T119" s="140"/>
+      <c r="T119" s="141"/>
     </row>
     <row r="120" s="15" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A120" s="136">
+      <c r="A120" s="137">
         <v>30800003</v>
       </c>
-      <c r="B120" s="188">
+      <c r="B120" s="189">
         <v>100800</v>
       </c>
-      <c r="C120" s="188" t="s">
+      <c r="C120" s="189" t="s">
         <v>251</v>
       </c>
-      <c r="D120" s="188">
+      <c r="D120" s="189">
         <v>308003</v>
       </c>
-      <c r="E120" s="138" t="s">
+      <c r="E120" s="139" t="s">
         <v>131</v>
       </c>
       <c r="F120" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="G120" s="188">
+      <c r="G120" s="189">
         <v>2080001</v>
       </c>
-      <c r="H120" s="138" t="s">
-        <v>63</v>
-      </c>
-      <c r="I120" s="138" t="s">
+      <c r="H120" s="139" t="s">
+        <v>63</v>
+      </c>
+      <c r="I120" s="139" t="s">
         <v>83</v>
       </c>
-      <c r="K120" s="99" t="s">
+      <c r="K120" s="100" t="s">
         <v>252</v>
       </c>
       <c r="L120" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="T120" s="140"/>
+      <c r="T120" s="141"/>
     </row>
     <row r="121" s="27" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A121" s="65">
+      <c r="A121" s="66">
         <v>30530001</v>
       </c>
-      <c r="B121" s="65">
+      <c r="B121" s="66">
         <v>105300</v>
       </c>
-      <c r="C121" s="65" t="s">
+      <c r="C121" s="66" t="s">
         <v>254</v>
       </c>
-      <c r="D121" s="189">
+      <c r="D121" s="190">
         <v>305301</v>
       </c>
-      <c r="E121" s="67" t="s">
+      <c r="E121" s="68" t="s">
         <v>110</v>
       </c>
-      <c r="F121" s="190" t="s">
+      <c r="F121" s="191" t="s">
         <v>111</v>
       </c>
-      <c r="G121" s="189">
+      <c r="G121" s="190">
         <v>2053001</v>
       </c>
-      <c r="H121" s="191" t="s">
-        <v>63</v>
-      </c>
-      <c r="I121" s="191" t="s">
+      <c r="H121" s="192" t="s">
+        <v>63</v>
+      </c>
+      <c r="I121" s="192" t="s">
         <v>83</v>
       </c>
       <c r="K121" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="L121" s="67" t="s">
+      <c r="L121" s="68" t="s">
         <v>256</v>
       </c>
-      <c r="T121" s="192"/>
+      <c r="T121" s="193"/>
     </row>
     <row r="122" s="27" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A122" s="65">
+      <c r="A122" s="66">
         <v>30530002</v>
       </c>
-      <c r="B122" s="65">
+      <c r="B122" s="66">
         <v>105300</v>
       </c>
-      <c r="C122" s="65" t="s">
+      <c r="C122" s="66" t="s">
         <v>254</v>
       </c>
-      <c r="D122" s="189">
+      <c r="D122" s="190">
         <v>305302</v>
       </c>
-      <c r="E122" s="67" t="s">
+      <c r="E122" s="68" t="s">
         <v>130</v>
       </c>
-      <c r="F122" s="190" t="s">
+      <c r="F122" s="191" t="s">
         <v>82</v>
       </c>
-      <c r="G122" s="189">
+      <c r="G122" s="190">
         <v>2053001</v>
       </c>
-      <c r="H122" s="191" t="s">
-        <v>63</v>
-      </c>
-      <c r="I122" s="191" t="s">
+      <c r="H122" s="192" t="s">
+        <v>63</v>
+      </c>
+      <c r="I122" s="192" t="s">
         <v>83</v>
       </c>
       <c r="K122" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="L122" s="67" t="s">
+      <c r="L122" s="68" t="s">
         <v>256</v>
       </c>
-      <c r="T122" s="192"/>
+      <c r="T122" s="193"/>
     </row>
     <row r="123" s="28" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A123" s="65">
+      <c r="A123" s="66">
         <v>30530003</v>
       </c>
-      <c r="B123" s="65">
+      <c r="B123" s="66">
         <v>105300</v>
       </c>
-      <c r="C123" s="65" t="s">
+      <c r="C123" s="66" t="s">
         <v>254</v>
       </c>
-      <c r="D123" s="189">
+      <c r="D123" s="190">
         <v>305303</v>
       </c>
-      <c r="E123" s="67" t="s">
+      <c r="E123" s="68" t="s">
         <v>131</v>
       </c>
-      <c r="F123" s="190" t="s">
+      <c r="F123" s="191" t="s">
         <v>86</v>
       </c>
-      <c r="G123" s="189">
+      <c r="G123" s="190">
         <v>2053001</v>
       </c>
-      <c r="H123" s="191" t="s">
-        <v>63</v>
-      </c>
-      <c r="I123" s="191" t="s">
+      <c r="H123" s="192" t="s">
+        <v>63</v>
+      </c>
+      <c r="I123" s="192" t="s">
         <v>83</v>
       </c>
       <c r="K123" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="L123" s="67" t="s">
+      <c r="L123" s="68" t="s">
         <v>256</v>
       </c>
-      <c r="T123" s="193"/>
+      <c r="T123" s="194"/>
     </row>
     <row r="124" s="9" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A124" s="106">
+      <c r="A124" s="107">
         <v>30570001</v>
       </c>
-      <c r="B124" s="106">
+      <c r="B124" s="107">
         <v>105700</v>
       </c>
-      <c r="C124" s="106" t="s">
+      <c r="C124" s="107" t="s">
         <v>257</v>
       </c>
-      <c r="D124" s="194">
+      <c r="D124" s="195">
         <v>305701</v>
       </c>
-      <c r="E124" s="108" t="s">
+      <c r="E124" s="109" t="s">
         <v>110</v>
       </c>
-      <c r="F124" s="195" t="s">
+      <c r="F124" s="196" t="s">
         <v>111</v>
       </c>
-      <c r="G124" s="194">
+      <c r="G124" s="195">
         <v>2057001</v>
       </c>
-      <c r="H124" s="196" t="s">
-        <v>63</v>
-      </c>
-      <c r="I124" s="196" t="s">
+      <c r="H124" s="197" t="s">
+        <v>63</v>
+      </c>
+      <c r="I124" s="197" t="s">
         <v>83</v>
       </c>
-      <c r="K124" s="109" t="s">
+      <c r="K124" s="110" t="s">
         <v>258</v>
       </c>
-      <c r="L124" s="197" t="s">
+      <c r="L124" s="198" t="s">
         <v>259</v>
       </c>
-      <c r="T124" s="110"/>
+      <c r="T124" s="111"/>
     </row>
     <row r="125" s="9" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A125" s="106">
+      <c r="A125" s="107">
         <v>30570002</v>
       </c>
-      <c r="B125" s="106">
+      <c r="B125" s="107">
         <v>105700</v>
       </c>
-      <c r="C125" s="106" t="s">
+      <c r="C125" s="107" t="s">
         <v>257</v>
       </c>
-      <c r="D125" s="194">
+      <c r="D125" s="195">
         <v>305702</v>
       </c>
-      <c r="E125" s="108" t="s">
+      <c r="E125" s="109" t="s">
         <v>130</v>
       </c>
-      <c r="F125" s="195" t="s">
+      <c r="F125" s="196" t="s">
         <v>82</v>
       </c>
-      <c r="G125" s="194">
+      <c r="G125" s="195">
         <v>2057001</v>
       </c>
-      <c r="H125" s="196" t="s">
-        <v>63</v>
-      </c>
-      <c r="I125" s="196" t="s">
+      <c r="H125" s="197" t="s">
+        <v>63</v>
+      </c>
+      <c r="I125" s="197" t="s">
         <v>83</v>
       </c>
-      <c r="K125" s="109" t="s">
+      <c r="K125" s="110" t="s">
         <v>258</v>
       </c>
-      <c r="L125" s="197" t="s">
+      <c r="L125" s="198" t="s">
         <v>259</v>
       </c>
-      <c r="T125" s="110"/>
+      <c r="T125" s="111"/>
     </row>
     <row r="126" s="9" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A126" s="106">
+      <c r="A126" s="107">
         <v>30570003</v>
       </c>
-      <c r="B126" s="106">
+      <c r="B126" s="107">
         <v>105700</v>
       </c>
-      <c r="C126" s="106" t="s">
+      <c r="C126" s="107" t="s">
         <v>257</v>
       </c>
-      <c r="D126" s="194">
+      <c r="D126" s="195">
         <v>305703</v>
       </c>
-      <c r="E126" s="108" t="s">
+      <c r="E126" s="109" t="s">
         <v>131</v>
       </c>
-      <c r="F126" s="195" t="s">
+      <c r="F126" s="196" t="s">
         <v>86</v>
       </c>
-      <c r="G126" s="194">
+      <c r="G126" s="195">
         <v>2057001</v>
       </c>
-      <c r="H126" s="196" t="s">
-        <v>63</v>
-      </c>
-      <c r="I126" s="196" t="s">
+      <c r="H126" s="197" t="s">
+        <v>63</v>
+      </c>
+      <c r="I126" s="197" t="s">
         <v>83</v>
       </c>
-      <c r="K126" s="109" t="s">
+      <c r="K126" s="110" t="s">
         <v>258</v>
       </c>
-      <c r="L126" s="197" t="s">
+      <c r="L126" s="198" t="s">
         <v>259</v>
       </c>
-      <c r="T126" s="110"/>
+      <c r="T126" s="111"/>
     </row>
     <row r="127" s="29" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A127" s="198">
+      <c r="A127" s="199">
         <v>30580001</v>
       </c>
-      <c r="B127" s="198">
+      <c r="B127" s="199">
         <v>105800</v>
       </c>
-      <c r="C127" s="198" t="s">
+      <c r="C127" s="199" t="s">
         <v>260</v>
       </c>
-      <c r="D127" s="199">
+      <c r="D127" s="200">
         <v>305801</v>
       </c>
-      <c r="E127" s="200" t="s">
+      <c r="E127" s="201" t="s">
         <v>110</v>
       </c>
       <c r="F127" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="G127" s="199">
+      <c r="G127" s="200">
         <v>2058001</v>
       </c>
-      <c r="H127" s="201" t="s">
-        <v>63</v>
-      </c>
-      <c r="I127" s="201" t="s">
+      <c r="H127" s="202" t="s">
+        <v>63</v>
+      </c>
+      <c r="I127" s="202" t="s">
         <v>83</v>
       </c>
-      <c r="K127" s="202" t="s">
+      <c r="K127" s="203" t="s">
         <v>261</v>
       </c>
       <c r="L127" s="29" t="s">
         <v>262</v>
       </c>
-      <c r="T127" s="203"/>
+      <c r="T127" s="204"/>
     </row>
     <row r="128" s="30" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A128" s="204">
+      <c r="A128" s="205">
         <v>30480001</v>
       </c>
-      <c r="B128" s="204">
+      <c r="B128" s="205">
         <v>104800</v>
       </c>
-      <c r="C128" s="204" t="s">
+      <c r="C128" s="205" t="s">
         <v>263</v>
       </c>
-      <c r="D128" s="204">
+      <c r="D128" s="205">
         <v>304801</v>
       </c>
       <c r="E128" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="F128" s="205" t="s">
+      <c r="F128" s="206" t="s">
         <v>111</v>
       </c>
-      <c r="G128" s="204">
+      <c r="G128" s="205">
         <v>2048001</v>
       </c>
       <c r="H128" s="30" t="s">
@@ -8069,30 +8083,30 @@
       <c r="L128" s="30" t="s">
         <v>265</v>
       </c>
-      <c r="M128" s="206"/>
-      <c r="N128" s="206"/>
-      <c r="T128" s="207"/>
+      <c r="M128" s="207"/>
+      <c r="N128" s="207"/>
+      <c r="T128" s="208"/>
     </row>
     <row r="129" s="30" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A129" s="204">
+      <c r="A129" s="205">
         <v>30480002</v>
       </c>
-      <c r="B129" s="204">
+      <c r="B129" s="205">
         <v>104800</v>
       </c>
-      <c r="C129" s="204" t="s">
+      <c r="C129" s="205" t="s">
         <v>263</v>
       </c>
-      <c r="D129" s="204">
+      <c r="D129" s="205">
         <v>304802</v>
       </c>
       <c r="E129" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="F129" s="205" t="s">
+      <c r="F129" s="206" t="s">
         <v>82</v>
       </c>
-      <c r="G129" s="204">
+      <c r="G129" s="205">
         <v>2048001</v>
       </c>
       <c r="H129" s="30" t="s">
@@ -8107,28 +8121,28 @@
       <c r="L129" s="30" t="s">
         <v>265</v>
       </c>
-      <c r="T129" s="208"/>
+      <c r="T129" s="209"/>
     </row>
     <row r="130" s="30" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A130" s="204">
+      <c r="A130" s="205">
         <v>30480003</v>
       </c>
-      <c r="B130" s="204">
+      <c r="B130" s="205">
         <v>104800</v>
       </c>
-      <c r="C130" s="204" t="s">
+      <c r="C130" s="205" t="s">
         <v>263</v>
       </c>
-      <c r="D130" s="204">
+      <c r="D130" s="205">
         <v>304803</v>
       </c>
       <c r="E130" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="F130" s="205" t="s">
+      <c r="F130" s="206" t="s">
         <v>86</v>
       </c>
-      <c r="G130" s="204">
+      <c r="G130" s="205">
         <v>2048001</v>
       </c>
       <c r="H130" s="30" t="s">
@@ -8143,19 +8157,19 @@
       <c r="L130" s="30" t="s">
         <v>265</v>
       </c>
-      <c r="T130" s="208"/>
+      <c r="T130" s="209"/>
     </row>
     <row r="131" s="31" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A131" s="95">
+      <c r="A131" s="96">
         <v>30550101</v>
       </c>
-      <c r="B131" s="95">
+      <c r="B131" s="96">
         <v>105501</v>
       </c>
-      <c r="C131" s="95" t="s">
+      <c r="C131" s="96" t="s">
         <v>266</v>
       </c>
-      <c r="D131" s="95">
+      <c r="D131" s="96">
         <v>305501</v>
       </c>
       <c r="E131" s="31" t="s">
@@ -8164,35 +8178,35 @@
       <c r="F131" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="G131" s="95">
+      <c r="G131" s="96">
         <v>2055011</v>
       </c>
-      <c r="H131" s="209" t="s">
+      <c r="H131" s="210" t="s">
         <v>63</v>
       </c>
       <c r="I131" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="K131" s="97"/>
-      <c r="Q131" s="209" t="s">
+      <c r="K131" s="98"/>
+      <c r="Q131" s="210" t="s">
         <v>268</v>
       </c>
       <c r="S131" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="T131" s="210"/>
+      <c r="T131" s="211"/>
     </row>
     <row r="132" s="32" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A132" s="37">
+      <c r="A132" s="38">
         <v>30410001</v>
       </c>
-      <c r="B132" s="37">
+      <c r="B132" s="38">
         <v>104100</v>
       </c>
-      <c r="C132" s="37" t="s">
+      <c r="C132" s="38" t="s">
         <v>269</v>
       </c>
-      <c r="D132" s="37">
+      <c r="D132" s="38">
         <v>304101</v>
       </c>
       <c r="E132" s="32" t="s">
@@ -8201,7 +8215,7 @@
       <c r="F132" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="G132" s="37">
+      <c r="G132" s="38">
         <v>2041001</v>
       </c>
       <c r="H132" s="32" t="s">
@@ -8210,27 +8224,27 @@
       <c r="I132" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="K132" s="39" t="s">
+      <c r="K132" s="40" t="s">
         <v>270</v>
       </c>
-      <c r="L132" s="211" t="s">
+      <c r="L132" s="212" t="s">
         <v>271</v>
       </c>
-      <c r="M132" s="211"/>
-      <c r="N132" s="211"/>
-      <c r="T132" s="44"/>
+      <c r="M132" s="212"/>
+      <c r="N132" s="212"/>
+      <c r="T132" s="45"/>
     </row>
     <row r="133" s="33" customFormat="1" ht="16.5" spans="1:20">
-      <c r="A133" s="212">
+      <c r="A133" s="213">
         <v>30420001</v>
       </c>
-      <c r="B133" s="212">
+      <c r="B133" s="213">
         <v>104200</v>
       </c>
-      <c r="C133" s="212" t="s">
+      <c r="C133" s="213" t="s">
         <v>272</v>
       </c>
-      <c r="D133" s="212">
+      <c r="D133" s="213">
         <v>304201</v>
       </c>
       <c r="E133" s="33" t="s">
@@ -8239,7 +8253,7 @@
       <c r="F133" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="G133" s="212">
+      <c r="G133" s="213">
         <v>2042001</v>
       </c>
       <c r="H133" s="33" t="s">
@@ -8248,118 +8262,127 @@
       <c r="I133" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="K133" s="213" t="s">
+      <c r="K133" s="214" t="s">
         <v>273</v>
       </c>
       <c r="L133" s="33" t="s">
         <v>271</v>
       </c>
-      <c r="T133" s="214"/>
-    </row>
-    <row r="134" spans="1:20">
-      <c r="A134" s="34">
+      <c r="T133" s="215"/>
+    </row>
+    <row r="134" s="34" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A134" s="216">
         <v>30190001</v>
       </c>
-      <c r="B134" s="34">
+      <c r="B134" s="216">
         <v>101900</v>
       </c>
-      <c r="C134" s="34" t="s">
+      <c r="C134" s="216" t="s">
         <v>274</v>
       </c>
-      <c r="D134" s="34">
+      <c r="D134" s="216">
         <v>301901</v>
       </c>
-      <c r="E134" t="s">
+      <c r="E134" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="F134" t="s">
+      <c r="F134" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="G134" s="34">
+      <c r="G134" s="216">
         <v>2019001</v>
       </c>
-      <c r="H134" t="s">
-        <v>63</v>
-      </c>
-      <c r="I134" t="s">
+      <c r="H134" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="I134" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="K134" s="35" t="s">
+      <c r="K134" s="217" t="s">
         <v>275</v>
       </c>
-      <c r="L134" t="s">
+      <c r="L134" s="34" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="135" spans="1:20">
-      <c r="A135" s="34">
+      <c r="M134" s="34"/>
+      <c r="N134" s="34"/>
+      <c r="T134" s="218"/>
+    </row>
+    <row r="135" s="34" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A135" s="216">
         <v>30190002</v>
       </c>
-      <c r="B135" s="34">
+      <c r="B135" s="216">
         <v>101900</v>
       </c>
-      <c r="C135" s="34" t="s">
+      <c r="C135" s="216" t="s">
         <v>274</v>
       </c>
-      <c r="D135" s="34">
+      <c r="D135" s="216">
         <v>301902</v>
       </c>
-      <c r="E135" t="s">
+      <c r="E135" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="F135" t="s">
+      <c r="F135" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="G135" s="34">
+      <c r="G135" s="216">
         <v>2019001</v>
       </c>
-      <c r="H135" t="s">
-        <v>63</v>
-      </c>
-      <c r="I135" t="s">
+      <c r="H135" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="I135" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="K135" s="35" t="s">
+      <c r="K135" s="217" t="s">
         <v>275</v>
       </c>
-      <c r="L135" t="s">
+      <c r="L135" s="34" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="136" spans="1:20">
-      <c r="A136" s="34">
+      <c r="M135" s="34"/>
+      <c r="N135" s="34"/>
+      <c r="T135" s="218"/>
+    </row>
+    <row r="136" s="34" customFormat="1" ht="16.5" spans="1:20">
+      <c r="A136" s="216">
         <v>30190003</v>
       </c>
-      <c r="B136" s="34">
+      <c r="B136" s="216">
         <v>101900</v>
       </c>
-      <c r="C136" s="34" t="s">
+      <c r="C136" s="216" t="s">
         <v>274</v>
       </c>
-      <c r="D136" s="34">
+      <c r="D136" s="216">
         <v>301903</v>
       </c>
-      <c r="E136" t="s">
+      <c r="E136" s="34" t="s">
         <v>224</v>
       </c>
-      <c r="F136" t="s">
+      <c r="F136" s="34" t="s">
         <v>225</v>
       </c>
-      <c r="G136" s="34">
+      <c r="G136" s="216">
         <v>2019001</v>
       </c>
-      <c r="H136" t="s">
-        <v>63</v>
-      </c>
-      <c r="I136" t="s">
+      <c r="H136" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="I136" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="K136" s="35" t="s">
+      <c r="K136" s="217" t="s">
         <v>275</v>
       </c>
-      <c r="L136" t="s">
+      <c r="L136" s="34" t="s">
         <v>265</v>
       </c>
+      <c r="M136" s="34"/>
+      <c r="N136" s="34"/>
+      <c r="T136" s="218"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2">
